--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -2302,7 +2302,11 @@
           <t>annaa@smartek21.com</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2320,7 +2324,11 @@
           <t>anna@transactglobal.com</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2338,7 +2346,11 @@
           <t>annapurna.a@fime.com</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2356,7 +2368,11 @@
           <t>annie.manoj@grasko.com</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2374,7 +2390,11 @@
           <t>anoob.abraham@arcadia.com</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2392,7 +2412,11 @@
           <t>anshika.khaitan@getvymo.com</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2410,7 +2434,11 @@
           <t>anshu.anand@absolutdata.com</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2428,7 +2456,11 @@
           <t>ansumans@mindfiresolutions.com</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2446,7 +2478,11 @@
           <t>anto.faria@urbanladder.com</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2464,7 +2500,11 @@
           <t>anuj@deskera.com</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2482,7 +2522,11 @@
           <t>anuja@codenation.co.in</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2500,7 +2544,11 @@
           <t>anupam.j@gsl.in</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2518,7 +2566,11 @@
           <t>anupam.srivastava@reltio.com</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2536,7 +2588,11 @@
           <t>anupamadg@erevmax.com</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2554,7 +2610,11 @@
           <t>anupriya.gandhi@juliacomputing.com</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2572,7 +2632,11 @@
           <t>anurag.rana@sirionlabs.com</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2590,7 +2654,11 @@
           <t>anurags@talisma.com</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2608,7 +2676,11 @@
           <t>anurag@uniphore.com</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2626,7 +2698,11 @@
           <t>anusha@srswebsolutions.com</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2644,7 +2720,11 @@
           <t>anusha.kishore@loco.gg</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2662,7 +2742,11 @@
           <t>aparna.gunjikar@softnautics.com</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2680,7 +2764,11 @@
           <t>aparna.srikanth@appsian.com</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2698,7 +2786,11 @@
           <t>aradhana@safexpay.com</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2716,7 +2808,11 @@
           <t>arathi.gs@vyomlabs.com</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -2830,7 +2830,11 @@
           <t>arathi.prabhu@altruistahealth.com</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2848,7 +2852,11 @@
           <t>arathi@suntecgroup.com</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2866,7 +2874,11 @@
           <t>aravind.chandrasekar@tigerspike.com</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2884,7 +2896,11 @@
           <t>aravind.warrier@rapidvaluesolutions.com</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2902,7 +2918,11 @@
           <t>archana@aufait.in</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2920,7 +2940,11 @@
           <t>archana.kp@kilowott.com</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2938,7 +2962,11 @@
           <t>archana@quinbay.com</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2956,7 +2984,11 @@
           <t>archana.manne@locuz.com</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2974,7 +3006,11 @@
           <t>archana.sarda@microlise.com</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -3028,7 +3028,11 @@
           <t>archana.shinde@cognologix.com</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3046,7 +3050,11 @@
           <t>arif.memon@abzooba.com</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3064,7 +3072,11 @@
           <t>arindam.kar@yodlee.com</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3082,7 +3094,11 @@
           <t>arjita.chawla@quytech.com</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3100,7 +3116,11 @@
           <t>arjun.chatterjee@sunlife.com</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3118,7 +3138,11 @@
           <t>arpanaj@umbrellainfocare.com</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3136,7 +3160,11 @@
           <t>arpita.sarkar@webskitters.com</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3154,7 +3182,11 @@
           <t>qa@artoonsolutions.com</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3172,7 +3204,11 @@
           <t>aru.uppal@datdyn.com</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3190,7 +3226,11 @@
           <t>arun.kumar@bobtechsolutions.com</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3208,7 +3248,11 @@
           <t>arun.kumar@shipsy.io</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3226,7 +3270,11 @@
           <t>arun.kumar@wavicledata.com</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3244,7 +3292,11 @@
           <t>arun@theatem.com</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3262,7 +3314,11 @@
           <t>arun.ravi@ipsoft.com</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3280,7 +3336,11 @@
           <t>arun.singh@puresoftware.com</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -3358,7 +3358,11 @@
           <t>arun@xto10x.com</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3376,7 +3380,11 @@
           <t>arunima.bhushan@orcapodservices.com</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3394,7 +3402,11 @@
           <t>arushi.goel@betterplace.co.in</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3412,7 +3424,11 @@
           <t>arushi.sawhney@e2eresearch.com</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3430,7 +3446,11 @@
           <t>arvind.sadasivan@ekaplus.com</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3448,7 +3468,11 @@
           <t>sharon@srinsofttech.com</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3466,7 +3490,11 @@
           <t>asha.j@unilogcorp.com</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3484,7 +3512,11 @@
           <t>ashish.karnik@pavilion.io</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3502,7 +3534,11 @@
           <t>ashish.naidu@mindgate.in</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -3556,7 +3556,11 @@
           <t>ashok@spenmo.com</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3574,7 +3578,11 @@
           <t>ashok.putsala@senecaglobal.com</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3592,7 +3600,11 @@
           <t>ashok.seshadri@objectfrontier.com</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3610,7 +3622,11 @@
           <t>ashok.tripathy@bpoconvergence.com</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3628,7 +3644,11 @@
           <t>ashraf.kazi@simplifyhealthcare.com</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3646,7 +3666,11 @@
           <t>ashraf.mulla@qseap.com</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3664,7 +3688,11 @@
           <t>ashton.lawrie@iitms.co.in</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3682,7 +3710,11 @@
           <t>ashutosh@tuya.com</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3700,7 +3732,11 @@
           <t>ashwanib@decisionminds.com</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3718,7 +3754,11 @@
           <t>ashwani@successive.tech</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3736,7 +3776,11 @@
           <t>ashwin@suki.ai</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3754,7 +3798,11 @@
           <t>ashwini.ashok@eton-solutions.com</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3772,7 +3820,11 @@
           <t>ashwini.janardhanan@kaleyra.com</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3790,7 +3842,11 @@
           <t>agoka@workfusion.com</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3808,7 +3864,11 @@
           <t>aswin@psrtek.com</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -3886,7 +3886,11 @@
           <t>atin.karmokar@pentagon.co.in</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3904,7 +3908,11 @@
           <t>atul.kanknala@craveinfotech.com</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3922,7 +3930,11 @@
           <t>atul.pal@innefu.com</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3940,7 +3952,11 @@
           <t>avinash@sedintechnologies.com</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3958,7 +3974,11 @@
           <t>ayush.daryani@niftel.com</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3976,7 +3996,11 @@
           <t>ayush.sinha@sugarboxnetworks.com</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3994,7 +4018,11 @@
           <t>babitha.nambiar@opusconsulting.com</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4012,7 +4040,11 @@
           <t>babu_thoppil@mahindrasatyam.com</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4030,7 +4062,11 @@
           <t>balaji@isourceindia.com</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -4084,7 +4084,11 @@
           <t>balaji.thiyagarajan@thirdware.com</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4102,7 +4106,11 @@
           <t>balakrishna.shetty@genisys-group.com</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4120,7 +4128,11 @@
           <t>balaraju.g@nslhub.com</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4138,7 +4150,11 @@
           <t>balesh@adarshsolutions.com</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4156,7 +4172,11 @@
           <t>balneet.birah@netsolutions.com</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4174,7 +4194,11 @@
           <t>bandana@airditsoftware.com</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4192,7 +4216,11 @@
           <t>bandla.shyamprasad@terralogic.com</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4210,7 +4238,11 @@
           <t>banmeet.kour@itbd.net</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4228,7 +4260,11 @@
           <t>bagrawal@cpg-inc.com</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4246,7 +4282,11 @@
           <t>barkha@trellissoft.ai</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4264,7 +4304,11 @@
           <t>barkha@wobot.ai</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4282,7 +4326,11 @@
           <t>basava@kamivision.com</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4300,7 +4348,11 @@
           <t>batool.ali@electriphi.ai</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4318,7 +4370,11 @@
           <t>bedisha@reward360.co</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4336,7 +4392,11 @@
           <t>benoy.koshy@sisainfosec.com</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -4414,7 +4414,11 @@
           <t>bensely.zachariah@fulcrumdigital.com</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4432,7 +4436,11 @@
           <t>bensley.zachariah@fulcrumdigital.com</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4450,7 +4458,11 @@
           <t>benson.mendez@microobjects.net</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4468,7 +4480,11 @@
           <t>bhakti.dharod@idfy.com</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4486,7 +4502,11 @@
           <t>bharat.bhartia@workindia.in</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4504,7 +4524,11 @@
           <t>bharat@ka-nex.com</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4522,7 +4546,11 @@
           <t>bravipati@appstekcorp.com</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4540,7 +4568,11 @@
           <t>bhargavic@aissel.com</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4558,7 +4590,11 @@
           <t>bharti.negi@edifecs.com</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4576,7 +4612,11 @@
           <t>bhavana@netcore.co.in</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4594,7 +4634,11 @@
           <t>bkaklotar@diabsolut.com</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4612,7 +4656,11 @@
           <t>bhavik@games2win.com</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4630,7 +4678,11 @@
           <t>bhavika.sheth@itcgindia.com</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4648,7 +4700,11 @@
           <t>bhavin@mydukaan.io</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4666,7 +4722,11 @@
           <t>bhavya@supplywisdom.com</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4684,7 +4744,11 @@
           <t>bhawna@weexcel.in</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4702,7 +4766,11 @@
           <t>bhupesh.wasmatkar@verse.in</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4720,7 +4788,11 @@
           <t>biju.v@inapp.com</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4738,7 +4810,11 @@
           <t>bikram.dash@tatwa.info</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4756,7 +4832,11 @@
           <t>bindu.krishnan@ospyn.com</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4774,7 +4854,11 @@
           <t>binoy.varghese@rgigroup.com</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4792,7 +4876,11 @@
           <t>biplob.das@izmoltd.com</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4810,7 +4898,11 @@
           <t>birendra.rout@weavertec.com</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4828,7 +4920,11 @@
           <t>bishnu.rai@iglobalservices.net</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -4942,7 +4942,11 @@
           <t>bosky.w@totalitglobal.com</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4960,7 +4964,11 @@
           <t>brij@claritusconsulting.com</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4978,7 +4986,11 @@
           <t>britto@xoxoday.com</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4996,7 +5008,11 @@
           <t>bushra.mehdi@axeno.co</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5014,7 +5030,11 @@
           <t>byju@rdalabs.com</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5032,7 +5052,11 @@
           <t>capt.kansal@writerinformation.com</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -5050,7 +5074,11 @@
           <t>celina.joseph@extentia.com</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5068,7 +5096,11 @@
           <t>chainsingh.rathore@thegatewaycorp.com</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5086,7 +5118,11 @@
           <t>cbhattacharya@inventive-it.com</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -5140,7 +5140,11 @@
           <t>cray@netwoven.com</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -5158,7 +5162,11 @@
           <t>chaitanya.arikati@abjayon.com</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -5176,7 +5184,11 @@
           <t>chaitanya.kanthi@smartims.com</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -5194,7 +5206,11 @@
           <t>chaitanya.peeta@polygon.technology</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -5212,7 +5228,11 @@
           <t>chamola.hal@hal-dz.com</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5230,7 +5250,11 @@
           <t>chanchal.chandiok@northgateps.com</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5248,7 +5272,11 @@
           <t>chandan@noida.interrasystems.com</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5266,7 +5294,11 @@
           <t>chandan.kashyap@mysenseinc.com</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5284,7 +5316,11 @@
           <t>chandinid@saglobal.com</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5302,7 +5338,11 @@
           <t>chandini@moolya.com</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5320,7 +5360,11 @@
           <t>chandnic@lambdatest.com</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5338,7 +5382,11 @@
           <t>chandniyadav@ucreate.co.in</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5356,7 +5404,11 @@
           <t>chandra.prakash@innoverdigital.com</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5374,7 +5426,11 @@
           <t>chandra.ratra@navigaglobal.com</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5392,7 +5448,11 @@
           <t>chandra@srivensys.com</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -5470,7 +5470,11 @@
           <t>cgv@eclinicalsol.com</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5488,7 +5492,11 @@
           <t>chandrashekarr@softura.com</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5506,7 +5514,11 @@
           <t>chandresh.kumar@jagrannewmedia.com</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5524,7 +5536,11 @@
           <t>charan@srinipharma.com</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5542,7 +5558,11 @@
           <t>charles.t@palni.com</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5560,7 +5580,11 @@
           <t>charmaine@streamoid.com</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5578,7 +5602,11 @@
           <t>cheryl.anjelo@colortokens.com</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5596,7 +5624,11 @@
           <t>cverma@fcsltd.com</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5614,7 +5646,11 @@
           <t>chetna@gokwik.co</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -5668,7 +5668,11 @@
           <t>chhavi.bhatnagar@acnovate.com</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5686,7 +5690,11 @@
           <t>chinmoy.roy@catalyst-us.com</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5704,7 +5712,11 @@
           <t>b.chintan@introlligent.com</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5722,7 +5734,11 @@
           <t>chirag.patel1@rangtech.com</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5740,7 +5756,11 @@
           <t>chirag.shah@iflair.com</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5758,7 +5778,11 @@
           <t>chiranjeevip@byteridge.com</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5776,7 +5800,11 @@
           <t>chitram@zconsolutions.com</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5794,7 +5822,11 @@
           <t>chitra.ravi@ample.co.in</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5812,7 +5844,11 @@
           <t>cireesha.m@etisbew.com</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -5830,7 +5866,11 @@
           <t>saurabh@caastle.com</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5848,7 +5888,11 @@
           <t>cynthia@netcore.co.in</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5866,7 +5910,11 @@
           <t>damayanti.ghosh@getvymo.com</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5884,7 +5932,11 @@
           <t>daniel.shaw@kpipartners.com</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5902,7 +5954,11 @@
           <t>dathree.javvadi@vncservices.in</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -5920,7 +5976,11 @@
           <t>debashishb@interrait.com</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -5998,7 +5998,11 @@
           <t>debdutta.bhowmick@atidiv.com</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -6016,7 +6020,11 @@
           <t>debojit.das@betterplace.co.in</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -6034,7 +6042,11 @@
           <t>dpassanha@everydayhealth.com</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -6052,7 +6064,11 @@
           <t>deep@thinkbridge.in</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -6070,7 +6086,11 @@
           <t>deep.patel@ics-global.in</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -6088,7 +6108,11 @@
           <t>bdeepa@zeomega.com</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -6106,7 +6130,11 @@
           <t>deepa@prdxn.com</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -6124,7 +6152,11 @@
           <t>deepa.makhija@gupshup.io</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -6142,7 +6174,11 @@
           <t>deepa.mukherjee@esri.in</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -6196,7 +6196,11 @@
           <t>deepa.palaniswamy@ducenit.com</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -6214,7 +6218,11 @@
           <t>deepa.sripathi@konicaminolta.com</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -6232,7 +6240,11 @@
           <t>deepak.babu@appviewx.com</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -6250,7 +6262,11 @@
           <t>deepak.chavan@visiblealpha.com</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -6268,7 +6284,11 @@
           <t>deepak.deshpande@netmagicsolutions.com</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -6286,7 +6306,11 @@
           <t>deepak@uchicago.edu</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -6304,7 +6328,11 @@
           <t>dkhanna@ishir.com</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -6322,7 +6350,11 @@
           <t>deepak.melwani@galaxyweblinks.co.in</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -6340,7 +6372,11 @@
           <t>deepak.pawar@accutech.co.in</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -6358,7 +6394,11 @@
           <t>deepak.ramakrishnan@csquare.in</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -6376,7 +6416,11 @@
           <t>deepak@dixitindia.com</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -6394,7 +6438,11 @@
           <t>deepali@proximity.tech</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -6412,7 +6460,11 @@
           <t>deepali.verdi@genzeon.com</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -6430,7 +6482,11 @@
           <t>deepashree.v@skience.com</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -6448,7 +6504,11 @@
           <t>deepika@appinessworld.com</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -6466,7 +6526,11 @@
           <t>deepika@webkul.com</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -6484,7 +6548,11 @@
           <t>deepthi.kesireddy@smartims.com</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -6502,7 +6570,11 @@
           <t>deepthi.v@etggs.com</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -6520,7 +6592,11 @@
           <t>deepti@mindcraft.in</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -6538,7 +6614,11 @@
           <t>deepti.bathija@orcapodservices.com</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -6556,7 +6636,11 @@
           <t>dlewis@conviva.com</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -6574,7 +6658,11 @@
           <t>deepti.m@trell.in</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -6592,7 +6680,11 @@
           <t>deepti.n@accelq.com</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -6610,7 +6702,11 @@
           <t>deepti.sahni@mobiloitte.com</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -6724,7 +6724,11 @@
           <t>dgtewari@quark.com</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -6742,7 +6746,11 @@
           <t>deeptiw@pre-scient.com</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -6760,7 +6768,11 @@
           <t>deo.kumar@akalinfosys.com</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -6778,7 +6790,11 @@
           <t>devang@strategicerp.com</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -6796,7 +6812,11 @@
           <t>devansh.narang@loco.gg</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -6814,7 +6834,11 @@
           <t>devanshi@brainerhub.com</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -6832,7 +6856,11 @@
           <t>devershi.desai@ssminfotech.com</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -6850,7 +6878,11 @@
           <t>dreddy@dvginteractive.com</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -6868,7 +6900,11 @@
           <t>devika@shopx.in</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -6922,7 +6922,11 @@
           <t>dharmendra.rawat@lumiq.ai</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -6940,7 +6944,11 @@
           <t>dharmendra@akshay.com</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -6958,7 +6966,11 @@
           <t>dharmik@atlan.com</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -6976,7 +6988,11 @@
           <t>dshankar@dataintensity.com</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -6994,7 +7010,11 @@
           <t>dkamboj@newtglobalcorp.com</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -7012,7 +7032,11 @@
           <t>dhirendra.panda@ivalue.co.in</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -7030,7 +7054,11 @@
           <t>dhritiparnad@zendrive.com</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -7048,7 +7076,11 @@
           <t>diksha@apptware.com</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -7066,7 +7098,11 @@
           <t>diksha.sisodia@eternussolutions.com</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -7084,7 +7120,11 @@
           <t>dileep.choyappally@nestgroup.net</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -7102,7 +7142,11 @@
           <t>borah.dilip@senrysa.com</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -7120,7 +7164,11 @@
           <t>dilip.s@theimperative.in</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -7138,7 +7186,11 @@
           <t>dimpal.patel@tacttree.com</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -7156,7 +7208,11 @@
           <t>dgokhale@crgroup.co.in</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -7174,7 +7230,11 @@
           <t>dinesh.hemdev@logixal.com</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -7252,7 +7252,11 @@
           <t>dinesh.rai@hirexa.com</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -7270,7 +7274,11 @@
           <t>dinesh.yuvaraj@ivymobility.com</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -7288,7 +7296,11 @@
           <t>dipalichavan@credenceanalytics.com</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -7306,7 +7318,11 @@
           <t>dipesh@pesto.tech</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -7324,7 +7340,11 @@
           <t>dipikasharma@slx.co.in</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -7342,7 +7362,11 @@
           <t>dipthir@dckap.com</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -7360,7 +7384,11 @@
           <t>dipti@insider.in</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -7378,7 +7406,11 @@
           <t>dipti.kothari@satincorp.com</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -7396,7 +7428,11 @@
           <t>disha.bali@remitonline.info</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -7450,7 +7450,11 @@
           <t>dishank.raj@aeriestechnology.com</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -7468,7 +7472,11 @@
           <t>da@virsec.com</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -7486,7 +7494,11 @@
           <t>divya.beneesh@zaggle.in</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -7504,7 +7516,11 @@
           <t>divya.b@greyorange.com</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -7522,7 +7538,11 @@
           <t>divya.chandrasekhara@infoworks.io</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -7540,7 +7560,11 @@
           <t>divya.dang@cloudanalogy.com</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -7558,7 +7582,11 @@
           <t>ddevapathni@gemini-us.com</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -7576,7 +7604,11 @@
           <t>divya@thescalers.com</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -7594,7 +7626,11 @@
           <t>divyajaggi@promactinfo.com</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -7612,7 +7648,11 @@
           <t>divya.jethi@cloudanalogy.com</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -7630,7 +7670,11 @@
           <t>divya.k@diamondpick.com</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -7648,7 +7692,11 @@
           <t>divya@taashee.com</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -7666,7 +7714,11 @@
           <t>divya@diamondpick.com</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -7684,7 +7736,11 @@
           <t>divyap@cegonsoft.com</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -7702,7 +7758,11 @@
           <t>divya.p@ceipal.com</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -7780,7 +7780,11 @@
           <t>divya.prasad@impelsys.com</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -7798,7 +7802,11 @@
           <t>divya.puthireddi@tanla.com</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -7816,7 +7824,11 @@
           <t>donna.ellies@br.iq</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -7834,7 +7846,11 @@
           <t>drishti@artoonsolutions.com</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -7852,7 +7868,11 @@
           <t>durga.akula@cotelligent.com</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -7870,7 +7890,11 @@
           <t>durgaprasada@proarch.com</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -7888,7 +7912,11 @@
           <t>edwin.vimal@sysvine.com</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -7906,7 +7934,11 @@
           <t>ekta.chowdhry@shipsy.io</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -7924,7 +7956,11 @@
           <t>ekta.kohli@simulationiq.com</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -7978,7 +7978,11 @@
           <t>elizabeth.j@appnomic.com</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -7996,7 +8000,11 @@
           <t>emilio@etouch.net</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -8014,7 +8022,11 @@
           <t>eram.qudsia@mygate.in</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -8032,7 +8044,11 @@
           <t>esha.mayekar@autoplant.in</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -8050,7 +8066,11 @@
           <t>eswari.v@tringapps.com</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -8068,7 +8088,11 @@
           <t>ety@buzzclan.com</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -8086,7 +8110,11 @@
           <t>eustine.thomas@ars-traffic.com</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -8104,7 +8132,11 @@
           <t>eyunni.kumar@bdxworld.com</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -8122,7 +8154,11 @@
           <t>fabiana.sobers@cashapona.com</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -8140,7 +8176,11 @@
           <t>vineet.shah@facileserv.com</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -8158,7 +8198,11 @@
           <t>faisal.siddiqui@uneecops.com</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -8176,7 +8220,11 @@
           <t>faiza.khan@apolisrises.com</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -8194,7 +8242,11 @@
           <t>fbegum@hitachi-solutions.com</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -8212,7 +8264,11 @@
           <t>farheen@rapidflowapps.com</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -8230,7 +8286,11 @@
           <t>fazal.karim@metaoption.com</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -8308,7 +8308,11 @@
           <t>firdaus.mehta@heliossolutions.co</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -8326,7 +8330,11 @@
           <t>francis.gonsalves@moengage.com</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -8344,7 +8352,11 @@
           <t>franklin@thescalers.com</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -8362,7 +8374,11 @@
           <t>frida.dias@mpsinteractive.com</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -8380,7 +8396,11 @@
           <t>friend.friend@niit-tech.com</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -8398,7 +8418,11 @@
           <t>ganapathy.d@mresult.com</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -8416,7 +8440,11 @@
           <t>gsomisetti@email.xtglobal.com</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -8434,7 +8462,11 @@
           <t>gargi.rajan@unicommerce.com</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -8452,7 +8484,11 @@
           <t>garima.pandey@epsoftinc.com</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -8506,7 +8506,11 @@
           <t>garima.pandey@rategain.com</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -8524,7 +8528,11 @@
           <t>garima.rathi@condecosoftware.com</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -8542,7 +8550,11 @@
           <t>garima.sangwan@accops.com</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -8560,7 +8572,11 @@
           <t>gsharma@nasscom.in</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -8578,7 +8594,11 @@
           <t>gyjoshi@workforcelogiq.com</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -8596,7 +8616,11 @@
           <t>gauravgaur@ironsystems.com</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -8614,7 +8638,11 @@
           <t>gaurav.s@amigainformatics.com</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -8632,7 +8660,11 @@
           <t>gaurav.upadhyay@v2solutions.com</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -8650,7 +8682,11 @@
           <t>gautam@firstconnectsolutions.com</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -8668,7 +8704,11 @@
           <t>gautamn@tblocks.com</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -8686,7 +8726,11 @@
           <t>gautam.pathak@opshub.com</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -8704,7 +8748,11 @@
           <t>gautam.prasad@ondemandagility.com</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -8722,7 +8770,11 @@
           <t>gautam.tungare@6degreesit.com</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -8740,7 +8792,11 @@
           <t>gautham.p@accubits.com</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -8758,7 +8814,11 @@
           <t>gayathri.arunkumar@tvsnext.io</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -8776,7 +8836,11 @@
           <t>gayathri.nagaraj@responsivemts.com</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -8794,7 +8858,11 @@
           <t>gayatri@aumnitechworks.com</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -8812,7 +8880,11 @@
           <t>gayatri.nikkula@inry.com</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -8830,7 +8902,11 @@
           <t>gayatrip@gathi.com</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -8848,7 +8924,11 @@
           <t>g.patil@kokonetworks.com</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -8866,7 +8946,11 @@
           <t>gayatri@dyooti.com</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -8884,7 +8968,11 @@
           <t>gazal@imarkinfotech.com</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -8902,7 +8990,11 @@
           <t>geetanjali.toopran@solix.com</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -8920,7 +9012,11 @@
           <t>giri.babu@neovatic.com</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -9034,7 +9034,11 @@
           <t>giridhar.d@e5.ai</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -9052,7 +9056,11 @@
           <t>gvemuganti@tataunistore.com</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -9070,7 +9078,11 @@
           <t>girish.subramanian@symphonyretailai.com</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -9088,7 +9100,11 @@
           <t>girish.k@infomazeapps.com</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -9106,7 +9122,11 @@
           <t>gita.madhuri@covalenseglobal.com</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -9124,7 +9144,11 @@
           <t>gitanjali.venkatesh@excelenciaconsulting. com</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -9142,7 +9166,11 @@
           <t>gitanjali.verma@w3villa.com</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -9160,7 +9188,11 @@
           <t>gopalakrishna.gubbi@jsw.in</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -9178,7 +9210,11 @@
           <t>gouthamb@systelinc.com</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -9232,7 +9232,11 @@
           <t>govind.bhandari@daloopa.com</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -9250,7 +9254,11 @@
           <t>govind@eoxvantage.com</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -9268,7 +9276,11 @@
           <t>govinda.shastry@igiusa.com</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -9286,7 +9298,11 @@
           <t>gracy@perfios.com</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -9304,7 +9320,11 @@
           <t>gripson.martes@detecttechnologies.com</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -9322,7 +9342,11 @@
           <t>gugapriya@ideassion.com</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -9340,7 +9364,11 @@
           <t>gulshan@near.com</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -9358,7 +9386,11 @@
           <t>gunjan@rnftechnologies.com</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -9376,7 +9408,11 @@
           <t>gurpreet.jaggi@betsol.com</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -9394,7 +9430,11 @@
           <t>gurpreet.singh@wingify.com</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -9412,7 +9452,11 @@
           <t>guru@one.com</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -9430,7 +9474,11 @@
           <t>gyan@centroxy.com</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -9448,7 +9496,11 @@
           <t>hanish.tiwari@ant.works</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -9466,7 +9518,11 @@
           <t>hank.mishra@anchanto.com</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -9484,7 +9540,11 @@
           <t>happy@capermint.com</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -9562,7 +9562,11 @@
           <t>hari.krishnan@avasotech.com</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -9580,7 +9584,11 @@
           <t>harikishore.p@excelra.com</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -9598,7 +9606,11 @@
           <t>hari.p@westagilelabs.com</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -9616,7 +9628,11 @@
           <t>harikrishna.bachala@mitsind.com</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -9634,7 +9650,11 @@
           <t>hariprasadadthale@askbrake.com</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -9652,7 +9672,11 @@
           <t>haris.a@truglobal.com</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -9670,7 +9694,11 @@
           <t>hari@zumen.com</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -9688,7 +9716,11 @@
           <t>harishankher@codingmart.com</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -9706,7 +9738,11 @@
           <t>harista.jakhar@impelsys.com</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -9724,7 +9760,11 @@
           <t>harith.chambravalli@observe.ai</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -9742,7 +9782,11 @@
           <t>haritha.etakula@jnettechnologies.com</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -9760,7 +9804,11 @@
           <t>harpreet.bali@nvish.com</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -9778,7 +9826,11 @@
           <t>harshk@elementsgs.com</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -9796,7 +9848,11 @@
           <t>harshada.moharil@freshgravity.com</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -9814,7 +9870,11 @@
           <t>harshida@cctech.co.in</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -9832,7 +9892,11 @@
           <t>husahu@ciphercloud.com</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -9850,7 +9914,11 @@
           <t>harshita.rathore@moonfroglabs.com</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -9868,7 +9936,11 @@
           <t>imran.h@apar.com</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -9886,7 +9958,11 @@
           <t>heena@clevertap.com</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -9904,7 +9980,11 @@
           <t>hemant.batra@supraits.com</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -9922,7 +10002,11 @@
           <t>hemant.pawar@ndsglobal.com</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -9940,7 +10024,11 @@
           <t>hemendra.bist@u2opiamobile.com</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -9958,7 +10046,11 @@
           <t>hemlata.goel@shl.com</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -9976,7 +10068,11 @@
           <t>hemraj@cloudthat.in</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -10090,7 +10090,11 @@
           <t>hsoni@infosenseglobal.com</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -10108,7 +10112,11 @@
           <t>hima@systango.com</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -10126,7 +10134,11 @@
           <t>himagauri@metamorphtech.com</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -10144,7 +10156,11 @@
           <t>himanshub@appcino.com</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -10162,7 +10178,11 @@
           <t>hmishra@valethi.com</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -10180,7 +10200,11 @@
           <t>himanshu@ditserv.com</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -10198,7 +10222,11 @@
           <t>hina.khan@acuteinformatics.in</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -10216,7 +10244,11 @@
           <t>hsingh@hitachi-solutions.com</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -10234,7 +10266,11 @@
           <t>hitesh.nair@aqmtechnologies.com</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -10288,7 +10288,11 @@
           <t>honeydeep@pando.ai</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -10306,7 +10310,11 @@
           <t>hrd@mawaimail.com</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -10324,7 +10332,11 @@
           <t>hrishikesh@sterlingsoftware.co.in</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -10342,7 +10354,11 @@
           <t>huma@dctinc.com</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -10360,7 +10376,11 @@
           <t>humera.iffath@truecaller.com</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -10378,7 +10398,11 @@
           <t>huzefa.retiwala@metro-services.in</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -10396,7 +10420,11 @@
           <t>ilham.mulla@blazeclan.com</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -10414,7 +10442,11 @@
           <t>img@imgglobalinfotech.com</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -10432,7 +10464,11 @@
           <t>imrannd@skoruz.com</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -10450,7 +10486,11 @@
           <t>inderjeet.gujral@apolisrises.com</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -10468,7 +10508,11 @@
           <t>tindrakumar@ntrustinfotech.com</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -10486,7 +10530,11 @@
           <t>inventum.recruiter@inventum.net</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -10504,7 +10552,11 @@
           <t>irudia.anthony@h1insights.com</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -10522,7 +10574,11 @@
           <t>ishani.sharma@idctechnologies.com</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -10540,7 +10596,11 @@
           <t>isle@opendestinations.com</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -10618,7 +10618,11 @@
           <t>jabeen@hulkapps.com</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -10636,7 +10640,11 @@
           <t>jacob.j@wrenchsolutions.com</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -10654,7 +10662,11 @@
           <t>jagadabhi.krishna@leoforce.com</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -10672,7 +10684,11 @@
           <t>jagadish.v@realworld-one.com</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -10690,7 +10706,11 @@
           <t>jaipal.addagatla@mutualmobile.com</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -10708,7 +10728,11 @@
           <t>jairaj.jagtap@satincorp.com</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -10726,7 +10750,11 @@
           <t>jaisy@freshersworld.com</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -10744,7 +10772,11 @@
           <t>janaki.naik@tatadigital.com</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -10762,7 +10794,11 @@
           <t>janani.prakaash@quantela.com</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -10780,7 +10816,11 @@
           <t>jpaul@securonix.com</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -10798,7 +10838,11 @@
           <t>jasinta@experience.com</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -10816,7 +10860,11 @@
           <t>jaslieen.baghh@blancco.com</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -10834,7 +10882,11 @@
           <t>jasmine.f@ptechnosoft.com</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -10852,7 +10904,11 @@
           <t>jasmine.vaswani@worldfashionexchange. com</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -10870,7 +10926,11 @@
           <t>jaspreetsingh@dataglove-us.com</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -10888,7 +10948,11 @@
           <t>jaya.laxmi@vincit.fi</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -10906,7 +10970,11 @@
           <t>jaya.pandey@brainvire.com</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -10924,7 +10992,11 @@
           <t>jay@customerxps.com</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -10942,7 +11014,11 @@
           <t>njayakumar@a-bits.com</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -10960,7 +11036,11 @@
           <t>jayaprakash@mirafra.com</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -10978,7 +11058,11 @@
           <t>jayashree.jayanth@ushur.com</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -10996,7 +11080,11 @@
           <t>jayashri@amrutsoftware.com</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -11014,7 +11102,11 @@
           <t>jayati.p@keka.com</t>
         </is>
       </c>
-      <c r="D486" t="inlineStr"/>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -11032,7 +11124,11 @@
           <t>jasolanki@workforcelogiq.com</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -11146,7 +11146,11 @@
           <t>jegannathan@isolve.global</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -11164,7 +11168,11 @@
           <t>jeswin.thomas@questionpro.com</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -11182,7 +11190,11 @@
           <t>jimeet@metamorphtech.com</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -11200,7 +11212,11 @@
           <t>jinu@m2comsys.com</t>
         </is>
       </c>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -11218,7 +11234,11 @@
           <t>jitendra.das@workinsync.io</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -11236,7 +11256,11 @@
           <t>jitendra.wankhede@anuntatech.com</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -11254,7 +11278,11 @@
           <t>jitesh@softnice.com</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr"/>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -11272,7 +11300,11 @@
           <t>jithesh.v@zucisystems.com</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -11290,7 +11322,11 @@
           <t>jpixentia@pixentia.com</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -11344,7 +11344,11 @@
           <t>joem@itamerica.com</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -11362,7 +11366,11 @@
           <t>joel.lobo@rtcamp.com</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -11380,7 +11388,11 @@
           <t>johnsonk@netrovert.net</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -11398,7 +11410,11 @@
           <t>joseph@vdartinc.com</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -11416,7 +11432,11 @@
           <t>joshua.henry@cloudsek.com</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -11434,7 +11454,11 @@
           <t>joshua.t@sailotech.com</t>
         </is>
       </c>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -11452,7 +11476,11 @@
           <t>jothi.prakash@bwdesigngroup.com</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -11470,7 +11498,11 @@
           <t>joy.dupati@sierraatlantic.com</t>
         </is>
       </c>
-      <c r="D504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -11488,7 +11520,11 @@
           <t>juhi.sharma@lockstep.io</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -11506,7 +11542,11 @@
           <t>justin@near.com</t>
         </is>
       </c>
-      <c r="D506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -11524,7 +11564,11 @@
           <t>jyothendraar@aditiconsulting.com</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -11542,7 +11586,11 @@
           <t>jyothsna.devi@kasmo.co</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -11560,7 +11608,11 @@
           <t>jyoti.g@commerceiq.ai</t>
         </is>
       </c>
-      <c r="D509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -11578,7 +11630,11 @@
           <t>jgupta@otsi-usa.com</t>
         </is>
       </c>
-      <c r="D510" t="inlineStr"/>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -11596,7 +11652,11 @@
           <t>jyoti.kajale@ampcus.com</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -11674,7 +11674,11 @@
           <t>jyoti.saini@apolisrises.com</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -11692,7 +11696,11 @@
           <t>jyoti.singh@zapcg.com</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -11710,7 +11718,11 @@
           <t>jyotsna.mahajan@sugarboxnetworks.com</t>
         </is>
       </c>
-      <c r="D514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -11728,7 +11740,11 @@
           <t>hr@dhaninfo.biz</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -11746,7 +11762,11 @@
           <t>kajal.tuteja@csquare.in</t>
         </is>
       </c>
-      <c r="D516" t="inlineStr"/>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -11764,7 +11784,11 @@
           <t>kalpana@theimperative.in</t>
         </is>
       </c>
-      <c r="D517" t="inlineStr"/>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -11782,7 +11806,11 @@
           <t>kalyan.neelagiri@soroco.com</t>
         </is>
       </c>
-      <c r="D518" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -11800,7 +11828,11 @@
           <t>kalyani.mahajan@paramatrix.com</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -11818,7 +11850,11 @@
           <t>kalyani.mudigonda@votarytech.com</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -11872,7 +11872,11 @@
           <t>kalyani.pendharkar@theblueflamelabs.com</t>
         </is>
       </c>
-      <c r="D521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -11890,7 +11894,11 @@
           <t>ksingh@skillgigs.com</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr"/>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -11908,7 +11916,11 @@
           <t>kamla.mulla@se2.com</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr"/>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -11926,7 +11938,11 @@
           <t>kanchan.jagtap@tatatechnologies.com</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr"/>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -11944,7 +11960,11 @@
           <t>kanchan.verma@qsstechnosoft.com</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -11962,7 +11982,11 @@
           <t>kanhaiya@cloudthing.com</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr"/>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -11980,7 +12004,11 @@
           <t>kanika@eglogics.com</t>
         </is>
       </c>
-      <c r="D527" t="inlineStr"/>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -11998,7 +12026,11 @@
           <t>kannan.krishnan@trinamix.com</t>
         </is>
       </c>
-      <c r="D528" t="inlineStr"/>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -12016,7 +12048,11 @@
           <t>kannu.taneja@areteanstech.com</t>
         </is>
       </c>
-      <c r="D529" t="inlineStr"/>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -12034,7 +12070,11 @@
           <t>kantan@labvantage.com</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr"/>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -12052,7 +12092,11 @@
           <t>kapeesh.saxena@genzeon.com</t>
         </is>
       </c>
-      <c r="D531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -12070,7 +12114,11 @@
           <t>kapil.katira@thegatewaycorp.com</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -12088,7 +12136,11 @@
           <t>karthick@ideas2it.com</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -12106,7 +12158,11 @@
           <t>karthik.chintapatla@visteon.com</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -12124,7 +12180,11 @@
           <t>karthik.i@springworks.in</t>
         </is>
       </c>
-      <c r="D535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -12202,7 +12202,11 @@
           <t>karthikr@operative.com</t>
         </is>
       </c>
-      <c r="D536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -12220,7 +12224,11 @@
           <t>karthikeyan@hiverhq.com</t>
         </is>
       </c>
-      <c r="D537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -12238,7 +12246,11 @@
           <t>karthikeyan.samuel@xansa.com</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -12256,7 +12268,11 @@
           <t>karthikeyan.sivasubramanian@saviynt.com</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -12274,7 +12290,11 @@
           <t>kartik.v@vtechsolution.com</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -12292,7 +12312,11 @@
           <t>kartik.sehgal@omnepresent.com</t>
         </is>
       </c>
-      <c r="D541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -12310,7 +12334,11 @@
           <t>karuna.geddam@arcserve.com</t>
         </is>
       </c>
-      <c r="D542" t="inlineStr"/>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -12328,7 +12356,11 @@
           <t>kausar.khatri@lauren.co.in</t>
         </is>
       </c>
-      <c r="D543" t="inlineStr"/>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -12346,7 +12378,11 @@
           <t>kavita.gupta@anm.com</t>
         </is>
       </c>
-      <c r="D544" t="inlineStr"/>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -12400,7 +12400,11 @@
           <t>kavitha.nandagopal@impelsys.com</t>
         </is>
       </c>
-      <c r="D545" t="inlineStr"/>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -12418,7 +12422,11 @@
           <t>kavita.tandon@simplifyhealthcare.com</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -12436,7 +12444,11 @@
           <t>kavita.y@valiancesolutions.com</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -12454,7 +12466,11 @@
           <t>kavita.yadav@valiancesolutions.com</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -12472,7 +12488,11 @@
           <t>kavitha@6thenergy.com</t>
         </is>
       </c>
-      <c r="D549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -12490,7 +12510,11 @@
           <t>mkavitha@sourcetrace.com</t>
         </is>
       </c>
-      <c r="D550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -12508,7 +12532,11 @@
           <t>kavitha.umasankar@wolterskluwer.com</t>
         </is>
       </c>
-      <c r="D551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -12526,7 +12554,11 @@
           <t>kavya.k@mygoconsulting.com</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -12544,7 +12576,11 @@
           <t>keerthi.kamasamudra@stellapps.com</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -12562,7 +12598,11 @@
           <t>keerthi.v@rlabsglobal.com</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -12580,7 +12620,11 @@
           <t>ketan.shetty@writerinformation.com</t>
         </is>
       </c>
-      <c r="D555" t="inlineStr"/>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -12598,7 +12642,11 @@
           <t>kevin@xeno.in</t>
         </is>
       </c>
-      <c r="D556" t="inlineStr"/>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -12616,7 +12664,11 @@
           <t>kparker@integrass.com</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -12634,7 +12686,11 @@
           <t>khandoba.k@techtreeit.com</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -12652,7 +12708,11 @@
           <t>khushboo@techspian.com</t>
         </is>
       </c>
-      <c r="D559" t="inlineStr"/>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -12730,7 +12730,11 @@
           <t>khushboo@techaheadcorp.com</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr"/>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -12748,7 +12752,11 @@
           <t>khushi@5ire.org</t>
         </is>
       </c>
-      <c r="D561" t="inlineStr"/>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -12766,7 +12774,11 @@
           <t>khyatisagar@appitsimple.com</t>
         </is>
       </c>
-      <c r="D562" t="inlineStr"/>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -12784,7 +12796,11 @@
           <t>kinjal@biztechconsultancy.com</t>
         </is>
       </c>
-      <c r="D563" t="inlineStr"/>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -12802,7 +12818,11 @@
           <t>kiran.bala@blueconchtech.com</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr"/>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -12820,7 +12840,11 @@
           <t>kkumar@adea.com</t>
         </is>
       </c>
-      <c r="D565" t="inlineStr"/>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -12838,7 +12862,11 @@
           <t>kiran.lal@tomiaglobal.com</t>
         </is>
       </c>
-      <c r="D566" t="inlineStr"/>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -12856,7 +12884,11 @@
           <t>kiran@manektech.com</t>
         </is>
       </c>
-      <c r="D567" t="inlineStr"/>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -12874,7 +12906,11 @@
           <t>kirans@mindfiresolutions.com</t>
         </is>
       </c>
-      <c r="D568" t="inlineStr"/>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -12892,7 +12928,11 @@
           <t>kiran.s@zerone-consulting.com</t>
         </is>
       </c>
-      <c r="D569" t="inlineStr"/>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -12910,7 +12950,11 @@
           <t>kirti.manucha@healthfore.com</t>
         </is>
       </c>
-      <c r="D570" t="inlineStr"/>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -12928,7 +12972,11 @@
           <t>kirti.manucha@religare.com</t>
         </is>
       </c>
-      <c r="D571" t="inlineStr"/>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -12946,7 +12994,11 @@
           <t>kishor.p@feuji.com</t>
         </is>
       </c>
-      <c r="D572" t="inlineStr"/>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -12964,7 +13016,11 @@
           <t>komal@balajidatasolutions.net</t>
         </is>
       </c>
-      <c r="D573" t="inlineStr"/>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -12982,7 +13038,11 @@
           <t>komala.t@acropetal.com</t>
         </is>
       </c>
-      <c r="D574" t="inlineStr"/>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -13000,7 +13060,11 @@
           <t>korak.saha@mjunction.in</t>
         </is>
       </c>
-      <c r="D575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -13018,7 +13082,11 @@
           <t>koundinya.adiraju@testingxperts.com</t>
         </is>
       </c>
-      <c r="D576" t="inlineStr"/>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -13036,7 +13104,11 @@
           <t>koustav@nasscom.in</t>
         </is>
       </c>
-      <c r="D577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -13054,7 +13126,11 @@
           <t>kkumar@polarismanagement.com</t>
         </is>
       </c>
-      <c r="D578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -13072,7 +13148,11 @@
           <t>krishan_kumar@taaltech.com</t>
         </is>
       </c>
-      <c r="D579" t="inlineStr"/>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -13090,7 +13170,11 @@
           <t>krishna_kumar@actis.co.in</t>
         </is>
       </c>
-      <c r="D580" t="inlineStr"/>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -13108,7 +13192,11 @@
           <t>knair@ixiacom.com</t>
         </is>
       </c>
-      <c r="D581" t="inlineStr"/>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -13126,7 +13214,11 @@
           <t>kramachandran@hitachi-solutions.com</t>
         </is>
       </c>
-      <c r="D582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -13144,7 +13236,11 @@
           <t>krishnanvr@savvy-it.com</t>
         </is>
       </c>
-      <c r="D583" t="inlineStr"/>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -13258,7 +13258,11 @@
           <t>krishnanand.joshi@teknorix.com</t>
         </is>
       </c>
-      <c r="D584" t="inlineStr"/>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -13276,7 +13280,11 @@
           <t>kriti@consummatetechnologies.com</t>
         </is>
       </c>
-      <c r="D585" t="inlineStr"/>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -13294,7 +13302,11 @@
           <t>kritika.khanduri@loginradius.com</t>
         </is>
       </c>
-      <c r="D586" t="inlineStr"/>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -13312,7 +13324,11 @@
           <t>kshama.patel@intech-systems.com</t>
         </is>
       </c>
-      <c r="D587" t="inlineStr"/>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -13330,7 +13346,11 @@
           <t>kuldeep.chobey@satincorp.com</t>
         </is>
       </c>
-      <c r="D588" t="inlineStr"/>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -13348,7 +13368,11 @@
           <t>kuldeepg@porteck.com</t>
         </is>
       </c>
-      <c r="D589" t="inlineStr"/>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -13366,7 +13390,11 @@
           <t>kulvir.kaur@cloudeq.com</t>
         </is>
       </c>
-      <c r="D590" t="inlineStr"/>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -13384,7 +13412,11 @@
           <t>kumara@aditiconsulting.com</t>
         </is>
       </c>
-      <c r="D591" t="inlineStr"/>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -13402,7 +13434,11 @@
           <t>kumuda.panda@evonsys.com</t>
         </is>
       </c>
-      <c r="D592" t="inlineStr"/>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -13456,7 +13456,11 @@
           <t>kunal@elsner.com</t>
         </is>
       </c>
-      <c r="D593" t="inlineStr"/>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -13474,7 +13478,11 @@
           <t>kunal.acharya@impelsys.com</t>
         </is>
       </c>
-      <c r="D594" t="inlineStr"/>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -13492,7 +13500,11 @@
           <t>kunal.wadhwani@pocketfm.com</t>
         </is>
       </c>
-      <c r="D595" t="inlineStr"/>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -13510,7 +13522,11 @@
           <t>kushagra.pande@jungleegames.com</t>
         </is>
       </c>
-      <c r="D596" t="inlineStr"/>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -13528,7 +13544,11 @@
           <t>lakshmi.eyyunni@narvar.com</t>
         </is>
       </c>
-      <c r="D597" t="inlineStr"/>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -13546,7 +13566,11 @@
           <t>lakshmipriya.radhakrishnan@bwdesigngroup. com</t>
         </is>
       </c>
-      <c r="D598" t="inlineStr"/>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -13564,7 +13588,11 @@
           <t>lakshmi@triconinfotech.com</t>
         </is>
       </c>
-      <c r="D599" t="inlineStr"/>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -13582,7 +13610,11 @@
           <t>lakshmi.p@qis.co.in</t>
         </is>
       </c>
-      <c r="D600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -13600,7 +13632,11 @@
           <t>lata.c@netconnectglobal.com</t>
         </is>
       </c>
-      <c r="D601" t="inlineStr"/>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -13618,7 +13654,11 @@
           <t>lata.kohli@cogentinfo.com</t>
         </is>
       </c>
-      <c r="D602" t="inlineStr"/>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -13636,7 +13676,11 @@
           <t>ltirounavoucarassou@yodlee.com</t>
         </is>
       </c>
-      <c r="D603" t="inlineStr"/>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -13654,7 +13698,11 @@
           <t>lshankar@liventus.com</t>
         </is>
       </c>
-      <c r="D604" t="inlineStr"/>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -13672,7 +13720,11 @@
           <t>lavita.n@endurance.com</t>
         </is>
       </c>
-      <c r="D605" t="inlineStr"/>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -13690,7 +13742,11 @@
           <t>laxman.reddy@lorhanit.com</t>
         </is>
       </c>
-      <c r="D606" t="inlineStr"/>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -13708,7 +13764,11 @@
           <t>leela.madhuri@cashapona.com</t>
         </is>
       </c>
-      <c r="D607" t="inlineStr"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -13786,7 +13786,11 @@
           <t>leena@getcerta.com</t>
         </is>
       </c>
-      <c r="D608" t="inlineStr"/>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -13804,7 +13808,11 @@
           <t>leena.xavier@solitontech.com</t>
         </is>
       </c>
-      <c r="D609" t="inlineStr"/>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -13822,7 +13830,11 @@
           <t>lvarughese@suyati.com</t>
         </is>
       </c>
-      <c r="D610" t="inlineStr"/>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -13840,7 +13852,11 @@
           <t>lipika.mohanty@crmnext.com</t>
         </is>
       </c>
-      <c r="D611" t="inlineStr"/>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -13858,7 +13874,11 @@
           <t>lisacrage@insolutionsglobal.com</t>
         </is>
       </c>
-      <c r="D612" t="inlineStr"/>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -13876,7 +13896,11 @@
           <t>litons@innov.in</t>
         </is>
       </c>
-      <c r="D613" t="inlineStr"/>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -13894,7 +13918,11 @@
           <t>lituja.mishra@apmosys.in</t>
         </is>
       </c>
-      <c r="D614" t="inlineStr"/>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -13912,7 +13940,11 @@
           <t>livin.varghese@teqfocus.com</t>
         </is>
       </c>
-      <c r="D615" t="inlineStr"/>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -13930,7 +13962,11 @@
           <t>logesh@clumio.com</t>
         </is>
       </c>
-      <c r="D616" t="inlineStr"/>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -13948,7 +13984,11 @@
           <t>lokesh@nexgeniots.com</t>
         </is>
       </c>
-      <c r="D617" t="inlineStr"/>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -13966,7 +14006,11 @@
           <t>luisa.mohanty@rategain.com</t>
         </is>
       </c>
-      <c r="D618" t="inlineStr"/>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -13984,7 +14028,11 @@
           <t>lydia.dsouza@progility.com.au</t>
         </is>
       </c>
-      <c r="D619" t="inlineStr"/>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -14002,7 +14050,11 @@
           <t>lydia.dsouza@progilitytech.com</t>
         </is>
       </c>
-      <c r="D620" t="inlineStr"/>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -14020,7 +14072,11 @@
           <t>lyndon.saldanha@manthan.com</t>
         </is>
       </c>
-      <c r="D621" t="inlineStr"/>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -14038,7 +14094,11 @@
           <t>maanoj@betterplace.co.in</t>
         </is>
       </c>
-      <c r="D622" t="inlineStr"/>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -14116,7 +14116,11 @@
           <t>maclean.raphael@wepindia.com</t>
         </is>
       </c>
-      <c r="D623" t="inlineStr"/>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -14134,7 +14138,11 @@
           <t>madhan.kumar@aditiconsulting.com</t>
         </is>
       </c>
-      <c r="D624" t="inlineStr"/>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -14152,7 +14160,11 @@
           <t>madhava.mallela@microexcel.com</t>
         </is>
       </c>
-      <c r="D625" t="inlineStr"/>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -14170,7 +14182,11 @@
           <t>madhavee.singh@blucognition.com</t>
         </is>
       </c>
-      <c r="D626" t="inlineStr"/>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -14188,7 +14204,11 @@
           <t>madhavig@operative.com</t>
         </is>
       </c>
-      <c r="D627" t="inlineStr"/>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -14206,7 +14226,11 @@
           <t>madhu.kapu@allyis.com</t>
         </is>
       </c>
-      <c r="D628" t="inlineStr"/>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -14224,7 +14248,11 @@
           <t>madhu.n@qualizeal.com</t>
         </is>
       </c>
-      <c r="D629" t="inlineStr"/>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -14242,7 +14270,11 @@
           <t>madhura.lanjekar@clariontechnologies.co.in</t>
         </is>
       </c>
-      <c r="D630" t="inlineStr"/>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -14260,7 +14292,11 @@
           <t>mmhamankar@yotta.com</t>
         </is>
       </c>
-      <c r="D631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -14314,7 +14314,11 @@
           <t>madhuri@gupshup.io</t>
         </is>
       </c>
-      <c r="D632" t="inlineStr"/>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -14332,7 +14336,11 @@
           <t>mpalaji@randomtrees.com</t>
         </is>
       </c>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -14350,7 +14358,11 @@
           <t>madhuri.rajath@goodera.com</t>
         </is>
       </c>
-      <c r="D634" t="inlineStr"/>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -14368,7 +14380,11 @@
           <t>madhuk@lentra.ai</t>
         </is>
       </c>
-      <c r="D635" t="inlineStr"/>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -14386,7 +14402,11 @@
           <t>madhusudhanan@imarque.co.in</t>
         </is>
       </c>
-      <c r="D636" t="inlineStr"/>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -14404,7 +14424,11 @@
           <t>madhvi.arora@yodlee.com</t>
         </is>
       </c>
-      <c r="D637" t="inlineStr"/>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -14422,7 +14446,11 @@
           <t>mahalakshmi@unilogcorp.com</t>
         </is>
       </c>
-      <c r="D638" t="inlineStr"/>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -14440,7 +14468,11 @@
           <t>mahasweta.paul@atyati.com</t>
         </is>
       </c>
-      <c r="D639" t="inlineStr"/>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -14458,7 +14490,11 @@
           <t>mahendra.singh@excelra.com</t>
         </is>
       </c>
-      <c r="D640" t="inlineStr"/>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -14476,7 +14512,11 @@
           <t>mahendra@vysystems.com</t>
         </is>
       </c>
-      <c r="D641" t="inlineStr"/>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -14494,7 +14534,11 @@
           <t>mahendran.s@kovaion.com</t>
         </is>
       </c>
-      <c r="D642" t="inlineStr"/>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -14512,7 +14556,11 @@
           <t>mahesh.bandaru@neewee.ai</t>
         </is>
       </c>
-      <c r="D643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -14530,7 +14578,11 @@
           <t>mahesh.h@zelitesolutions.com</t>
         </is>
       </c>
-      <c r="D644" t="inlineStr"/>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -14548,7 +14600,11 @@
           <t>mainka.s@geeklurn.com</t>
         </is>
       </c>
-      <c r="D645" t="inlineStr"/>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -14566,7 +14622,11 @@
           <t>malathip@boston-technology.com</t>
         </is>
       </c>
-      <c r="D646" t="inlineStr"/>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -14644,7 +14644,11 @@
           <t>malini.venugopal@people10.com</t>
         </is>
       </c>
-      <c r="D647" t="inlineStr"/>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -14662,7 +14666,11 @@
           <t>mallika.poojari@featsystems.com</t>
         </is>
       </c>
-      <c r="D648" t="inlineStr"/>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -14680,7 +14688,11 @@
           <t>mamatha.n@modefin.com</t>
         </is>
       </c>
-      <c r="D649" t="inlineStr"/>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -14698,7 +14710,11 @@
           <t>mamta@cognustechnology.com</t>
         </is>
       </c>
-      <c r="D650" t="inlineStr"/>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -14716,7 +14732,11 @@
           <t>mamta.nath@e-pspl.com</t>
         </is>
       </c>
-      <c r="D651" t="inlineStr"/>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -14734,7 +14754,11 @@
           <t>mamta.yadav@amantyatech.com</t>
         </is>
       </c>
-      <c r="D652" t="inlineStr"/>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -14752,7 +14776,11 @@
           <t>mamtha@sigmoidanalytics.com</t>
         </is>
       </c>
-      <c r="D653" t="inlineStr"/>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -14770,7 +14798,11 @@
           <t>mamtha.akula@netradyne.com</t>
         </is>
       </c>
-      <c r="D654" t="inlineStr"/>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -14788,7 +14820,11 @@
           <t>mchakraborty@phdata.io</t>
         </is>
       </c>
-      <c r="D655" t="inlineStr"/>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -14842,7 +14842,11 @@
           <t>manasi.kelkar@cropin.com</t>
         </is>
       </c>
-      <c r="D656" t="inlineStr"/>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -14860,7 +14864,11 @@
           <t>manav.jain@loconav.com</t>
         </is>
       </c>
-      <c r="D657" t="inlineStr"/>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -14878,7 +14886,11 @@
           <t>manda.kishore@evolutyz.com</t>
         </is>
       </c>
-      <c r="D658" t="inlineStr"/>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -14896,7 +14908,11 @@
           <t>mandeep.singh@tulip.co</t>
         </is>
       </c>
-      <c r="D659" t="inlineStr"/>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -14914,7 +14930,11 @@
           <t>mandeep.virdi@esri.in</t>
         </is>
       </c>
-      <c r="D660" t="inlineStr"/>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -14932,7 +14952,11 @@
           <t>manin@karyatech.com</t>
         </is>
       </c>
-      <c r="D661" t="inlineStr"/>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -14950,7 +14974,11 @@
           <t>manian@callezee.com</t>
         </is>
       </c>
-      <c r="D662" t="inlineStr"/>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -14968,7 +14996,11 @@
           <t>manikmahajan@qainfotech.com</t>
         </is>
       </c>
-      <c r="D663" t="inlineStr"/>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -14986,7 +15018,11 @@
           <t>manik.mondal@qbadvisory.com</t>
         </is>
       </c>
-      <c r="D664" t="inlineStr"/>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -15004,7 +15040,11 @@
           <t>manikandan.b@itech-india.com</t>
         </is>
       </c>
-      <c r="D665" t="inlineStr"/>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -15022,7 +15062,11 @@
           <t>mtripathi@phdata.io</t>
         </is>
       </c>
-      <c r="D666" t="inlineStr"/>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -15040,7 +15084,11 @@
           <t>msitania@egain.com</t>
         </is>
       </c>
-      <c r="D667" t="inlineStr"/>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -15058,7 +15106,11 @@
           <t>manisha@dreamsoft4u.com</t>
         </is>
       </c>
-      <c r="D668" t="inlineStr"/>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -15076,7 +15128,11 @@
           <t>manisha.dash@celigo.com</t>
         </is>
       </c>
-      <c r="D669" t="inlineStr"/>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -15094,7 +15150,11 @@
           <t>mdixit@netrixllc.com</t>
         </is>
       </c>
-      <c r="D670" t="inlineStr"/>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -15112,7 +15172,11 @@
           <t>manjeet.walia@harbingergroup.com</t>
         </is>
       </c>
-      <c r="D671" t="inlineStr"/>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -15130,7 +15194,11 @@
           <t>manjiri.shinde@cloudmoyo.com</t>
         </is>
       </c>
-      <c r="D672" t="inlineStr"/>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -15148,7 +15216,11 @@
           <t>manju.jacob@sarvatra.in</t>
         </is>
       </c>
-      <c r="D673" t="inlineStr"/>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -15166,7 +15238,11 @@
           <t>manju@nichi.com</t>
         </is>
       </c>
-      <c r="D674" t="inlineStr"/>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -15184,7 +15260,11 @@
           <t>manoj@ampl.app</t>
         </is>
       </c>
-      <c r="D675" t="inlineStr"/>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -15202,7 +15282,11 @@
           <t>manoj@techversantinfotech.com</t>
         </is>
       </c>
-      <c r="D676" t="inlineStr"/>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -15220,7 +15304,11 @@
           <t>manoj.parikatil@goodera.com</t>
         </is>
       </c>
-      <c r="D677" t="inlineStr"/>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -15238,7 +15326,11 @@
           <t>mxp@amitysoftware.com</t>
         </is>
       </c>
-      <c r="D678" t="inlineStr"/>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -15256,7 +15348,11 @@
           <t>asta_onboarding@astacrs.com</t>
         </is>
       </c>
-      <c r="D679" t="inlineStr"/>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -15370,7 +15370,11 @@
           <t>manoj.sehgal@rvu.in</t>
         </is>
       </c>
-      <c r="D680" t="inlineStr"/>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -15388,7 +15392,11 @@
           <t>manuel.fernandes@antheliohealth.com</t>
         </is>
       </c>
-      <c r="D681" t="inlineStr"/>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -15406,7 +15414,11 @@
           <t>jobs@skyonn.com</t>
         </is>
       </c>
-      <c r="D682" t="inlineStr"/>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -15424,7 +15436,11 @@
           <t>maria.fernandes@draup.com</t>
         </is>
       </c>
-      <c r="D683" t="inlineStr"/>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -15442,7 +15458,11 @@
           <t>mary.basu@fivesdigital.com</t>
         </is>
       </c>
-      <c r="D684" t="inlineStr"/>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -15460,7 +15480,11 @@
           <t>mary@software.com</t>
         </is>
       </c>
-      <c r="D685" t="inlineStr"/>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -15478,7 +15502,11 @@
           <t>maximus.j@infoplusltd.co.uk</t>
         </is>
       </c>
-      <c r="D686" t="inlineStr"/>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -15496,7 +15524,11 @@
           <t>maya.john@verse.in</t>
         </is>
       </c>
-      <c r="D687" t="inlineStr"/>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -15514,7 +15546,11 @@
           <t>maya.nagpal@verolt.com</t>
         </is>
       </c>
-      <c r="D688" t="inlineStr"/>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -15568,7 +15568,11 @@
           <t>mayank.agarwal@gaana.com</t>
         </is>
       </c>
-      <c r="D689" t="inlineStr"/>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -15586,7 +15590,11 @@
           <t>mayank.ahuja@nickelfox.com</t>
         </is>
       </c>
-      <c r="D690" t="inlineStr"/>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -15604,7 +15612,11 @@
           <t>mayank@tripoto.com</t>
         </is>
       </c>
-      <c r="D691" t="inlineStr"/>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -15622,7 +15634,11 @@
           <t>mmitra@adaequare.com</t>
         </is>
       </c>
-      <c r="D692" t="inlineStr"/>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -15640,7 +15656,11 @@
           <t>mayur.pabari@smartsensesolutions.com</t>
         </is>
       </c>
-      <c r="D693" t="inlineStr"/>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -15658,7 +15678,11 @@
           <t>mayur.sisodiya@collabera.com</t>
         </is>
       </c>
-      <c r="D694" t="inlineStr"/>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -15676,7 +15700,11 @@
           <t>medha.sharma@kiwitech.com</t>
         </is>
       </c>
-      <c r="D695" t="inlineStr"/>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -15694,7 +15722,11 @@
           <t>medhika@uniphore.com</t>
         </is>
       </c>
-      <c r="D696" t="inlineStr"/>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -15712,7 +15744,11 @@
           <t>meena@airmeet.com</t>
         </is>
       </c>
-      <c r="D697" t="inlineStr"/>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -15730,7 +15766,11 @@
           <t>meenakshi.banerjee@crmnext.in</t>
         </is>
       </c>
-      <c r="D698" t="inlineStr"/>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -15748,7 +15788,11 @@
           <t>meenakshi.jha@talentica.com</t>
         </is>
       </c>
-      <c r="D699" t="inlineStr"/>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -15766,7 +15810,11 @@
           <t>meenakshi.kogje@newvisionsoftware.in</t>
         </is>
       </c>
-      <c r="D700" t="inlineStr"/>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -15784,7 +15832,11 @@
           <t>megh@inheritx.com</t>
         </is>
       </c>
-      <c r="D701" t="inlineStr"/>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -15802,7 +15854,11 @@
           <t>megh.risaldar@sms-magic.com</t>
         </is>
       </c>
-      <c r="D702" t="inlineStr"/>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -15820,7 +15876,11 @@
           <t>megh@godrej.com</t>
         </is>
       </c>
-      <c r="D703" t="inlineStr"/>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -15838,7 +15898,11 @@
           <t>meghana@idrive.com</t>
         </is>
       </c>
-      <c r="D704" t="inlineStr"/>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -15856,7 +15920,11 @@
           <t>meghnam@smartek21.com</t>
         </is>
       </c>
-      <c r="D705" t="inlineStr"/>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -15874,7 +15942,11 @@
           <t>mehak@startupnation.com</t>
         </is>
       </c>
-      <c r="D706" t="inlineStr"/>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -15892,7 +15964,11 @@
           <t>gaurav@mphrx.com</t>
         </is>
       </c>
-      <c r="D707" t="inlineStr"/>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -15910,7 +15986,11 @@
           <t>michelle.joseph@gupshup.io</t>
         </is>
       </c>
-      <c r="D708" t="inlineStr"/>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -15928,7 +16008,11 @@
           <t>mili.panicker@webengage.com</t>
         </is>
       </c>
-      <c r="D709" t="inlineStr"/>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -15946,7 +16030,11 @@
           <t>minal.vilekar@theimperative.in</t>
         </is>
       </c>
-      <c r="D710" t="inlineStr"/>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -15964,7 +16052,11 @@
           <t>minal@protechmanize.com</t>
         </is>
       </c>
-      <c r="D711" t="inlineStr"/>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -15982,7 +16074,11 @@
           <t>miriam.shaju@avanzegroup.com</t>
         </is>
       </c>
-      <c r="D712" t="inlineStr"/>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -16096,7 +16096,11 @@
           <t>mirunalini@volantetech.com</t>
         </is>
       </c>
-      <c r="D713" t="inlineStr"/>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -16114,7 +16118,11 @@
           <t>mithun.jose@savantis.com</t>
         </is>
       </c>
-      <c r="D714" t="inlineStr"/>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -16132,7 +16140,11 @@
           <t>m.patel@easternenterprise.com</t>
         </is>
       </c>
-      <c r="D715" t="inlineStr"/>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -16150,7 +16162,11 @@
           <t>mhussain@trimaxamericas.com</t>
         </is>
       </c>
-      <c r="D716" t="inlineStr"/>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -16168,7 +16184,11 @@
           <t>msiddique@quessgts.com</t>
         </is>
       </c>
-      <c r="D717" t="inlineStr"/>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -16186,7 +16206,11 @@
           <t>mohammed@uniphore.com</t>
         </is>
       </c>
-      <c r="D718" t="inlineStr"/>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -16204,7 +16228,11 @@
           <t>mohammed.rizwan@reverieinc.com</t>
         </is>
       </c>
-      <c r="D719" t="inlineStr"/>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -16222,7 +16250,11 @@
           <t>samiullah.mohammed@antheliohealth.com</t>
         </is>
       </c>
-      <c r="D720" t="inlineStr"/>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -16240,7 +16272,11 @@
           <t>tariq.yaseen@panzertechnologies.net</t>
         </is>
       </c>
-      <c r="D721" t="inlineStr"/>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -16258,7 +16294,11 @@
           <t>mohan.joshi@myglamm.com</t>
         </is>
       </c>
-      <c r="D722" t="inlineStr"/>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -16276,7 +16316,11 @@
           <t>mbansal@deqode.com</t>
         </is>
       </c>
-      <c r="D723" t="inlineStr"/>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -16294,7 +16338,11 @@
           <t>monica.bajaj@soft-corner.com</t>
         </is>
       </c>
-      <c r="D724" t="inlineStr"/>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -16312,7 +16360,11 @@
           <t>monica@pingasolutions.com</t>
         </is>
       </c>
-      <c r="D725" t="inlineStr"/>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -16330,7 +16382,11 @@
           <t>monika@precisiontechcorp.com</t>
         </is>
       </c>
-      <c r="D726" t="inlineStr"/>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -16348,7 +16404,11 @@
           <t>monika@embitel.com</t>
         </is>
       </c>
-      <c r="D727" t="inlineStr"/>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -16366,7 +16426,11 @@
           <t>monika.miglani@zigram.tech</t>
         </is>
       </c>
-      <c r="D728" t="inlineStr"/>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -16384,7 +16448,11 @@
           <t>monika@bridgelabz.com</t>
         </is>
       </c>
-      <c r="D729" t="inlineStr"/>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -16402,7 +16470,11 @@
           <t>monika@techretail.in</t>
         </is>
       </c>
-      <c r="D730" t="inlineStr"/>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -16420,7 +16492,11 @@
           <t>mgupta@helm360.com</t>
         </is>
       </c>
-      <c r="D731" t="inlineStr"/>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -16438,7 +16514,11 @@
           <t>moumi@spartanpoker.com</t>
         </is>
       </c>
-      <c r="D732" t="inlineStr"/>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -16456,7 +16536,11 @@
           <t>mrudhula.g@feuji.com</t>
         </is>
       </c>
-      <c r="D733" t="inlineStr"/>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
@@ -16474,7 +16558,11 @@
           <t>mrudul.k@fssglobal.in</t>
         </is>
       </c>
-      <c r="D734" t="inlineStr"/>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -16492,7 +16580,11 @@
           <t>mruga.dave@vagaro.com</t>
         </is>
       </c>
-      <c r="D735" t="inlineStr"/>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -16510,7 +16602,11 @@
           <t>mrugesh.maisuriya@procuretiger.com</t>
         </is>
       </c>
-      <c r="D736" t="inlineStr"/>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -16624,7 +16624,11 @@
           <t>mrugesh.raval@nascentinfo.com</t>
         </is>
       </c>
-      <c r="D737" t="inlineStr"/>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -16642,7 +16646,11 @@
           <t>mugdha.wagh@ellicium.com</t>
         </is>
       </c>
-      <c r="D738" t="inlineStr"/>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -16660,7 +16668,11 @@
           <t>payable@awign.com</t>
         </is>
       </c>
-      <c r="D739" t="inlineStr"/>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -16678,7 +16690,11 @@
           <t>mujeeb@panzertechnologies.net</t>
         </is>
       </c>
-      <c r="D740" t="inlineStr"/>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -16696,7 +16712,11 @@
           <t>mukesh.t@lrsservices.in</t>
         </is>
       </c>
-      <c r="D741" t="inlineStr"/>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
@@ -16714,7 +16734,11 @@
           <t>mukta.dar@absolutdata.com</t>
         </is>
       </c>
-      <c r="D742" t="inlineStr"/>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -16732,7 +16756,11 @@
           <t>mukta.dewan@caeliusconsulting.com</t>
         </is>
       </c>
-      <c r="D743" t="inlineStr"/>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
@@ -16750,7 +16778,11 @@
           <t>murali.k@excelacom.in</t>
         </is>
       </c>
-      <c r="D744" t="inlineStr"/>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
@@ -16768,7 +16800,11 @@
           <t>murali@softlogicsys.in</t>
         </is>
       </c>
-      <c r="D745" t="inlineStr"/>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
@@ -16786,7 +16822,11 @@
           <t>pmurugesan@corenttech.com</t>
         </is>
       </c>
-      <c r="D746" t="inlineStr"/>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
@@ -16804,7 +16844,11 @@
           <t>muthukumar.k@technogeninc.com</t>
         </is>
       </c>
-      <c r="D747" t="inlineStr"/>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
@@ -16822,7 +16866,11 @@
           <t>muthyala.manasa@absyz.com</t>
         </is>
       </c>
-      <c r="D748" t="inlineStr"/>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -16840,7 +16888,11 @@
           <t>n.siddharth@urbanpiper.com</t>
         </is>
       </c>
-      <c r="D749" t="inlineStr"/>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
@@ -16858,7 +16910,11 @@
           <t>nagamani.yerneni@softsol.com</t>
         </is>
       </c>
-      <c r="D750" t="inlineStr"/>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
@@ -16876,7 +16932,11 @@
           <t>naganagouda.sj@globaledgesoft.com</t>
         </is>
       </c>
-      <c r="D751" t="inlineStr"/>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
@@ -16894,7 +16954,11 @@
           <t>naindeep.kaur@bpktechmail.com</t>
         </is>
       </c>
-      <c r="D752" t="inlineStr"/>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
@@ -16912,7 +16976,11 @@
           <t>nalini@amresearch.in</t>
         </is>
       </c>
-      <c r="D753" t="inlineStr"/>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
@@ -16930,7 +16998,11 @@
           <t>namita.sinha@sunlife.com</t>
         </is>
       </c>
-      <c r="D754" t="inlineStr"/>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -16948,7 +17020,11 @@
           <t>namrata.k@inspiredgeit.com</t>
         </is>
       </c>
-      <c r="D755" t="inlineStr"/>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
@@ -16966,7 +17042,11 @@
           <t>nancy.andrews@ideas2it.com</t>
         </is>
       </c>
-      <c r="D756" t="inlineStr"/>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
@@ -16984,7 +17064,11 @@
           <t>nancy.varghese@inflowtechnologies.com</t>
         </is>
       </c>
-      <c r="D757" t="inlineStr"/>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
@@ -17002,7 +17086,11 @@
           <t>nandakishore.padmanabhan@crmnext.com</t>
         </is>
       </c>
-      <c r="D758" t="inlineStr"/>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
@@ -17020,7 +17108,11 @@
           <t>nandini.aggarwal@enhancesys.com</t>
         </is>
       </c>
-      <c r="D759" t="inlineStr"/>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
@@ -17038,7 +17130,11 @@
           <t>nandini.tandon@indusface.com</t>
         </is>
       </c>
-      <c r="D760" t="inlineStr"/>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -17152,7 +17152,11 @@
           <t>nandita.singh@selp.in</t>
         </is>
       </c>
-      <c r="D761" t="inlineStr"/>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
@@ -17170,7 +17174,11 @@
           <t>nbhatnagar@e-emphasys.com</t>
         </is>
       </c>
-      <c r="D762" t="inlineStr"/>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
@@ -17188,7 +17196,11 @@
           <t>narasimhan@opsera.io</t>
         </is>
       </c>
-      <c r="D763" t="inlineStr"/>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
@@ -17206,7 +17218,11 @@
           <t>narayana@smartedgesolutions.co.uk</t>
         </is>
       </c>
-      <c r="D764" t="inlineStr"/>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -17224,7 +17240,11 @@
           <t>narayana.pawar@privafy.com</t>
         </is>
       </c>
-      <c r="D765" t="inlineStr"/>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
@@ -17242,7 +17262,11 @@
           <t>narender@lsarecruit.co.uk</t>
         </is>
       </c>
-      <c r="D766" t="inlineStr"/>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
@@ -17260,7 +17284,11 @@
           <t>narendra.s@netenrich.com</t>
         </is>
       </c>
-      <c r="D767" t="inlineStr"/>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
@@ -17278,7 +17306,11 @@
           <t>naresh@ncsus.net</t>
         </is>
       </c>
-      <c r="D768" t="inlineStr"/>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
@@ -17296,7 +17328,11 @@
           <t>naresh.nuthulapati@atmecs.com</t>
         </is>
       </c>
-      <c r="D769" t="inlineStr"/>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -17350,7 +17350,11 @@
           <t>natarajan@uniquehire.in</t>
         </is>
       </c>
-      <c r="D770" t="inlineStr"/>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
@@ -17368,7 +17372,11 @@
           <t>naveen@primusglobal.com</t>
         </is>
       </c>
-      <c r="D771" t="inlineStr"/>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
@@ -17386,7 +17394,11 @@
           <t>naveen@crayondata.com</t>
         </is>
       </c>
-      <c r="D772" t="inlineStr"/>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
@@ -17404,7 +17416,11 @@
           <t>naveen.shankar@estuate.com</t>
         </is>
       </c>
-      <c r="D773" t="inlineStr"/>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
@@ -17422,7 +17438,11 @@
           <t>naveen.s@bourntec.com</t>
         </is>
       </c>
-      <c r="D774" t="inlineStr"/>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
@@ -17440,7 +17460,11 @@
           <t>naveen@dynpro.com</t>
         </is>
       </c>
-      <c r="D775" t="inlineStr"/>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
@@ -17458,7 +17482,11 @@
           <t>navleen.bhatia@tcs.com</t>
         </is>
       </c>
-      <c r="D776" t="inlineStr"/>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
@@ -17476,7 +17504,11 @@
           <t>navneet@inventechinfo.com</t>
         </is>
       </c>
-      <c r="D777" t="inlineStr"/>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
@@ -17494,7 +17526,11 @@
           <t>nawaaz.hafeez@ivlglobal.com</t>
         </is>
       </c>
-      <c r="D778" t="inlineStr"/>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
@@ -17512,7 +17548,11 @@
           <t>nayaki@numerictech.com</t>
         </is>
       </c>
-      <c r="D779" t="inlineStr"/>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
@@ -17530,7 +17570,11 @@
           <t>nayanam@aditiconsulting.com</t>
         </is>
       </c>
-      <c r="D780" t="inlineStr"/>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
@@ -17548,7 +17592,11 @@
           <t>nayazuddin.meer@slkgroup.com</t>
         </is>
       </c>
-      <c r="D781" t="inlineStr"/>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
@@ -17566,7 +17614,11 @@
           <t>neel.rao@serole.com</t>
         </is>
       </c>
-      <c r="D782" t="inlineStr"/>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
@@ -17584,7 +17636,11 @@
           <t>neelam.sharma@provartesting.com</t>
         </is>
       </c>
-      <c r="D783" t="inlineStr"/>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
@@ -17602,7 +17658,11 @@
           <t>neelima.vaka@minfytech.com</t>
         </is>
       </c>
-      <c r="D784" t="inlineStr"/>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -17680,7 +17680,11 @@
           <t>nagle@valethi.com</t>
         </is>
       </c>
-      <c r="D785" t="inlineStr"/>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -17698,7 +17702,11 @@
           <t>neena@fintinc.com</t>
         </is>
       </c>
-      <c r="D786" t="inlineStr"/>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -17716,7 +17724,11 @@
           <t>neerajsharma@cavistatech.com</t>
         </is>
       </c>
-      <c r="D787" t="inlineStr"/>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -17734,7 +17746,11 @@
           <t>neeraj@fourkites.com</t>
         </is>
       </c>
-      <c r="D788" t="inlineStr"/>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -17752,7 +17768,11 @@
           <t>neetu.choudhary@idsnext.com</t>
         </is>
       </c>
-      <c r="D789" t="inlineStr"/>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -17770,7 +17790,11 @@
           <t>neha.bhandari@vmock.com</t>
         </is>
       </c>
-      <c r="D790" t="inlineStr"/>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -17788,7 +17812,11 @@
           <t>nbhise@tracelink.com</t>
         </is>
       </c>
-      <c r="D791" t="inlineStr"/>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -17806,7 +17834,11 @@
           <t>neha@thinkbridge.com</t>
         </is>
       </c>
-      <c r="D792" t="inlineStr"/>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
@@ -17824,7 +17856,11 @@
           <t>neha.c@greyorange.com</t>
         </is>
       </c>
-      <c r="D793" t="inlineStr"/>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -17842,7 +17878,11 @@
           <t>neha@aistechnolabs.com</t>
         </is>
       </c>
-      <c r="D794" t="inlineStr"/>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
@@ -17860,7 +17900,11 @@
           <t>nchoudhary@tractionondemand.com</t>
         </is>
       </c>
-      <c r="D795" t="inlineStr"/>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -17878,7 +17922,11 @@
           <t>neha.kohli@benq.com</t>
         </is>
       </c>
-      <c r="D796" t="inlineStr"/>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
@@ -17896,7 +17944,11 @@
           <t>neha@i2k2.com</t>
         </is>
       </c>
-      <c r="D797" t="inlineStr"/>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -17914,7 +17966,11 @@
           <t>neha@trell.in</t>
         </is>
       </c>
-      <c r="D798" t="inlineStr"/>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -17932,7 +17988,11 @@
           <t>nehasharma@freeskout.com</t>
         </is>
       </c>
-      <c r="D799" t="inlineStr"/>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
@@ -17950,7 +18010,11 @@
           <t>neha.sharma@infodartmail.com</t>
         </is>
       </c>
-      <c r="D800" t="inlineStr"/>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -17968,7 +18032,11 @@
           <t>neha.sharma@cavisson.com</t>
         </is>
       </c>
-      <c r="D801" t="inlineStr"/>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -17986,7 +18054,11 @@
           <t>neha@multiqos.com</t>
         </is>
       </c>
-      <c r="D802" t="inlineStr"/>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
@@ -18004,7 +18076,11 @@
           <t>neha@dynalogindia.com</t>
         </is>
       </c>
-      <c r="D803" t="inlineStr"/>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
@@ -18022,7 +18098,11 @@
           <t>neville.postwalla@harbingergroup.com</t>
         </is>
       </c>
-      <c r="D804" t="inlineStr"/>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
@@ -18040,7 +18120,11 @@
           <t>nevyg@norwintechnologies.com</t>
         </is>
       </c>
-      <c r="D805" t="inlineStr"/>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
@@ -18058,7 +18142,11 @@
           <t>nibedita.dutta@natureglobal.com</t>
         </is>
       </c>
-      <c r="D806" t="inlineStr"/>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -18076,7 +18164,11 @@
           <t>nidhi.vishnoi@2isolutions.com</t>
         </is>
       </c>
-      <c r="D807" t="inlineStr"/>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
@@ -18094,7 +18186,11 @@
           <t>nidhi@empirix.com</t>
         </is>
       </c>
-      <c r="D808" t="inlineStr"/>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -18208,7 +18208,11 @@
           <t>nidhi@indusnet.co.in</t>
         </is>
       </c>
-      <c r="D809" t="inlineStr"/>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -18226,7 +18230,11 @@
           <t>nidhi@cystemslogic.com</t>
         </is>
       </c>
-      <c r="D810" t="inlineStr"/>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
@@ -18244,7 +18252,11 @@
           <t>nidhi.singh@iapcorp.com</t>
         </is>
       </c>
-      <c r="D811" t="inlineStr"/>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
@@ -18262,7 +18274,11 @@
           <t>nidhi.srivastava@trangile.com</t>
         </is>
       </c>
-      <c r="D812" t="inlineStr"/>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -18280,7 +18296,11 @@
           <t>nidhuraj@everest.engineering</t>
         </is>
       </c>
-      <c r="D813" t="inlineStr"/>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -18298,7 +18318,11 @@
           <t>nigel@recruitnxt.com</t>
         </is>
       </c>
-      <c r="D814" t="inlineStr"/>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
@@ -18316,7 +18340,11 @@
           <t>niharika.patel@jetsynthesys.com</t>
         </is>
       </c>
-      <c r="D815" t="inlineStr"/>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -18334,7 +18362,11 @@
           <t>nikhil.bhat@lipi.in</t>
         </is>
       </c>
-      <c r="D816" t="inlineStr"/>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
@@ -18352,7 +18384,11 @@
           <t>nikhil.jangir@saviance.com</t>
         </is>
       </c>
-      <c r="D817" t="inlineStr"/>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -18406,7 +18406,11 @@
           <t>nikhil.kadu@verinite.com</t>
         </is>
       </c>
-      <c r="D818" t="inlineStr"/>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
@@ -18424,7 +18428,11 @@
           <t>nikhil.kulkarni@ncircletech.com</t>
         </is>
       </c>
-      <c r="D819" t="inlineStr"/>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
@@ -18442,7 +18450,11 @@
           <t>nikhil.m@purplle.com</t>
         </is>
       </c>
-      <c r="D820" t="inlineStr"/>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
@@ -18460,7 +18472,11 @@
           <t>nikita@goleadingit.com</t>
         </is>
       </c>
-      <c r="D821" t="inlineStr"/>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
@@ -18478,7 +18494,11 @@
           <t>nilangini.gupta@panamaxil.com</t>
         </is>
       </c>
-      <c r="D822" t="inlineStr"/>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
@@ -18496,7 +18516,11 @@
           <t>nilesh.indulkar@trantorinc.com</t>
         </is>
       </c>
-      <c r="D823" t="inlineStr"/>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
@@ -18514,7 +18538,11 @@
           <t>nimesh@haptik.ai</t>
         </is>
       </c>
-      <c r="D824" t="inlineStr"/>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
@@ -18532,7 +18560,11 @@
           <t>nimesh@jeavio.com</t>
         </is>
       </c>
-      <c r="D825" t="inlineStr"/>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
@@ -18550,7 +18582,11 @@
           <t>nimmy.c@v2solutions.com</t>
         </is>
       </c>
-      <c r="D826" t="inlineStr"/>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
@@ -18568,7 +18604,11 @@
           <t>nipsy.jhamb@altudo.co</t>
         </is>
       </c>
-      <c r="D827" t="inlineStr"/>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
@@ -18586,7 +18626,11 @@
           <t>nirmaln@scorgconsult.com</t>
         </is>
       </c>
-      <c r="D828" t="inlineStr"/>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
@@ -18604,7 +18648,11 @@
           <t>nirmala@technobind.com</t>
         </is>
       </c>
-      <c r="D829" t="inlineStr"/>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
@@ -18622,7 +18670,11 @@
           <t>nirmiti.hr@eventbeep.com</t>
         </is>
       </c>
-      <c r="D830" t="inlineStr"/>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
@@ -18640,7 +18692,11 @@
           <t>nirupa.l@smaartt.com</t>
         </is>
       </c>
-      <c r="D831" t="inlineStr"/>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
@@ -18658,7 +18714,11 @@
           <t>sridhar.n@qwikcilver.com</t>
         </is>
       </c>
-      <c r="D832" t="inlineStr"/>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -18736,7 +18736,11 @@
           <t>nirzari.sen@benisontech.com</t>
         </is>
       </c>
-      <c r="D833" t="inlineStr"/>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
@@ -18754,7 +18758,11 @@
           <t>nisha.motwani@pratititech.com</t>
         </is>
       </c>
-      <c r="D834" t="inlineStr"/>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
@@ -18772,7 +18780,11 @@
           <t>nisha.nair@sagarsoft.in</t>
         </is>
       </c>
-      <c r="D835" t="inlineStr"/>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
@@ -18790,7 +18802,11 @@
           <t>nisha.n@technovert.com</t>
         </is>
       </c>
-      <c r="D836" t="inlineStr"/>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
@@ -18808,7 +18824,11 @@
           <t>nisharoy@aabasoft.com</t>
         </is>
       </c>
-      <c r="D837" t="inlineStr"/>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
@@ -18826,7 +18846,11 @@
           <t>nisha.saini@aurigait.com</t>
         </is>
       </c>
-      <c r="D838" t="inlineStr"/>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
@@ -18844,7 +18868,11 @@
           <t>nisha.s@seanergydigital.com</t>
         </is>
       </c>
-      <c r="D839" t="inlineStr"/>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
@@ -18862,7 +18890,11 @@
           <t>nishant@smartkargo.com</t>
         </is>
       </c>
-      <c r="D840" t="inlineStr"/>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
@@ -18880,7 +18912,11 @@
           <t>nishant.shukla@hoonartek.com</t>
         </is>
       </c>
-      <c r="D841" t="inlineStr"/>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
@@ -18898,7 +18934,11 @@
           <t>nishita@fissionlabs.com</t>
         </is>
       </c>
-      <c r="D842" t="inlineStr"/>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
@@ -18916,7 +18956,11 @@
           <t>nishith.parikh@krishtechnolabs.com</t>
         </is>
       </c>
-      <c r="D843" t="inlineStr"/>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
@@ -18934,7 +18978,11 @@
           <t>nishtha.sareen@dionglobal.com</t>
         </is>
       </c>
-      <c r="D844" t="inlineStr"/>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
@@ -18952,7 +19000,11 @@
           <t>nishu.nits@ongraph.com</t>
         </is>
       </c>
-      <c r="D845" t="inlineStr"/>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
@@ -18970,7 +19022,11 @@
           <t>naryasomayajula@rrootshell.com</t>
         </is>
       </c>
-      <c r="D846" t="inlineStr"/>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
@@ -18988,7 +19044,11 @@
           <t>nitasha.dusi@atidiv.com</t>
         </is>
       </c>
-      <c r="D847" t="inlineStr"/>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
@@ -19006,7 +19066,11 @@
           <t>nitesh.karir@moksatechnologies.com</t>
         </is>
       </c>
-      <c r="D848" t="inlineStr"/>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -19024,7 +19088,11 @@
           <t>nithyanandham@facilio.com</t>
         </is>
       </c>
-      <c r="D849" t="inlineStr"/>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
@@ -19042,7 +19110,11 @@
           <t>nitika.bhandari@mavenwave.com</t>
         </is>
       </c>
-      <c r="D850" t="inlineStr"/>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
@@ -19060,7 +19132,11 @@
           <t>nitin.g@intellectbizware.com</t>
         </is>
       </c>
-      <c r="D851" t="inlineStr"/>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
@@ -19078,7 +19154,11 @@
           <t>nitin.m@totalitglobal.com</t>
         </is>
       </c>
-      <c r="D852" t="inlineStr"/>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -19096,7 +19176,11 @@
           <t>nitin.nahata@gameskraft.com</t>
         </is>
       </c>
-      <c r="D853" t="inlineStr"/>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
@@ -19114,7 +19198,11 @@
           <t>nitin.padharia@indianic.com</t>
         </is>
       </c>
-      <c r="D854" t="inlineStr"/>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -19132,7 +19220,11 @@
           <t>nitin@itlize.com</t>
         </is>
       </c>
-      <c r="D855" t="inlineStr"/>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -19150,7 +19242,11 @@
           <t>nitin.sharma@altudo.co</t>
         </is>
       </c>
-      <c r="D856" t="inlineStr"/>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -19264,7 +19264,11 @@
           <t>nitin.suri@webomaze.com</t>
         </is>
       </c>
-      <c r="D857" t="inlineStr"/>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
@@ -19282,7 +19286,11 @@
           <t>nitin.verma@xicom.biz</t>
         </is>
       </c>
-      <c r="D858" t="inlineStr"/>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
@@ -19300,7 +19308,11 @@
           <t>nitish.k@sphinxworldbiz.com</t>
         </is>
       </c>
-      <c r="D859" t="inlineStr"/>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
@@ -19318,7 +19330,11 @@
           <t>nitisha.baalay@innovapptive.com</t>
         </is>
       </c>
-      <c r="D860" t="inlineStr"/>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
@@ -19336,7 +19352,11 @@
           <t>nk@ezesoft.com</t>
         </is>
       </c>
-      <c r="D861" t="inlineStr"/>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
@@ -19354,7 +19374,11 @@
           <t>nivedita.kaushal@idmworks.com</t>
         </is>
       </c>
-      <c r="D862" t="inlineStr"/>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
@@ -19372,7 +19396,11 @@
           <t>nivrutha.s@appviewx.com</t>
         </is>
       </c>
-      <c r="D863" t="inlineStr"/>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
@@ -19390,7 +19418,11 @@
           <t>niyati@teksun.us</t>
         </is>
       </c>
-      <c r="D864" t="inlineStr"/>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
@@ -19408,7 +19440,11 @@
           <t>nupur@ixigo.com</t>
         </is>
       </c>
-      <c r="D865" t="inlineStr"/>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -19462,7 +19462,11 @@
           <t>nphatak@potomactpl.com</t>
         </is>
       </c>
-      <c r="D866" t="inlineStr"/>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
@@ -19480,7 +19484,11 @@
           <t>nusrat.supediwala@panamaxil.com</t>
         </is>
       </c>
-      <c r="D867" t="inlineStr"/>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
@@ -19498,7 +19506,11 @@
           <t>info@o2finfo.com</t>
         </is>
       </c>
-      <c r="D868" t="inlineStr"/>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
@@ -19516,7 +19528,11 @@
           <t>oindrila.das@rteservices.com</t>
         </is>
       </c>
-      <c r="D869" t="inlineStr"/>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
@@ -19534,7 +19550,11 @@
           <t>omeshmakhija@appitsimple.com</t>
         </is>
       </c>
-      <c r="D870" t="inlineStr"/>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
@@ -19552,7 +19572,11 @@
           <t>omkarp@coreflexsolutions.com</t>
         </is>
       </c>
-      <c r="D871" t="inlineStr"/>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
@@ -19570,7 +19594,11 @@
           <t>padmajasingh.arya@cogencis.com</t>
         </is>
       </c>
-      <c r="D872" t="inlineStr"/>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
@@ -19588,7 +19616,11 @@
           <t>padmanavk@nsdl.co.in</t>
         </is>
       </c>
-      <c r="D873" t="inlineStr"/>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
@@ -19606,7 +19638,11 @@
           <t>padmashree.alva@mresult.com</t>
         </is>
       </c>
-      <c r="D874" t="inlineStr"/>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
@@ -19624,7 +19660,11 @@
           <t>pmishra@bhavnacorp.com</t>
         </is>
       </c>
-      <c r="D875" t="inlineStr"/>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
@@ -19642,7 +19682,11 @@
           <t>pallavi.sharma@digimantra.com</t>
         </is>
       </c>
-      <c r="D876" t="inlineStr"/>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
@@ -19660,7 +19704,11 @@
           <t>pallavi.singh@paycraftsol.com</t>
         </is>
       </c>
-      <c r="D877" t="inlineStr"/>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
@@ -19678,7 +19726,11 @@
           <t>pallavi@techmatrixconsulting.com</t>
         </is>
       </c>
-      <c r="D878" t="inlineStr"/>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
@@ -19696,7 +19748,11 @@
           <t>panchalid@zenoti.com</t>
         </is>
       </c>
-      <c r="D879" t="inlineStr"/>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
@@ -19714,7 +19770,11 @@
           <t>pandey@fsltechnologies.com</t>
         </is>
       </c>
-      <c r="D880" t="inlineStr"/>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -19792,7 +19792,11 @@
           <t>pankaj.chopra@corecard.com</t>
         </is>
       </c>
-      <c r="D881" t="inlineStr"/>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
@@ -19810,7 +19814,11 @@
           <t>psingh@everquote.com</t>
         </is>
       </c>
-      <c r="D882" t="inlineStr"/>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
@@ -19828,7 +19836,11 @@
           <t>paramananda.c@itelligencegroup.com</t>
         </is>
       </c>
-      <c r="D883" t="inlineStr"/>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
@@ -19846,7 +19858,11 @@
           <t>parameswar.p@recykal.com</t>
         </is>
       </c>
-      <c r="D884" t="inlineStr"/>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
@@ -19864,7 +19880,11 @@
           <t>pardeepp@damcogroup.com</t>
         </is>
       </c>
-      <c r="D885" t="inlineStr"/>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
@@ -19882,7 +19902,11 @@
           <t>parinita.kaur@intellolabs.com</t>
         </is>
       </c>
-      <c r="D886" t="inlineStr"/>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
@@ -19900,7 +19924,11 @@
           <t>pdutta@diabsolut.com</t>
         </is>
       </c>
-      <c r="D887" t="inlineStr"/>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
@@ -19918,7 +19946,11 @@
           <t>parneet.waraich@myrealdata.in</t>
         </is>
       </c>
-      <c r="D888" t="inlineStr"/>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
@@ -19936,7 +19968,11 @@
           <t>paromita.areng@zaggle.in</t>
         </is>
       </c>
-      <c r="D889" t="inlineStr"/>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -19990,7 +19990,11 @@
           <t>parool.duggal@bijnis.com</t>
         </is>
       </c>
-      <c r="D890" t="inlineStr"/>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
@@ -20008,7 +20012,11 @@
           <t>pparavasthu@vitechinc.com</t>
         </is>
       </c>
-      <c r="D891" t="inlineStr"/>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
@@ -20026,7 +20034,11 @@
           <t>parthiban.santhanakrishnan@volantetech. com</t>
         </is>
       </c>
-      <c r="D892" t="inlineStr"/>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
@@ -20044,7 +20056,11 @@
           <t>parul.gala@smarteinc.com</t>
         </is>
       </c>
-      <c r="D893" t="inlineStr"/>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
@@ -20062,7 +20078,11 @@
           <t>parvathy.therembil@sourcebits.com</t>
         </is>
       </c>
-      <c r="D894" t="inlineStr"/>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
@@ -20080,7 +20100,11 @@
           <t>amjad.pasha@fiorano.com</t>
         </is>
       </c>
-      <c r="D895" t="inlineStr"/>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
@@ -20098,7 +20122,11 @@
           <t>patel.kavita@jeksonvision.com</t>
         </is>
       </c>
-      <c r="D896" t="inlineStr"/>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
@@ -20116,7 +20144,11 @@
           <t>pathanjali.bhat@relevancelab.com</t>
         </is>
       </c>
-      <c r="D897" t="inlineStr"/>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
@@ -20134,7 +20166,11 @@
           <t>patricia.natalia@learnquest.com</t>
         </is>
       </c>
-      <c r="D898" t="inlineStr"/>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
@@ -20152,7 +20188,11 @@
           <t>paul.jacob@pramati.com</t>
         </is>
       </c>
-      <c r="D899" t="inlineStr"/>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
@@ -20170,7 +20210,11 @@
           <t>paul.daniel@tanla.com</t>
         </is>
       </c>
-      <c r="D900" t="inlineStr"/>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
@@ -20188,7 +20232,11 @@
           <t>paul@salesken.ai</t>
         </is>
       </c>
-      <c r="D901" t="inlineStr"/>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
@@ -20206,7 +20254,11 @@
           <t>pavan.b@fluentgrid.com</t>
         </is>
       </c>
-      <c r="D902" t="inlineStr"/>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
@@ -20224,7 +20276,11 @@
           <t>pk@eightfold.ai</t>
         </is>
       </c>
-      <c r="D903" t="inlineStr"/>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
@@ -20242,7 +20298,11 @@
           <t>pavankumar.k@winwire.com</t>
         </is>
       </c>
-      <c r="D904" t="inlineStr"/>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -20320,7 +20320,11 @@
           <t>pkumar@appstekcorp.com</t>
         </is>
       </c>
-      <c r="D905" t="inlineStr"/>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
@@ -20338,7 +20342,11 @@
           <t>pavank@eximiusdesign.com</t>
         </is>
       </c>
-      <c r="D906" t="inlineStr"/>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
@@ -20356,7 +20364,11 @@
           <t>pavan.r@amplelogic.com</t>
         </is>
       </c>
-      <c r="D907" t="inlineStr"/>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
@@ -20374,7 +20386,11 @@
           <t>pavanv@sidgs.com</t>
         </is>
       </c>
-      <c r="D908" t="inlineStr"/>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
@@ -20392,7 +20408,11 @@
           <t>pavan.vemuri@m3bi.com</t>
         </is>
       </c>
-      <c r="D909" t="inlineStr"/>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
@@ -20410,7 +20430,11 @@
           <t>pavan.vooribindi@mckinleyrice.co</t>
         </is>
       </c>
-      <c r="D910" t="inlineStr"/>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
@@ -20428,7 +20452,11 @@
           <t>pavithra.bopanna@entropiktech.com</t>
         </is>
       </c>
-      <c r="D911" t="inlineStr"/>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
@@ -20446,7 +20474,11 @@
           <t>pavithra.desai@infracloud.io</t>
         </is>
       </c>
-      <c r="D912" t="inlineStr"/>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
@@ -20464,7 +20496,11 @@
           <t>payal@highpeaksw.com</t>
         </is>
       </c>
-      <c r="D913" t="inlineStr"/>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -20518,7 +20518,11 @@
           <t>payal@safe.security</t>
         </is>
       </c>
-      <c r="D914" t="inlineStr"/>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
@@ -20536,7 +20540,11 @@
           <t>payyalore.sainath@larvol.com</t>
         </is>
       </c>
-      <c r="D915" t="inlineStr"/>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
@@ -20554,7 +20562,11 @@
           <t>pdsouza@cartesianconsulting.com</t>
         </is>
       </c>
-      <c r="D916" t="inlineStr"/>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
@@ -20572,7 +20584,11 @@
           <t>peeyush.singhal@monsterindia.com</t>
         </is>
       </c>
-      <c r="D917" t="inlineStr"/>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
@@ -20590,7 +20606,11 @@
           <t>peterson.pereira@cignex.com</t>
         </is>
       </c>
-      <c r="D918" t="inlineStr"/>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
@@ -20608,7 +20628,11 @@
           <t>phani@eminds.ai</t>
         </is>
       </c>
-      <c r="D919" t="inlineStr"/>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
@@ -20626,7 +20650,11 @@
           <t>phani.kumar@soroco.com</t>
         </is>
       </c>
-      <c r="D920" t="inlineStr"/>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
@@ -20644,7 +20672,11 @@
           <t>phanidhars@dextara.com</t>
         </is>
       </c>
-      <c r="D921" t="inlineStr"/>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
@@ -20662,7 +20694,11 @@
           <t>philip.manikya@posidex.com</t>
         </is>
       </c>
-      <c r="D922" t="inlineStr"/>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
@@ -20680,7 +20716,11 @@
           <t>piali.goswami@optimusinfo.com</t>
         </is>
       </c>
-      <c r="D923" t="inlineStr"/>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
@@ -20698,7 +20738,11 @@
           <t>piyalib@digitalaptech.com</t>
         </is>
       </c>
-      <c r="D924" t="inlineStr"/>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
@@ -20716,7 +20760,11 @@
           <t>piyush.naik@digivalet.com</t>
         </is>
       </c>
-      <c r="D925" t="inlineStr"/>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
@@ -20734,7 +20782,11 @@
           <t>piyush.r@apna.co</t>
         </is>
       </c>
-      <c r="D926" t="inlineStr"/>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
@@ -20752,7 +20804,11 @@
           <t>pooja@agri10x.com</t>
         </is>
       </c>
-      <c r="D927" t="inlineStr"/>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
@@ -20770,7 +20826,11 @@
           <t>pooja@zentekinfosoft.com</t>
         </is>
       </c>
-      <c r="D928" t="inlineStr"/>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -20848,7 +20848,11 @@
           <t>pooja.arora@minosha.in</t>
         </is>
       </c>
-      <c r="D929" t="inlineStr"/>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
@@ -20866,7 +20870,11 @@
           <t>pooja.m@aress.com</t>
         </is>
       </c>
-      <c r="D930" t="inlineStr"/>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
@@ -20884,7 +20892,11 @@
           <t>pooja.madappa@netradyne.com</t>
         </is>
       </c>
-      <c r="D931" t="inlineStr"/>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
@@ -20902,7 +20914,11 @@
           <t>pooja.malawade@nanostuffs.com</t>
         </is>
       </c>
-      <c r="D932" t="inlineStr"/>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
@@ -20920,7 +20936,11 @@
           <t>pooja@avestacs.com</t>
         </is>
       </c>
-      <c r="D933" t="inlineStr"/>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
@@ -20938,7 +20958,11 @@
           <t>pooja@incnut.com</t>
         </is>
       </c>
-      <c r="D934" t="inlineStr"/>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
@@ -20956,7 +20980,11 @@
           <t>pooja.pareek@myglamm.com</t>
         </is>
       </c>
-      <c r="D935" t="inlineStr"/>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
@@ -20974,7 +21002,11 @@
           <t>poonam@nuvento.com</t>
         </is>
       </c>
-      <c r="D936" t="inlineStr"/>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
@@ -20992,7 +21024,11 @@
           <t>poonam.b@cynetsystems.com</t>
         </is>
       </c>
-      <c r="D937" t="inlineStr"/>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
@@ -21010,7 +21046,11 @@
           <t>poonam.yadav@webmobril.com</t>
         </is>
       </c>
-      <c r="D938" t="inlineStr"/>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
@@ -21028,7 +21068,11 @@
           <t>poornima.gowda@fortanix.com</t>
         </is>
       </c>
-      <c r="D939" t="inlineStr"/>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
@@ -21046,7 +21090,11 @@
           <t>poornima.narayanappa@symphonysummit. com</t>
         </is>
       </c>
-      <c r="D940" t="inlineStr"/>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
@@ -21064,7 +21112,11 @@
           <t>pp@yodlee.com</t>
         </is>
       </c>
-      <c r="D941" t="inlineStr"/>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
@@ -21082,7 +21134,11 @@
           <t>poornima@testvagrant.com</t>
         </is>
       </c>
-      <c r="D942" t="inlineStr"/>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
@@ -21100,7 +21156,11 @@
           <t>poornima.s@d4insight.com</t>
         </is>
       </c>
-      <c r="D943" t="inlineStr"/>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
@@ -21118,7 +21178,11 @@
           <t>poulo@goleadingit.com</t>
         </is>
       </c>
-      <c r="D944" t="inlineStr"/>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
@@ -21136,7 +21200,11 @@
           <t>prabha.giri@acropolisinfotech.com</t>
         </is>
       </c>
-      <c r="D945" t="inlineStr"/>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
@@ -21154,7 +21222,11 @@
           <t>prabha.masilamani@plivo.com</t>
         </is>
       </c>
-      <c r="D946" t="inlineStr"/>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
@@ -21172,7 +21244,11 @@
           <t>prabhu@atmecs.com</t>
         </is>
       </c>
-      <c r="D947" t="inlineStr"/>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
@@ -21190,7 +21266,11 @@
           <t>prachi.singh@vinculumgroup.com</t>
         </is>
       </c>
-      <c r="D948" t="inlineStr"/>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
@@ -21208,7 +21288,11 @@
           <t>pradeep.boiri@otsi.co.in</t>
         </is>
       </c>
-      <c r="D949" t="inlineStr"/>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
@@ -21226,7 +21310,11 @@
           <t>pradeep.chigurupati@mindtickle.com</t>
         </is>
       </c>
-      <c r="D950" t="inlineStr"/>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -21332,7 +21332,11 @@
           <t>pradeep.k@mindteck.com</t>
         </is>
       </c>
-      <c r="D951" t="inlineStr"/>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
@@ -21350,7 +21354,11 @@
           <t>krishnanp@kaizentek.com</t>
         </is>
       </c>
-      <c r="D952" t="inlineStr"/>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
@@ -21368,7 +21376,11 @@
           <t>pradeep.kumar@andortech.com</t>
         </is>
       </c>
-      <c r="D953" t="inlineStr"/>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
@@ -21386,7 +21398,11 @@
           <t>pradeepkumar@newtglobalcorp.com</t>
         </is>
       </c>
-      <c r="D954" t="inlineStr"/>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
@@ -21404,7 +21420,11 @@
           <t>pradeep@bidgely.com</t>
         </is>
       </c>
-      <c r="D955" t="inlineStr"/>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
@@ -21422,7 +21442,11 @@
           <t>pradeep_r@3dplmsoftware.com</t>
         </is>
       </c>
-      <c r="D956" t="inlineStr"/>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
@@ -21440,7 +21464,11 @@
           <t>pradeep@digiryte.com</t>
         </is>
       </c>
-      <c r="D957" t="inlineStr"/>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
@@ -21458,7 +21486,11 @@
           <t>pradeep@servosys.com</t>
         </is>
       </c>
-      <c r="D958" t="inlineStr"/>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
@@ -21476,7 +21508,11 @@
           <t>pradep.s@zuper.co</t>
         </is>
       </c>
-      <c r="D959" t="inlineStr"/>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -21530,7 +21530,11 @@
           <t>pradnya.kulkarni@afourtech.com</t>
         </is>
       </c>
-      <c r="D960" t="inlineStr"/>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
@@ -21548,7 +21552,11 @@
           <t>pjaiswal@xento.com</t>
         </is>
       </c>
-      <c r="D961" t="inlineStr"/>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
@@ -21566,7 +21574,11 @@
           <t>pragati@aryacma.co.in</t>
         </is>
       </c>
-      <c r="D962" t="inlineStr"/>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
@@ -21584,7 +21596,11 @@
           <t>pkumar@aienterprise.com</t>
         </is>
       </c>
-      <c r="D963" t="inlineStr"/>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
@@ -21602,7 +21618,11 @@
           <t>pragati@onamagroup.com</t>
         </is>
       </c>
-      <c r="D964" t="inlineStr"/>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
@@ -21620,7 +21640,11 @@
           <t>pragati.tilve@creativecapsule.com</t>
         </is>
       </c>
-      <c r="D965" t="inlineStr"/>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
@@ -21638,7 +21662,11 @@
           <t>hr.orbit@orbitindia.net</t>
         </is>
       </c>
-      <c r="D966" t="inlineStr"/>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
@@ -21656,7 +21684,11 @@
           <t>pragya.khanna@lirik.io</t>
         </is>
       </c>
-      <c r="D967" t="inlineStr"/>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
@@ -21674,7 +21706,11 @@
           <t>pragya.parashar@claritusconsulting.com</t>
         </is>
       </c>
-      <c r="D968" t="inlineStr"/>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
@@ -21692,7 +21728,11 @@
           <t>prajeeth.g@winwire.com</t>
         </is>
       </c>
-      <c r="D969" t="inlineStr"/>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
@@ -21710,7 +21750,11 @@
           <t>prajeetha.prasad@thoughtspot.com</t>
         </is>
       </c>
-      <c r="D970" t="inlineStr"/>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
@@ -21728,7 +21772,11 @@
           <t>prakash.b@payoda.com</t>
         </is>
       </c>
-      <c r="D971" t="inlineStr"/>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
@@ -21746,7 +21794,11 @@
           <t>prakashk@newtglobalcorp.com</t>
         </is>
       </c>
-      <c r="D972" t="inlineStr"/>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
@@ -21764,7 +21816,11 @@
           <t>prakashpn@suntecgroup.com</t>
         </is>
       </c>
-      <c r="D973" t="inlineStr"/>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
@@ -21782,7 +21838,11 @@
           <t>prakash.rc@kriyanxw.com</t>
         </is>
       </c>
-      <c r="D974" t="inlineStr"/>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -21860,7 +21860,11 @@
           <t>prakyath.k@verifaya.com</t>
         </is>
       </c>
-      <c r="D975" t="inlineStr"/>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
@@ -21878,7 +21882,11 @@
           <t>pramodh.karumbaiah@trell.co</t>
         </is>
       </c>
-      <c r="D976" t="inlineStr"/>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
@@ -21896,7 +21904,11 @@
           <t>pranab.mishra@criticalriver.com</t>
         </is>
       </c>
-      <c r="D977" t="inlineStr"/>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
@@ -21914,7 +21926,11 @@
           <t>pranali.shinde@featsystems.com</t>
         </is>
       </c>
-      <c r="D978" t="inlineStr"/>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
@@ -21932,7 +21948,11 @@
           <t>pranay@precisiontechcorp.com</t>
         </is>
       </c>
-      <c r="D979" t="inlineStr"/>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
@@ -21950,7 +21970,11 @@
           <t>pranitha@tyfone.com</t>
         </is>
       </c>
-      <c r="D980" t="inlineStr"/>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
@@ -21968,7 +21992,11 @@
           <t>prasaanth.s@ivymobility.com</t>
         </is>
       </c>
-      <c r="D981" t="inlineStr"/>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
@@ -21986,7 +22014,11 @@
           <t>prasad.bagawade@infrasofttech.com</t>
         </is>
       </c>
-      <c r="D982" t="inlineStr"/>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
@@ -22004,7 +22036,11 @@
           <t>prasad_k@abmindia.com</t>
         </is>
       </c>
-      <c r="D983" t="inlineStr"/>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -22058,7 +22058,11 @@
           <t>prasad_narayan@neovasolutions.in</t>
         </is>
       </c>
-      <c r="D984" t="inlineStr"/>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
@@ -22076,7 +22080,11 @@
           <t>prasad_r@preludesys.com</t>
         </is>
       </c>
-      <c r="D985" t="inlineStr"/>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
@@ -22094,7 +22102,11 @@
           <t>prasanna.soparkar@steeplap.com</t>
         </is>
       </c>
-      <c r="D986" t="inlineStr"/>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
@@ -22112,7 +22124,11 @@
           <t>prashant.dubey@techilaservices.com</t>
         </is>
       </c>
-      <c r="D987" t="inlineStr"/>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
@@ -22130,7 +22146,11 @@
           <t>prashant@kljindia.com</t>
         </is>
       </c>
-      <c r="D988" t="inlineStr"/>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
@@ -22148,7 +22168,11 @@
           <t>prashant.parashar@clevertap.com</t>
         </is>
       </c>
-      <c r="D989" t="inlineStr"/>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
@@ -22166,7 +22190,11 @@
           <t>prashant@diverselynx.com</t>
         </is>
       </c>
-      <c r="D990" t="inlineStr"/>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
@@ -22184,7 +22212,11 @@
           <t>prashanth.kulkarni@v2solutions.com</t>
         </is>
       </c>
-      <c r="D991" t="inlineStr"/>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
@@ -22202,7 +22234,11 @@
           <t>prashasti@muvi.com</t>
         </is>
       </c>
-      <c r="D992" t="inlineStr"/>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
@@ -22220,7 +22256,11 @@
           <t>prasheel.pardhe@trantorinc.com</t>
         </is>
       </c>
-      <c r="D993" t="inlineStr"/>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
@@ -22238,7 +22278,11 @@
           <t>prastily@vaisesika.in</t>
         </is>
       </c>
-      <c r="D994" t="inlineStr"/>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
@@ -22256,7 +22300,11 @@
           <t>pratheek.machaya@valentabpo.com</t>
         </is>
       </c>
-      <c r="D995" t="inlineStr"/>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
@@ -22274,7 +22322,11 @@
           <t>prathyusha@5cnetwork.com</t>
         </is>
       </c>
-      <c r="D996" t="inlineStr"/>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
@@ -22292,7 +22344,11 @@
           <t>pratik.m@baazigames.com</t>
         </is>
       </c>
-      <c r="D997" t="inlineStr"/>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
@@ -22310,7 +22366,11 @@
           <t>pratim.purkait@rtns.in</t>
         </is>
       </c>
-      <c r="D998" t="inlineStr"/>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -22388,7 +22388,11 @@
           <t>pratyush.sinha@catalystone.com</t>
         </is>
       </c>
-      <c r="D999" t="inlineStr"/>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
@@ -22406,7 +22410,11 @@
           <t>praveen.gupta@amantyatech.com</t>
         </is>
       </c>
-      <c r="D1000" t="inlineStr"/>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
@@ -22424,7 +22432,11 @@
           <t>pjoseph@suyati.com</t>
         </is>
       </c>
-      <c r="D1001" t="inlineStr"/>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
@@ -22442,7 +22454,11 @@
           <t>praveen@maxval.com</t>
         </is>
       </c>
-      <c r="D1002" t="inlineStr"/>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
@@ -22460,7 +22476,11 @@
           <t>praveen.kunta@incture.com</t>
         </is>
       </c>
-      <c r="D1003" t="inlineStr"/>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
@@ -22478,7 +22498,11 @@
           <t>praveen.nambiar@rigvedtech.com</t>
         </is>
       </c>
-      <c r="D1004" t="inlineStr"/>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
@@ -22496,7 +22520,11 @@
           <t>praveen.r@softpath.net</t>
         </is>
       </c>
-      <c r="D1005" t="inlineStr"/>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
@@ -22514,7 +22542,11 @@
           <t>praveen.singh@xduce.com</t>
         </is>
       </c>
-      <c r="D1006" t="inlineStr"/>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
@@ -22532,7 +22564,11 @@
           <t>praveen.zore@agiliad.com</t>
         </is>
       </c>
-      <c r="D1007" t="inlineStr"/>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
@@ -22550,7 +22586,11 @@
           <t>pravin.kankane@flo-group.com</t>
         </is>
       </c>
-      <c r="D1008" t="inlineStr"/>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
@@ -22568,7 +22608,11 @@
           <t>pravin.subba@tanla.com</t>
         </is>
       </c>
-      <c r="D1009" t="inlineStr"/>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
@@ -22586,7 +22630,11 @@
           <t>preeth.joseph@bridgei2i.com</t>
         </is>
       </c>
-      <c r="D1010" t="inlineStr"/>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
@@ -22604,7 +22652,11 @@
           <t>preetha@frontier.in</t>
         </is>
       </c>
-      <c r="D1011" t="inlineStr"/>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
@@ -22622,7 +22674,11 @@
           <t>preetham.singh@tanla.com</t>
         </is>
       </c>
-      <c r="D1012" t="inlineStr"/>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
@@ -22640,7 +22696,11 @@
           <t>preethy.paul@insemitech.com</t>
         </is>
       </c>
-      <c r="D1013" t="inlineStr"/>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
@@ -22658,7 +22718,11 @@
           <t>preeti.das@tripstack.com</t>
         </is>
       </c>
-      <c r="D1014" t="inlineStr"/>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
@@ -22676,7 +22740,11 @@
           <t>preeti.kalyankar@mosambee.com</t>
         </is>
       </c>
-      <c r="D1015" t="inlineStr"/>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
@@ -22694,7 +22762,11 @@
           <t>pmani@verisys.com</t>
         </is>
       </c>
-      <c r="D1016" t="inlineStr"/>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
@@ -22712,7 +22784,11 @@
           <t>preeti.mathur@eproductivitysoftware.com</t>
         </is>
       </c>
-      <c r="D1017" t="inlineStr"/>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
@@ -22730,7 +22806,11 @@
           <t>preeti.msw@wundermanthompson.com</t>
         </is>
       </c>
-      <c r="D1018" t="inlineStr"/>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
@@ -22748,7 +22828,11 @@
           <t>preeti.phansalkar@clariontech.com</t>
         </is>
       </c>
-      <c r="D1019" t="inlineStr"/>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
@@ -22766,7 +22850,11 @@
           <t>preety@cozentus.com</t>
         </is>
       </c>
-      <c r="D1020" t="inlineStr"/>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
@@ -22784,7 +22872,11 @@
           <t>prem.nair@toshiba-tsip.com</t>
         </is>
       </c>
-      <c r="D1021" t="inlineStr"/>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
@@ -22802,7 +22894,11 @@
           <t>prerna.kohli@cyware.com</t>
         </is>
       </c>
-      <c r="D1022" t="inlineStr"/>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -22916,7 +22916,11 @@
           <t>prince.kumar@innohubtechnologies.com</t>
         </is>
       </c>
-      <c r="D1023" t="inlineStr"/>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
@@ -22934,7 +22938,11 @@
           <t>priscilla.f@mantralabsglobal.com</t>
         </is>
       </c>
-      <c r="D1024" t="inlineStr"/>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
@@ -22952,7 +22960,11 @@
           <t>pritha@near.com</t>
         </is>
       </c>
-      <c r="D1025" t="inlineStr"/>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
@@ -22970,7 +22982,11 @@
           <t>priti.mhatre@zaggle.in</t>
         </is>
       </c>
-      <c r="D1026" t="inlineStr"/>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
@@ -22988,7 +23004,11 @@
           <t>priya.bagla@fullestop.com</t>
         </is>
       </c>
-      <c r="D1027" t="inlineStr"/>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
@@ -23006,7 +23026,11 @@
           <t>priya.bhogineni@yexle.com</t>
         </is>
       </c>
-      <c r="D1028" t="inlineStr"/>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
@@ -23024,7 +23048,11 @@
           <t>priya.malhotra@daffodilsw.com</t>
         </is>
       </c>
-      <c r="D1029" t="inlineStr"/>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
@@ -23042,7 +23070,11 @@
           <t>priya@flexasoft.com</t>
         </is>
       </c>
-      <c r="D1030" t="inlineStr"/>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
@@ -23060,7 +23092,11 @@
           <t>priya@congruentindia.com</t>
         </is>
       </c>
-      <c r="D1031" t="inlineStr"/>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -23114,7 +23114,11 @@
           <t>priya.subramanian@talview.com</t>
         </is>
       </c>
-      <c r="D1032" t="inlineStr"/>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
@@ -23132,7 +23136,11 @@
           <t>priya@jungleegames.com</t>
         </is>
       </c>
-      <c r="D1033" t="inlineStr"/>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
@@ -23150,7 +23158,11 @@
           <t>priya@quartic.ai</t>
         </is>
       </c>
-      <c r="D1034" t="inlineStr"/>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
@@ -23168,7 +23180,11 @@
           <t>priyadarshini@tatacliq.com</t>
         </is>
       </c>
-      <c r="D1035" t="inlineStr"/>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
@@ -23186,7 +23202,11 @@
           <t>priyadarshini.torke@jobsforher.com</t>
         </is>
       </c>
-      <c r="D1036" t="inlineStr"/>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
@@ -23204,7 +23224,11 @@
           <t>priyanka.basak@cbnits.com</t>
         </is>
       </c>
-      <c r="D1037" t="inlineStr"/>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
@@ -23222,7 +23246,11 @@
           <t>priyanka.grover@fifthnote.co</t>
         </is>
       </c>
-      <c r="D1038" t="inlineStr"/>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
@@ -23240,7 +23268,11 @@
           <t>pjaiswal@paktolus.com</t>
         </is>
       </c>
-      <c r="D1039" t="inlineStr"/>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
@@ -23258,7 +23290,11 @@
           <t>priyankam@chimeratechnologies.com</t>
         </is>
       </c>
-      <c r="D1040" t="inlineStr"/>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
@@ -23276,7 +23312,11 @@
           <t>priyanka.priyadarshini@hcl.com</t>
         </is>
       </c>
-      <c r="D1041" t="inlineStr"/>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
@@ -23294,7 +23334,11 @@
           <t>priyanka@freshersworld.com</t>
         </is>
       </c>
-      <c r="D1042" t="inlineStr"/>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
@@ -23312,7 +23356,11 @@
           <t>priyanka.s@decimaltech.com</t>
         </is>
       </c>
-      <c r="D1043" t="inlineStr"/>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
@@ -23330,7 +23378,11 @@
           <t>priyankashu@flock.com</t>
         </is>
       </c>
-      <c r="D1044" t="inlineStr"/>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
@@ -23348,7 +23400,11 @@
           <t>priyom.barooah@kritikalvision.ai</t>
         </is>
       </c>
-      <c r="D1045" t="inlineStr"/>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
@@ -23366,7 +23422,11 @@
           <t>prof.dutt@onebcg.com</t>
         </is>
       </c>
-      <c r="D1046" t="inlineStr"/>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -23444,7 +23444,11 @@
           <t>pronami.borah@travclan.com</t>
         </is>
       </c>
-      <c r="D1047" t="inlineStr"/>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
@@ -23462,7 +23466,11 @@
           <t>puja@affle.com</t>
         </is>
       </c>
-      <c r="D1048" t="inlineStr"/>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
@@ -23480,7 +23488,11 @@
           <t>punitha.n@zucisystems.com</t>
         </is>
       </c>
-      <c r="D1049" t="inlineStr"/>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
@@ -23498,7 +23510,11 @@
           <t>purvap@zenoti.com</t>
         </is>
       </c>
-      <c r="D1050" t="inlineStr"/>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
@@ -23516,7 +23532,11 @@
           <t>pushpendra.y@cynetsystems.com</t>
         </is>
       </c>
-      <c r="D1051" t="inlineStr"/>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
@@ -23534,7 +23554,11 @@
           <t>pushpinder.singh@se2.com</t>
         </is>
       </c>
-      <c r="D1052" t="inlineStr"/>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
@@ -23552,7 +23576,11 @@
           <t>rabi@flobiz.in</t>
         </is>
       </c>
-      <c r="D1053" t="inlineStr"/>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
@@ -23570,7 +23598,11 @@
           <t>radhakrishnak@spanidea.com</t>
         </is>
       </c>
-      <c r="D1054" t="inlineStr"/>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
@@ -23588,7 +23620,11 @@
           <t>r.nair@suntecgroup.com</t>
         </is>
       </c>
-      <c r="D1055" t="inlineStr"/>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
@@ -23606,7 +23642,11 @@
           <t>radhika.boppana@blackstraw.ai</t>
         </is>
       </c>
-      <c r="D1056" t="inlineStr"/>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
@@ -23624,7 +23664,11 @@
           <t>radhika.khurana@impactanalytics.co</t>
         </is>
       </c>
-      <c r="D1057" t="inlineStr"/>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
@@ -23642,7 +23686,11 @@
           <t>raghava.krishna@nslhub.com</t>
         </is>
       </c>
-      <c r="D1058" t="inlineStr"/>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
@@ -23660,7 +23708,11 @@
           <t>raghavendra@syscloud.com</t>
         </is>
       </c>
-      <c r="D1059" t="inlineStr"/>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
@@ -23678,7 +23730,11 @@
           <t>raghavendra@fidelisgroup.in</t>
         </is>
       </c>
-      <c r="D1060" t="inlineStr"/>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
@@ -23696,7 +23752,11 @@
           <t>rgawde@softcell.com</t>
         </is>
       </c>
-      <c r="D1061" t="inlineStr"/>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
@@ -23714,7 +23774,11 @@
           <t>ragini.m@seanergydigital.com</t>
         </is>
       </c>
-      <c r="D1062" t="inlineStr"/>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
@@ -23732,7 +23796,11 @@
           <t>rahul.a@softpath.net</t>
         </is>
       </c>
-      <c r="D1063" t="inlineStr"/>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
@@ -23750,7 +23818,11 @@
           <t>rahul.bansode@digitalf5.com</t>
         </is>
       </c>
-      <c r="D1064" t="inlineStr"/>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
@@ -23768,7 +23840,11 @@
           <t>rahul@netmagicsolutions.com</t>
         </is>
       </c>
-      <c r="D1065" t="inlineStr"/>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
@@ -23786,7 +23862,11 @@
           <t>rahul.inamdar@infracloud.io</t>
         </is>
       </c>
-      <c r="D1066" t="inlineStr"/>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
@@ -23804,7 +23884,11 @@
           <t>rahul.vishawantham@vaave.com</t>
         </is>
       </c>
-      <c r="D1067" t="inlineStr"/>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
@@ -23822,7 +23906,11 @@
           <t>rabubakkar@amrepinspect.com</t>
         </is>
       </c>
-      <c r="D1068" t="inlineStr"/>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
@@ -23840,7 +23928,11 @@
           <t>raj.agarwal@360degreecloud.in</t>
         </is>
       </c>
-      <c r="D1069" t="inlineStr"/>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
@@ -23858,7 +23950,11 @@
           <t>rajbose@avataar.me</t>
         </is>
       </c>
-      <c r="D1070" t="inlineStr"/>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -23972,7 +23972,11 @@
           <t>r.kish@selectsys.com</t>
         </is>
       </c>
-      <c r="D1071" t="inlineStr"/>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -23994,7 +23994,11 @@
           <t>raja.pamidi@nttdata.com</t>
         </is>
       </c>
-      <c r="D1072" t="inlineStr"/>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
@@ -24012,7 +24016,11 @@
           <t>rajagopal@antra.com</t>
         </is>
       </c>
-      <c r="D1073" t="inlineStr"/>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
@@ -24030,7 +24038,11 @@
           <t>rajanip@resilienceitusa.com</t>
         </is>
       </c>
-      <c r="D1074" t="inlineStr"/>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
@@ -24048,7 +24060,11 @@
           <t>rajani.siddhartha@dreamorbit.com</t>
         </is>
       </c>
-      <c r="D1075" t="inlineStr"/>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
@@ -24066,7 +24082,11 @@
           <t>m.rajashree@xangars.com</t>
         </is>
       </c>
-      <c r="D1076" t="inlineStr"/>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
@@ -24084,7 +24104,11 @@
           <t>rajatb@damcogroup.com</t>
         </is>
       </c>
-      <c r="D1077" t="inlineStr"/>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
@@ -24102,7 +24126,11 @@
           <t>rajat.das@ondemandagility.com</t>
         </is>
       </c>
-      <c r="D1078" t="inlineStr"/>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
@@ -24120,7 +24148,11 @@
           <t>rajat.mehra@nxtgen.com</t>
         </is>
       </c>
-      <c r="D1079" t="inlineStr"/>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
@@ -24138,7 +24170,11 @@
           <t>rajeeb@q3tech.com</t>
         </is>
       </c>
-      <c r="D1080" t="inlineStr"/>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
@@ -24156,7 +24192,11 @@
           <t>rajeev.bhardwaj@sunlife.com</t>
         </is>
       </c>
-      <c r="D1081" t="inlineStr"/>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
@@ -24174,7 +24214,11 @@
           <t>rajeev.s@algonomy.com</t>
         </is>
       </c>
-      <c r="D1082" t="inlineStr"/>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
@@ -24192,7 +24236,11 @@
           <t>rsen@medline.com</t>
         </is>
       </c>
-      <c r="D1083" t="inlineStr"/>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
@@ -24210,7 +24258,11 @@
           <t>rajendra.bn@exilant.com</t>
         </is>
       </c>
-      <c r="D1084" t="inlineStr"/>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
@@ -24228,7 +24280,11 @@
           <t>rajeshn@techaffinity.com</t>
         </is>
       </c>
-      <c r="D1085" t="inlineStr"/>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
@@ -24246,7 +24302,11 @@
           <t>rajesh@dremio.com</t>
         </is>
       </c>
-      <c r="D1086" t="inlineStr"/>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
@@ -24264,7 +24324,11 @@
           <t>rajesh.babu@softobiz.com</t>
         </is>
       </c>
-      <c r="D1087" t="inlineStr"/>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
@@ -24282,7 +24346,11 @@
           <t>rajeshb@coffeebeans.io</t>
         </is>
       </c>
-      <c r="D1088" t="inlineStr"/>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
@@ -24300,7 +24368,11 @@
           <t>rajesh.kethepalle@electrifai.net</t>
         </is>
       </c>
-      <c r="D1089" t="inlineStr"/>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
@@ -24318,7 +24390,11 @@
           <t>rajeshm@damcogroup.com</t>
         </is>
       </c>
-      <c r="D1090" t="inlineStr"/>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
@@ -24336,7 +24412,11 @@
           <t>rajesh@fissionlabs.com</t>
         </is>
       </c>
-      <c r="D1091" t="inlineStr"/>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
@@ -24354,7 +24434,11 @@
           <t>rajesh.yadav@gstn.org.in</t>
         </is>
       </c>
-      <c r="D1092" t="inlineStr"/>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
@@ -24372,7 +24456,11 @@
           <t>rajitha.jaffer@jmrinfotech.com</t>
         </is>
       </c>
-      <c r="D1093" t="inlineStr"/>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
@@ -24390,7 +24478,11 @@
           <t>rkumar@cendyn.com</t>
         </is>
       </c>
-      <c r="D1094" t="inlineStr"/>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
@@ -24408,7 +24500,11 @@
           <t>rajneesh.malik@mindtickle.com</t>
         </is>
       </c>
-      <c r="D1095" t="inlineStr"/>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -24522,7 +24522,11 @@
           <t>rajni@growexx.com</t>
         </is>
       </c>
-      <c r="D1096" t="inlineStr"/>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
@@ -24540,7 +24544,11 @@
           <t>rajni.noronha@cignex.com</t>
         </is>
       </c>
-      <c r="D1097" t="inlineStr"/>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
@@ -24558,7 +24566,11 @@
           <t>rajni.singh@indinnovation.com</t>
         </is>
       </c>
-      <c r="D1098" t="inlineStr"/>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
@@ -24576,7 +24588,11 @@
           <t>rajsekhar.dangeti@zensark.com</t>
         </is>
       </c>
-      <c r="D1099" t="inlineStr"/>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
@@ -24594,7 +24610,11 @@
           <t>raju.vatsavayi@nsight-inc.com</t>
         </is>
       </c>
-      <c r="D1100" t="inlineStr"/>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
@@ -24612,7 +24632,11 @@
           <t>rajyashree@technodysis.com</t>
         </is>
       </c>
-      <c r="D1101" t="inlineStr"/>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
@@ -24630,7 +24654,11 @@
           <t>rakesh.arora@skilrock.com</t>
         </is>
       </c>
-      <c r="D1102" t="inlineStr"/>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
@@ -24648,7 +24676,11 @@
           <t>rakesh.arora@sugaldamani.com</t>
         </is>
       </c>
-      <c r="D1103" t="inlineStr"/>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
@@ -24666,7 +24698,11 @@
           <t>rakesh@taazaa.com</t>
         </is>
       </c>
-      <c r="D1104" t="inlineStr"/>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
@@ -24684,7 +24720,11 @@
           <t>rakesh.badam@tomiaglobal.com</t>
         </is>
       </c>
-      <c r="D1105" t="inlineStr"/>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
@@ -24702,7 +24742,11 @@
           <t>rakesh.e@63moons.com</t>
         </is>
       </c>
-      <c r="D1106" t="inlineStr"/>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
@@ -24720,7 +24764,11 @@
           <t>rakesh.kumar@anetcorp.com</t>
         </is>
       </c>
-      <c r="D1107" t="inlineStr"/>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
@@ -24738,7 +24786,11 @@
           <t>rakesh@mergenit.com</t>
         </is>
       </c>
-      <c r="D1108" t="inlineStr"/>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
@@ -24756,7 +24808,11 @@
           <t>rakesh.vishwakarma@tejora.com</t>
         </is>
       </c>
-      <c r="D1109" t="inlineStr"/>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
@@ -24774,7 +24830,11 @@
           <t>rakshita@easyeat.ai</t>
         </is>
       </c>
-      <c r="D1110" t="inlineStr"/>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
@@ -24792,7 +24852,11 @@
           <t>ram.r@kairostech.com</t>
         </is>
       </c>
-      <c r="D1111" t="inlineStr"/>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
@@ -24810,7 +24874,11 @@
           <t>ram.varadamoorthy@ducenit.com</t>
         </is>
       </c>
-      <c r="D1112" t="inlineStr"/>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
@@ -24828,7 +24896,11 @@
           <t>rama.c@soroco.com</t>
         </is>
       </c>
-      <c r="D1113" t="inlineStr"/>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
@@ -24846,7 +24918,11 @@
           <t>ramakrishnac@msrcosmos.com</t>
         </is>
       </c>
-      <c r="D1114" t="inlineStr"/>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
@@ -24864,7 +24940,11 @@
           <t>ramakrishna.jampala@paradigmit.com</t>
         </is>
       </c>
-      <c r="D1115" t="inlineStr"/>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
@@ -24882,7 +24962,11 @@
           <t>rtsk@seec.com</t>
         </is>
       </c>
-      <c r="D1116" t="inlineStr"/>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
@@ -24900,7 +24984,11 @@
           <t>ramani@hirect.in</t>
         </is>
       </c>
-      <c r="D1117" t="inlineStr"/>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
@@ -24918,7 +25006,11 @@
           <t>ramanjit.goswami@inadev.com</t>
         </is>
       </c>
-      <c r="D1118" t="inlineStr"/>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
@@ -24936,7 +25028,11 @@
           <t>ramanujam.cs@ifocussystec.com</t>
         </is>
       </c>
-      <c r="D1119" t="inlineStr"/>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -25050,7 +25050,11 @@
           <t>ramaprasad.baleguli@v2solutions.com</t>
         </is>
       </c>
-      <c r="D1120" t="inlineStr"/>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
@@ -25068,7 +25072,11 @@
           <t>head.hr@abmindia.com</t>
         </is>
       </c>
-      <c r="D1121" t="inlineStr"/>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
@@ -25086,7 +25094,11 @@
           <t>rmantana@evoketechnologies.com</t>
         </is>
       </c>
-      <c r="D1122" t="inlineStr"/>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
@@ -25104,7 +25116,11 @@
           <t>ramesh.parepalli@purviewservices.com</t>
         </is>
       </c>
-      <c r="D1123" t="inlineStr"/>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
@@ -25122,7 +25138,11 @@
           <t>ramesh.talwar@crmnext.com</t>
         </is>
       </c>
-      <c r="D1124" t="inlineStr"/>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
@@ -25140,7 +25160,11 @@
           <t>ramkrishna.sahu@ceptes.com</t>
         </is>
       </c>
-      <c r="D1125" t="inlineStr"/>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
@@ -25158,7 +25182,11 @@
           <t>eradi.ramya@aujas.com</t>
         </is>
       </c>
-      <c r="D1126" t="inlineStr"/>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
@@ -25176,7 +25204,11 @@
           <t>ramya.hv@profinch.com</t>
         </is>
       </c>
-      <c r="D1127" t="inlineStr"/>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
@@ -25194,7 +25226,11 @@
           <t>ramya.menon@edifecs.com</t>
         </is>
       </c>
-      <c r="D1128" t="inlineStr"/>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -25248,7 +25248,11 @@
           <t>ramya.ramachandran@cloudsek.com</t>
         </is>
       </c>
-      <c r="D1129" t="inlineStr"/>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
@@ -25266,7 +25270,11 @@
           <t>ramya.s@greyorange.com</t>
         </is>
       </c>
-      <c r="D1130" t="inlineStr"/>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
@@ -25284,7 +25292,11 @@
           <t>ramya.venkatesh@profinch.com</t>
         </is>
       </c>
-      <c r="D1131" t="inlineStr"/>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
@@ -25302,7 +25314,11 @@
           <t>rana.bose@emds.com</t>
         </is>
       </c>
-      <c r="D1132" t="inlineStr"/>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
@@ -25320,7 +25336,11 @@
           <t>ranjan.hooda@rpsconsulting.in</t>
         </is>
       </c>
-      <c r="D1133" t="inlineStr"/>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
@@ -25338,7 +25358,11 @@
           <t>ranjana@finessedirect.com</t>
         </is>
       </c>
-      <c r="D1134" t="inlineStr"/>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
@@ -25356,7 +25380,11 @@
           <t>ranjani.sunkara@incture.com</t>
         </is>
       </c>
-      <c r="D1135" t="inlineStr"/>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
@@ -25374,7 +25402,11 @@
           <t>ranjeeta.d@iksula.com</t>
         </is>
       </c>
-      <c r="D1136" t="inlineStr"/>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
@@ -25392,7 +25424,11 @@
           <t>ranjitd@spancobpo.com</t>
         </is>
       </c>
-      <c r="D1137" t="inlineStr"/>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
@@ -25410,7 +25446,11 @@
           <t>ranjith.vp@aujas.com</t>
         </is>
       </c>
-      <c r="D1138" t="inlineStr"/>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
@@ -25428,7 +25468,11 @@
           <t>ranjitha.s@healthasyst.com</t>
         </is>
       </c>
-      <c r="D1139" t="inlineStr"/>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
@@ -25446,7 +25490,11 @@
           <t>ranju@eateam.com</t>
         </is>
       </c>
-      <c r="D1140" t="inlineStr"/>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
@@ -25464,7 +25512,11 @@
           <t>rashmi.chauhan@rategain.com</t>
         </is>
       </c>
-      <c r="D1141" t="inlineStr"/>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
@@ -25482,7 +25534,11 @@
           <t>rashmi.george@niveussolutions.com</t>
         </is>
       </c>
-      <c r="D1142" t="inlineStr"/>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
@@ -25500,7 +25556,11 @@
           <t>rashmi.gupte@wisdmlabs.com</t>
         </is>
       </c>
-      <c r="D1143" t="inlineStr"/>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -25578,7 +25578,11 @@
           <t>rashmi.taksande@softdel.com</t>
         </is>
       </c>
-      <c r="D1144" t="inlineStr"/>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
@@ -25596,7 +25600,11 @@
           <t>rashmita.pradhan@teklink.com</t>
         </is>
       </c>
-      <c r="D1145" t="inlineStr"/>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
@@ -25614,7 +25622,11 @@
           <t>rashmme.eshwar@datacore.com</t>
         </is>
       </c>
-      <c r="D1146" t="inlineStr"/>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
@@ -25632,7 +25644,11 @@
           <t>ratan.dalal@global-csg.com</t>
         </is>
       </c>
-      <c r="D1147" t="inlineStr"/>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
@@ -25650,7 +25666,11 @@
           <t>ratika.mirji@neviton.com</t>
         </is>
       </c>
-      <c r="D1148" t="inlineStr"/>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
@@ -25668,7 +25688,11 @@
           <t>ratish@maintec.com</t>
         </is>
       </c>
-      <c r="D1149" t="inlineStr"/>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
@@ -25686,7 +25710,11 @@
           <t>ratish.r@iantindia.com</t>
         </is>
       </c>
-      <c r="D1150" t="inlineStr"/>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
@@ -25704,7 +25732,11 @@
           <t>ravdeep.singh@sourcefuse.com</t>
         </is>
       </c>
-      <c r="D1151" t="inlineStr"/>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
@@ -25722,7 +25754,11 @@
           <t>raveendra.datla@smartims.com</t>
         </is>
       </c>
-      <c r="D1152" t="inlineStr"/>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -25776,7 +25776,11 @@
           <t>ravi.bhushan@techilaservices.com</t>
         </is>
       </c>
-      <c r="D1153" t="inlineStr"/>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
@@ -25794,7 +25798,11 @@
           <t>ravi.devara@tammina.com</t>
         </is>
       </c>
-      <c r="D1154" t="inlineStr"/>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
@@ -25812,7 +25820,11 @@
           <t>ravi.gurunathan@ivalue.co.in</t>
         </is>
       </c>
-      <c r="D1155" t="inlineStr"/>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
@@ -25830,7 +25842,11 @@
           <t>ravi.k@crmit.com</t>
         </is>
       </c>
-      <c r="D1156" t="inlineStr"/>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
@@ -25848,7 +25864,11 @@
           <t>ravi.kasinadhuni@crmit.com</t>
         </is>
       </c>
-      <c r="D1157" t="inlineStr"/>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
@@ -25866,7 +25886,11 @@
           <t>ravi.kuchampudi@zenq.com</t>
         </is>
       </c>
-      <c r="D1158" t="inlineStr"/>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
@@ -25884,7 +25908,11 @@
           <t>ravi.kumar@ample.co.in</t>
         </is>
       </c>
-      <c r="D1159" t="inlineStr"/>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
@@ -25902,7 +25930,11 @@
           <t>rkumar@saiconinc.com</t>
         </is>
       </c>
-      <c r="D1160" t="inlineStr"/>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
@@ -25920,7 +25952,11 @@
           <t>ravi.mourya@waisl.in</t>
         </is>
       </c>
-      <c r="D1161" t="inlineStr"/>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
@@ -25938,7 +25974,11 @@
           <t>ravi.shankar@crmit.com</t>
         </is>
       </c>
-      <c r="D1162" t="inlineStr"/>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
@@ -25956,7 +25996,11 @@
           <t>ravi@olivetech.com</t>
         </is>
       </c>
-      <c r="D1163" t="inlineStr"/>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
@@ -25974,7 +26018,11 @@
           <t>ravi.vattikota@itelligencegroup.com</t>
         </is>
       </c>
-      <c r="D1164" t="inlineStr"/>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
@@ -25992,7 +26040,11 @@
           <t>ravichandran@spantechnologyservices.com</t>
         </is>
       </c>
-      <c r="D1165" t="inlineStr"/>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
@@ -26010,7 +26062,11 @@
           <t>ravikumarm@aditiconsulting.com</t>
         </is>
       </c>
-      <c r="D1166" t="inlineStr"/>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
@@ -26028,7 +26084,11 @@
           <t>ravindra.dandekar@myglamm.com</t>
         </is>
       </c>
-      <c r="D1167" t="inlineStr"/>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -26106,7 +26106,11 @@
           <t>ravindra.musunuru@prowesssoft.com</t>
         </is>
       </c>
-      <c r="D1168" t="inlineStr"/>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
@@ -26124,7 +26128,11 @@
           <t>ravisankar.velidi@increff.com</t>
         </is>
       </c>
-      <c r="D1169" t="inlineStr"/>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
@@ -26142,7 +26150,11 @@
           <t>ravish.chadha@niyuj.com</t>
         </is>
       </c>
-      <c r="D1170" t="inlineStr"/>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
@@ -26160,7 +26172,11 @@
           <t>ravishanker.kannan@solverminds.com</t>
         </is>
       </c>
-      <c r="D1171" t="inlineStr"/>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
@@ -26178,7 +26194,11 @@
           <t>ravitha.devasenapathy@epikindifi.com</t>
         </is>
       </c>
-      <c r="D1172" t="inlineStr"/>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
@@ -26196,7 +26216,11 @@
           <t>rkaur@primusglobal.com</t>
         </is>
       </c>
-      <c r="D1173" t="inlineStr"/>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
@@ -26214,7 +26238,11 @@
           <t>ralbro@stand8.io</t>
         </is>
       </c>
-      <c r="D1174" t="inlineStr"/>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
@@ -26232,7 +26260,11 @@
           <t>reddy@mantratechno.com</t>
         </is>
       </c>
-      <c r="D1175" t="inlineStr"/>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
@@ -26250,7 +26282,11 @@
           <t>reena.bajaj@solverminds.com</t>
         </is>
       </c>
-      <c r="D1176" t="inlineStr"/>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -26304,7 +26304,11 @@
           <t>reena@matellio.com</t>
         </is>
       </c>
-      <c r="D1177" t="inlineStr"/>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
@@ -26322,7 +26326,11 @@
           <t>reena.v@adani.com</t>
         </is>
       </c>
-      <c r="D1178" t="inlineStr"/>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
@@ -26340,7 +26348,11 @@
           <t>reenaa.s@63moons.com</t>
         </is>
       </c>
-      <c r="D1179" t="inlineStr"/>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
@@ -26358,7 +26370,11 @@
           <t>rehan.abdi@kiwitech.com</t>
         </is>
       </c>
-      <c r="D1180" t="inlineStr"/>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
@@ -26376,7 +26392,11 @@
           <t>rehana.inamdar@smarteinc.com</t>
         </is>
       </c>
-      <c r="D1181" t="inlineStr"/>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
@@ -26394,7 +26414,11 @@
           <t>rekha.nair@navis.com</t>
         </is>
       </c>
-      <c r="D1182" t="inlineStr"/>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
@@ -26412,7 +26436,11 @@
           <t>rekhap@codeforce.com</t>
         </is>
       </c>
-      <c r="D1183" t="inlineStr"/>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
@@ -26430,7 +26458,11 @@
           <t>remi.vaz@sureprep.com</t>
         </is>
       </c>
-      <c r="D1184" t="inlineStr"/>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
@@ -26448,7 +26480,11 @@
           <t>remisa.dhar@percipere.co</t>
         </is>
       </c>
-      <c r="D1185" t="inlineStr"/>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
@@ -26466,7 +26502,11 @@
           <t>rena.so@endurance.com</t>
         </is>
       </c>
-      <c r="D1186" t="inlineStr"/>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
@@ -26484,7 +26524,11 @@
           <t>rency.hakani@manektech.com</t>
         </is>
       </c>
-      <c r="D1187" t="inlineStr"/>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
@@ -26502,7 +26546,11 @@
           <t>renju.nithin@bridge-global.com</t>
         </is>
       </c>
-      <c r="D1188" t="inlineStr"/>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
@@ -26520,7 +26568,11 @@
           <t>renu.srivastava@agdata.com</t>
         </is>
       </c>
-      <c r="D1189" t="inlineStr"/>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
@@ -26538,7 +26590,11 @@
           <t>reshma.bopanna@girmiti.com</t>
         </is>
       </c>
-      <c r="D1190" t="inlineStr"/>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
@@ -26556,7 +26612,11 @@
           <t>reshma.mohan@gemini-us.com</t>
         </is>
       </c>
-      <c r="D1191" t="inlineStr"/>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
@@ -26574,7 +26634,11 @@
           <t>revathi.venkatesh@ibridgellc.com</t>
         </is>
       </c>
-      <c r="D1192" t="inlineStr"/>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
@@ -26592,7 +26656,11 @@
           <t>revathy.reddy@glu.com</t>
         </is>
       </c>
-      <c r="D1193" t="inlineStr"/>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
@@ -26610,7 +26678,11 @@
           <t>richa.pande@inatech.com</t>
         </is>
       </c>
-      <c r="D1194" t="inlineStr"/>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
@@ -26628,7 +26700,11 @@
           <t>joseph@purpletalk.com</t>
         </is>
       </c>
-      <c r="D1195" t="inlineStr"/>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
@@ -26646,7 +26722,11 @@
           <t>ridhimag@pharmarack.com</t>
         </is>
       </c>
-      <c r="D1196" t="inlineStr"/>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
@@ -26664,7 +26744,11 @@
           <t>rijil.kannoth@infobelt.com</t>
         </is>
       </c>
-      <c r="D1197" t="inlineStr"/>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
@@ -26682,7 +26766,11 @@
           <t>rima@maropost.com</t>
         </is>
       </c>
-      <c r="D1198" t="inlineStr"/>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
@@ -26700,7 +26788,11 @@
           <t>rkukreja@pelican.ai</t>
         </is>
       </c>
-      <c r="D1199" t="inlineStr"/>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
@@ -26718,7 +26810,11 @@
           <t>rinki.goel@hevodata.com</t>
         </is>
       </c>
-      <c r="D1200" t="inlineStr"/>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -26832,7 +26832,11 @@
           <t>rinkuc@lumel.com</t>
         </is>
       </c>
-      <c r="D1201" t="inlineStr"/>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
@@ -26850,7 +26854,11 @@
           <t>rishabhkalra@cetpainfotech.com</t>
         </is>
       </c>
-      <c r="D1202" t="inlineStr"/>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
@@ -26868,7 +26876,11 @@
           <t>rishabh.jain@angara.com</t>
         </is>
       </c>
-      <c r="D1203" t="inlineStr"/>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
@@ -26886,7 +26898,11 @@
           <t>radvani@thegoldensource.com</t>
         </is>
       </c>
-      <c r="D1204" t="inlineStr"/>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
@@ -26904,7 +26920,11 @@
           <t>rjatana@docmation.com</t>
         </is>
       </c>
-      <c r="D1205" t="inlineStr"/>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
@@ -26922,7 +26942,11 @@
           <t>ritika.jha@codelogicx.com</t>
         </is>
       </c>
-      <c r="D1206" t="inlineStr"/>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
@@ -26940,7 +26964,11 @@
           <t>ritika.malhotra@dotpe.in</t>
         </is>
       </c>
-      <c r="D1207" t="inlineStr"/>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
@@ -26958,7 +26986,11 @@
           <t>ritika.naithani@infollion.com</t>
         </is>
       </c>
-      <c r="D1208" t="inlineStr"/>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
@@ -26976,7 +27008,11 @@
           <t>ritu.malhotra@zemosolabs.com</t>
         </is>
       </c>
-      <c r="D1209" t="inlineStr"/>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -27030,7 +27030,11 @@
           <t>robin@burgeonits.net</t>
         </is>
       </c>
-      <c r="D1210" t="inlineStr"/>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
@@ -27048,7 +27052,11 @@
           <t>robin.massey@fivesdigital.com</t>
         </is>
       </c>
-      <c r="D1211" t="inlineStr"/>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
@@ -27066,7 +27074,11 @@
           <t>robin.thomas@ecsfin.com</t>
         </is>
       </c>
-      <c r="D1212" t="inlineStr"/>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
@@ -27084,7 +27096,11 @@
           <t>rohini@innobox.com</t>
         </is>
       </c>
-      <c r="D1213" t="inlineStr"/>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
@@ -27102,7 +27118,11 @@
           <t>rohini.radhakrishnan@ideas2it.com</t>
         </is>
       </c>
-      <c r="D1214" t="inlineStr"/>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1215">
       <c r="A1215" t="inlineStr">
@@ -27120,7 +27140,11 @@
           <t>rohini.rai@taazaa.com</t>
         </is>
       </c>
-      <c r="D1215" t="inlineStr"/>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
@@ -27138,7 +27162,11 @@
           <t>rohiniw@nitorinfotech.com</t>
         </is>
       </c>
-      <c r="D1216" t="inlineStr"/>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
@@ -27156,7 +27184,11 @@
           <t>rohit.jain@kalelogistics.com</t>
         </is>
       </c>
-      <c r="D1217" t="inlineStr"/>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
@@ -27174,7 +27206,11 @@
           <t>rohit@mindpooltech.com</t>
         </is>
       </c>
-      <c r="D1218" t="inlineStr"/>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
@@ -27192,7 +27228,11 @@
           <t>rohit.minton@hpiinc.com</t>
         </is>
       </c>
-      <c r="D1219" t="inlineStr"/>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
@@ -27210,7 +27250,11 @@
           <t>rohit.singh@blucognition.ai</t>
         </is>
       </c>
-      <c r="D1220" t="inlineStr"/>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
@@ -27228,7 +27272,11 @@
           <t>rsingh@issquaredinc.com</t>
         </is>
       </c>
-      <c r="D1221" t="inlineStr"/>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
@@ -27246,7 +27294,11 @@
           <t>roli.singh@vfislk.com</t>
         </is>
       </c>
-      <c r="D1222" t="inlineStr"/>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1223">
       <c r="A1223" t="inlineStr">
@@ -27264,7 +27316,11 @@
           <t>roohi.syeda@forecastera.com</t>
         </is>
       </c>
-      <c r="D1223" t="inlineStr"/>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1224">
       <c r="A1224" t="inlineStr">
@@ -27282,7 +27338,11 @@
           <t>roopa.g@aujas.com</t>
         </is>
       </c>
-      <c r="D1224" t="inlineStr"/>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
@@ -27300,7 +27360,11 @@
           <t>roopa.rajesh@bobcares.com</t>
         </is>
       </c>
-      <c r="D1225" t="inlineStr"/>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
@@ -27318,7 +27382,11 @@
           <t>roopali@aitglobalinc.com</t>
         </is>
       </c>
-      <c r="D1226" t="inlineStr"/>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
@@ -27336,7 +27404,11 @@
           <t>nair.roshan@tcs.com</t>
         </is>
       </c>
-      <c r="D1227" t="inlineStr"/>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
@@ -27354,7 +27426,11 @@
           <t>roshan.thomas@ivldsp.com</t>
         </is>
       </c>
-      <c r="D1228" t="inlineStr"/>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
@@ -27372,7 +27448,11 @@
           <t>roshni.j@netenrich.com</t>
         </is>
       </c>
-      <c r="D1229" t="inlineStr"/>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
@@ -27390,7 +27470,11 @@
           <t>roshni.s@apty.io</t>
         </is>
       </c>
-      <c r="D1230" t="inlineStr"/>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
@@ -27408,7 +27492,11 @@
           <t>rosy.mitra@altiusdata.com</t>
         </is>
       </c>
-      <c r="D1231" t="inlineStr"/>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
@@ -27426,7 +27514,11 @@
           <t>roy.mathew@aqmtechnologies.com</t>
         </is>
       </c>
-      <c r="D1232" t="inlineStr"/>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
@@ -27444,7 +27536,11 @@
           <t>roystone@accubits.com</t>
         </is>
       </c>
-      <c r="D1233" t="inlineStr"/>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -27558,7 +27558,11 @@
           <t>ruby.baksi@harbingergroup.com</t>
         </is>
       </c>
-      <c r="D1234" t="inlineStr"/>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
@@ -27576,7 +27580,11 @@
           <t>ruchi@clearbit.com</t>
         </is>
       </c>
-      <c r="D1235" t="inlineStr"/>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
@@ -27594,7 +27602,11 @@
           <t>ruchi.batra@beetel.in</t>
         </is>
       </c>
-      <c r="D1236" t="inlineStr"/>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
@@ -27612,7 +27624,11 @@
           <t>ruchi.bhayani@neutrinotechsystems.com</t>
         </is>
       </c>
-      <c r="D1237" t="inlineStr"/>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
@@ -27630,7 +27646,11 @@
           <t>ruchi@prodexnet.com</t>
         </is>
       </c>
-      <c r="D1238" t="inlineStr"/>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
@@ -27648,7 +27668,11 @@
           <t>ruchi.jain@lighthouseindia.com</t>
         </is>
       </c>
-      <c r="D1239" t="inlineStr"/>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
@@ -27666,7 +27690,11 @@
           <t>ruchi.mago@orange.com</t>
         </is>
       </c>
-      <c r="D1240" t="inlineStr"/>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
@@ -27684,7 +27712,11 @@
           <t>ruchi@headspin.io</t>
         </is>
       </c>
-      <c r="D1241" t="inlineStr"/>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
@@ -27702,7 +27734,11 @@
           <t>ruchika@rooter.io</t>
         </is>
       </c>
-      <c r="D1242" t="inlineStr"/>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
@@ -27720,7 +27756,11 @@
           <t>rkohli@tata.com</t>
         </is>
       </c>
-      <c r="D1243" t="inlineStr"/>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
@@ -27738,7 +27778,11 @@
           <t>ruchika.sawhney@cometchat.com</t>
         </is>
       </c>
-      <c r="D1244" t="inlineStr"/>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
@@ -27756,7 +27800,11 @@
           <t>ruchira.g@greyorange.com</t>
         </is>
       </c>
-      <c r="D1245" t="inlineStr"/>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
@@ -27774,7 +27822,11 @@
           <t>rupab@zenoti.com</t>
         </is>
       </c>
-      <c r="D1246" t="inlineStr"/>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
@@ -27792,7 +27844,11 @@
           <t>rbagaddeo@microproindia.com</t>
         </is>
       </c>
-      <c r="D1247" t="inlineStr"/>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
@@ -27810,7 +27866,11 @@
           <t>rupali.veerkar@bitwiseglobal.com</t>
         </is>
       </c>
-      <c r="D1248" t="inlineStr"/>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1249">
       <c r="A1249" t="inlineStr">
@@ -27828,7 +27888,11 @@
           <t>rushikesh.rajendra@thegatewaycorp.com</t>
         </is>
       </c>
-      <c r="D1249" t="inlineStr"/>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
@@ -27846,7 +27910,11 @@
           <t>rustom@1eq.com</t>
         </is>
       </c>
-      <c r="D1250" t="inlineStr"/>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
@@ -27864,7 +27932,11 @@
           <t>sabina.juvekar@cloudaction.com</t>
         </is>
       </c>
-      <c r="D1251" t="inlineStr"/>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
@@ -27882,7 +27954,11 @@
           <t>sacchin.kalkal@vertexglobalservices.com</t>
         </is>
       </c>
-      <c r="D1252" t="inlineStr"/>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1253">
       <c r="A1253" t="inlineStr">
@@ -27900,7 +27976,11 @@
           <t>sachin.girolla@triarqhealth.com</t>
         </is>
       </c>
-      <c r="D1253" t="inlineStr"/>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1254">
       <c r="A1254" t="inlineStr">
@@ -27918,7 +27998,11 @@
           <t>sadi.hussain@simpplr.com</t>
         </is>
       </c>
-      <c r="D1254" t="inlineStr"/>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1255">
       <c r="A1255" t="inlineStr">
@@ -27936,7 +28020,11 @@
           <t>sagar.arondekar@joshsoftware.com</t>
         </is>
       </c>
-      <c r="D1255" t="inlineStr"/>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
@@ -27954,7 +28042,11 @@
           <t>sagorika.s@insync.co.in</t>
         </is>
       </c>
-      <c r="D1256" t="inlineStr"/>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1257">
       <c r="A1257" t="inlineStr">
@@ -27972,7 +28064,11 @@
           <t>sahana@tecplix.com</t>
         </is>
       </c>
-      <c r="D1257" t="inlineStr"/>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -28086,7 +28086,11 @@
           <t>sahil.sharma@rategain.com</t>
         </is>
       </c>
-      <c r="D1258" t="inlineStr"/>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
@@ -28104,7 +28108,11 @@
           <t>sai.b@terasoftware.com</t>
         </is>
       </c>
-      <c r="D1259" t="inlineStr"/>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
@@ -28122,7 +28130,11 @@
           <t>sai.t@saranshinc.com</t>
         </is>
       </c>
-      <c r="D1260" t="inlineStr"/>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
@@ -28140,7 +28152,11 @@
           <t>ssaranu@dataeconomy.io</t>
         </is>
       </c>
-      <c r="D1261" t="inlineStr"/>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
@@ -28158,7 +28174,11 @@
           <t>sailyv@futurismtechnologies.com</t>
         </is>
       </c>
-      <c r="D1262" t="inlineStr"/>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
@@ -28176,7 +28196,11 @@
           <t>sajani@i95dev.com</t>
         </is>
       </c>
-      <c r="D1263" t="inlineStr"/>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
@@ -28194,7 +28218,11 @@
           <t>sajitha.nair@antra.com</t>
         </is>
       </c>
-      <c r="D1264" t="inlineStr"/>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
@@ -28212,7 +28240,11 @@
           <t>sakshia@winjit.com</t>
         </is>
       </c>
-      <c r="D1265" t="inlineStr"/>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
@@ -28230,7 +28262,11 @@
           <t>sakshi.agrawal@solacetechnologies.co.in</t>
         </is>
       </c>
-      <c r="D1266" t="inlineStr"/>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
@@ -28248,7 +28284,11 @@
           <t>sakshi.goyal@mtxb2b.com</t>
         </is>
       </c>
-      <c r="D1267" t="inlineStr"/>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
@@ -28266,7 +28306,11 @@
           <t>sakshi.themaskar@ceinsys.com</t>
         </is>
       </c>
-      <c r="D1268" t="inlineStr"/>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
@@ -28284,7 +28328,11 @@
           <t>smanohar@cdcsoftware.com</t>
         </is>
       </c>
-      <c r="D1269" t="inlineStr"/>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
@@ -28302,7 +28350,11 @@
           <t>samathar@ideyalabs.com</t>
         </is>
       </c>
-      <c r="D1270" t="inlineStr"/>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
@@ -28320,7 +28372,11 @@
           <t>sameer.deo@riaadvisory.com</t>
         </is>
       </c>
-      <c r="D1271" t="inlineStr"/>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
@@ -28338,7 +28394,11 @@
           <t>sameer.jadhav@tavisca.com</t>
         </is>
       </c>
-      <c r="D1272" t="inlineStr"/>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
@@ -28356,7 +28416,11 @@
           <t>sameer.kumar@equifax.com</t>
         </is>
       </c>
-      <c r="D1273" t="inlineStr"/>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
@@ -28374,7 +28438,11 @@
           <t>ssamant@omnicogroup.com</t>
         </is>
       </c>
-      <c r="D1274" t="inlineStr"/>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
@@ -28392,7 +28460,11 @@
           <t>sameera.chowdry@brainly.com</t>
         </is>
       </c>
-      <c r="D1275" t="inlineStr"/>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1276">
       <c r="A1276" t="inlineStr">
@@ -28410,7 +28482,11 @@
           <t>samidha.varadkar@63moons.com</t>
         </is>
       </c>
-      <c r="D1276" t="inlineStr"/>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1277">
       <c r="A1277" t="inlineStr">
@@ -28428,7 +28504,11 @@
           <t>samir.dhond@ittiam.com</t>
         </is>
       </c>
-      <c r="D1277" t="inlineStr"/>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
@@ -28446,7 +28526,11 @@
           <t>samir.mehta@skill-mine.com</t>
         </is>
       </c>
-      <c r="D1278" t="inlineStr"/>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
@@ -28464,7 +28548,11 @@
           <t>sanchari@polygon.technology</t>
         </is>
       </c>
-      <c r="D1279" t="inlineStr"/>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
@@ -28482,7 +28570,11 @@
           <t>sanchis@fiftyfivetech.io</t>
         </is>
       </c>
-      <c r="D1280" t="inlineStr"/>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
@@ -28500,7 +28592,11 @@
           <t>sanchita.chakraborty@assetanalytix.com</t>
         </is>
       </c>
-      <c r="D1281" t="inlineStr"/>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -28614,7 +28614,11 @@
           <t>adops@phoenixsoftwares.in</t>
         </is>
       </c>
-      <c r="D1282" t="inlineStr"/>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
@@ -28632,7 +28636,11 @@
           <t>snair@catchpoint.com</t>
         </is>
       </c>
-      <c r="D1283" t="inlineStr"/>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
@@ -28650,7 +28658,11 @@
           <t>sandhya@singsys.com</t>
         </is>
       </c>
-      <c r="D1284" t="inlineStr"/>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
@@ -28668,7 +28680,11 @@
           <t>sandipb@prdxn.com</t>
         </is>
       </c>
-      <c r="D1285" t="inlineStr"/>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
@@ -28686,7 +28702,11 @@
           <t>sandip.raj@cheersin.com</t>
         </is>
       </c>
-      <c r="D1286" t="inlineStr"/>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
@@ -28704,7 +28724,11 @@
           <t>sandipan.kar@thegatewaycorp.com</t>
         </is>
       </c>
-      <c r="D1287" t="inlineStr"/>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
@@ -28722,7 +28746,11 @@
           <t>sangeeta.tandon@ionidea.com</t>
         </is>
       </c>
-      <c r="D1288" t="inlineStr"/>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
@@ -28740,7 +28768,11 @@
           <t>sangeethab@sidgs.com</t>
         </is>
       </c>
-      <c r="D1289" t="inlineStr"/>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
@@ -28758,7 +28790,11 @@
           <t>sangeetha@focussoftnet.com</t>
         </is>
       </c>
-      <c r="D1290" t="inlineStr"/>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -28812,7 +28812,11 @@
           <t>sroy@aapnainfotech.com</t>
         </is>
       </c>
-      <c r="D1291" t="inlineStr"/>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
@@ -28830,7 +28834,11 @@
           <t>sangita.nair@buyerforesight.com</t>
         </is>
       </c>
-      <c r="D1292" t="inlineStr"/>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
@@ -28848,7 +28856,11 @@
           <t>sanika.arora@piri.ai</t>
         </is>
       </c>
-      <c r="D1293" t="inlineStr"/>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
@@ -28866,7 +28878,11 @@
           <t>ssingh@in.rm.com</t>
         </is>
       </c>
-      <c r="D1294" t="inlineStr"/>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
@@ -28884,7 +28900,11 @@
           <t>sanjay.chandel@joveo.com</t>
         </is>
       </c>
-      <c r="D1295" t="inlineStr"/>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
@@ -28902,7 +28922,11 @@
           <t>sanjayj@zenoti.com</t>
         </is>
       </c>
-      <c r="D1296" t="inlineStr"/>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
@@ -28920,7 +28944,11 @@
           <t>sanjay.mashere@neml.in</t>
         </is>
       </c>
-      <c r="D1297" t="inlineStr"/>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
@@ -28938,7 +28966,11 @@
           <t>sanjay.mirchandani@sttelemediagdc.in</t>
         </is>
       </c>
-      <c r="D1298" t="inlineStr"/>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
@@ -28956,7 +28988,11 @@
           <t>sshanmugaum@controlcase.com</t>
         </is>
       </c>
-      <c r="D1299" t="inlineStr"/>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
@@ -28974,7 +29010,11 @@
           <t>sanjayv@zenithsoft.com</t>
         </is>
       </c>
-      <c r="D1300" t="inlineStr"/>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
@@ -28992,7 +29032,11 @@
           <t>sanjeeta@learningspiral.co.in</t>
         </is>
       </c>
-      <c r="D1301" t="inlineStr"/>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
@@ -29010,7 +29054,11 @@
           <t>sanjeev.dhokte@accops.com</t>
         </is>
       </c>
-      <c r="D1302" t="inlineStr"/>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
@@ -29028,7 +29076,11 @@
           <t>sanjeev.kumar@drishinfo.com</t>
         </is>
       </c>
-      <c r="D1303" t="inlineStr"/>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
@@ -29046,7 +29098,11 @@
           <t>sanjeev.rana@crestechsoftware.com</t>
         </is>
       </c>
-      <c r="D1304" t="inlineStr"/>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
@@ -29064,7 +29120,11 @@
           <t>sanjeev.verma@sttelemediagdc.in</t>
         </is>
       </c>
-      <c r="D1305" t="inlineStr"/>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
@@ -29082,7 +29142,11 @@
           <t>sanjukta.biswas@algoworks.com</t>
         </is>
       </c>
-      <c r="D1306" t="inlineStr"/>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
@@ -29100,7 +29164,11 @@
           <t>snath@macrosoftinc.com</t>
         </is>
       </c>
-      <c r="D1307" t="inlineStr"/>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
@@ -29118,7 +29186,11 @@
           <t>sanketh.r@autorabit.com</t>
         </is>
       </c>
-      <c r="D1308" t="inlineStr"/>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
@@ -29136,7 +29208,11 @@
           <t>santosh@hexagonglobal.in</t>
         </is>
       </c>
-      <c r="D1309" t="inlineStr"/>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
@@ -29154,7 +29230,11 @@
           <t>santosh@agilecrm.com</t>
         </is>
       </c>
-      <c r="D1310" t="inlineStr"/>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
@@ -29172,7 +29252,11 @@
           <t>santosh.kamble@clariontechnologies.co.in</t>
         </is>
       </c>
-      <c r="D1311" t="inlineStr"/>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
@@ -29190,7 +29274,11 @@
           <t>santosh.prajapati@saggezza.com</t>
         </is>
       </c>
-      <c r="D1312" t="inlineStr"/>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
@@ -29208,7 +29296,11 @@
           <t>santosh.s@telematics4u.com</t>
         </is>
       </c>
-      <c r="D1313" t="inlineStr"/>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
@@ -29226,7 +29318,11 @@
           <t>santosh.singh@scikey.ai</t>
         </is>
       </c>
-      <c r="D1314" t="inlineStr"/>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -29340,7 +29340,11 @@
           <t>sanya.nagpal@leena.ai</t>
         </is>
       </c>
-      <c r="D1315" t="inlineStr"/>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
@@ -29358,7 +29362,11 @@
           <t>sapana.suresh@trizetto.com</t>
         </is>
       </c>
-      <c r="D1316" t="inlineStr"/>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
@@ -29376,7 +29384,11 @@
           <t>sapna@codingmart.com</t>
         </is>
       </c>
-      <c r="D1317" t="inlineStr"/>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
@@ -29394,7 +29406,11 @@
           <t>sapna.sukhrani@milessoft.com</t>
         </is>
       </c>
-      <c r="D1318" t="inlineStr"/>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
@@ -29412,7 +29428,11 @@
           <t>sapna.verma@mtxb2b.com</t>
         </is>
       </c>
-      <c r="D1319" t="inlineStr"/>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
@@ -29430,7 +29450,11 @@
           <t>sarabjeet.gill@cloudmoyo.com</t>
         </is>
       </c>
-      <c r="D1320" t="inlineStr"/>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
@@ -29448,7 +29472,11 @@
           <t>sarada.kandanur@kore.com</t>
         </is>
       </c>
-      <c r="D1321" t="inlineStr"/>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
@@ -29466,7 +29494,11 @@
           <t>sarah.john@onearchwell.com</t>
         </is>
       </c>
-      <c r="D1322" t="inlineStr"/>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
@@ -29484,7 +29516,11 @@
           <t>saraswathi@vasudhaika.net</t>
         </is>
       </c>
-      <c r="D1323" t="inlineStr"/>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -29538,7 +29538,11 @@
           <t>sarath.v@insemitech.com</t>
         </is>
       </c>
-      <c r="D1324" t="inlineStr"/>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
@@ -29556,7 +29560,11 @@
           <t>saravanakumar@coresolutionsinc.com</t>
         </is>
       </c>
-      <c r="D1325" t="inlineStr"/>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
@@ -29574,7 +29582,11 @@
           <t>spadmanabhan@coresolutionsinc.com</t>
         </is>
       </c>
-      <c r="D1326" t="inlineStr"/>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
@@ -29592,7 +29604,11 @@
           <t>saravanan.muralidharan@janes.com</t>
         </is>
       </c>
-      <c r="D1327" t="inlineStr"/>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
@@ -29610,7 +29626,11 @@
           <t>saravanan.thinagarasamy@impigertech.com</t>
         </is>
       </c>
-      <c r="D1328" t="inlineStr"/>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
@@ -29628,7 +29648,11 @@
           <t>svaze@montran.com</t>
         </is>
       </c>
-      <c r="D1329" t="inlineStr"/>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
@@ -29646,7 +29670,11 @@
           <t>sarita@nasscom.in</t>
         </is>
       </c>
-      <c r="D1330" t="inlineStr"/>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
@@ -29664,7 +29692,11 @@
           <t>sarita.singh@games24x7.com</t>
         </is>
       </c>
-      <c r="D1331" t="inlineStr"/>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
@@ -29682,7 +29714,11 @@
           <t>saroj.tripathy@muvi.com</t>
         </is>
       </c>
-      <c r="D1332" t="inlineStr"/>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
@@ -29700,7 +29736,11 @@
           <t>sasank.pandey@hevodata.com</t>
         </is>
       </c>
-      <c r="D1333" t="inlineStr"/>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
@@ -29718,7 +29758,11 @@
           <t>sasikala.vedam@prowesssoft.com</t>
         </is>
       </c>
-      <c r="D1334" t="inlineStr"/>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
@@ -29736,7 +29780,11 @@
           <t>schinnaiah@yodlee.com</t>
         </is>
       </c>
-      <c r="D1335" t="inlineStr"/>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
@@ -29754,7 +29802,11 @@
           <t>sathish.kumar@valgenesis.com</t>
         </is>
       </c>
-      <c r="D1336" t="inlineStr"/>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
@@ -29772,7 +29824,11 @@
           <t>sathyaprakash.sekaran@amnet-systems.com</t>
         </is>
       </c>
-      <c r="D1337" t="inlineStr"/>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
@@ -29790,7 +29846,11 @@
           <t>sathyanarayanan@c1exchange.com</t>
         </is>
       </c>
-      <c r="D1338" t="inlineStr"/>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -29868,7 +29868,11 @@
           <t>skumar@liquidhub.com</t>
         </is>
       </c>
-      <c r="D1339" t="inlineStr"/>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
@@ -29886,7 +29890,11 @@
           <t>satyak@wilcosource.com</t>
         </is>
       </c>
-      <c r="D1340" t="inlineStr"/>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
@@ -29904,7 +29912,11 @@
           <t>satyanrayana.s@bbm.com</t>
         </is>
       </c>
-      <c r="D1341" t="inlineStr"/>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
@@ -29922,7 +29934,11 @@
           <t>satyendu.naik@kcsitglobal.com</t>
         </is>
       </c>
-      <c r="D1342" t="inlineStr"/>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
@@ -29940,7 +29956,11 @@
           <t>satyodai.krovi@eka1.com</t>
         </is>
       </c>
-      <c r="D1343" t="inlineStr"/>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
@@ -29958,7 +29978,11 @@
           <t>saud.zafar@raydeninteractive.com</t>
         </is>
       </c>
-      <c r="D1344" t="inlineStr"/>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
@@ -29976,7 +30000,11 @@
           <t>saumya.singh@akalinfosys.com</t>
         </is>
       </c>
-      <c r="D1345" t="inlineStr"/>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
@@ -29994,7 +30022,11 @@
           <t>saurabh.jadhav@sumerusolutions.com</t>
         </is>
       </c>
-      <c r="D1346" t="inlineStr"/>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
@@ -30012,7 +30044,11 @@
           <t>slion@curologic.com</t>
         </is>
       </c>
-      <c r="D1347" t="inlineStr"/>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
@@ -30030,7 +30066,11 @@
           <t>saurabhm@tatainteractive.com</t>
         </is>
       </c>
-      <c r="D1348" t="inlineStr"/>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
@@ -30048,7 +30088,11 @@
           <t>saurabh.srivastavaa@stellarinfo.com</t>
         </is>
       </c>
-      <c r="D1349" t="inlineStr"/>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
@@ -30066,7 +30110,11 @@
           <t>saurav.sanyal@sunlife.com</t>
         </is>
       </c>
-      <c r="D1350" t="inlineStr"/>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
@@ -30084,7 +30132,11 @@
           <t>skaranth@ipass.com</t>
         </is>
       </c>
-      <c r="D1351" t="inlineStr"/>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
@@ -30102,7 +30154,11 @@
           <t>savitha.r@colortokens.com</t>
         </is>
       </c>
-      <c r="D1352" t="inlineStr"/>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
@@ -30120,7 +30176,11 @@
           <t>sayanti.s@nitorinfotech.com</t>
         </is>
       </c>
-      <c r="D1353" t="inlineStr"/>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
@@ -30138,7 +30198,11 @@
           <t>sayeram.balakumar@reflectionsinfos.com</t>
         </is>
       </c>
-      <c r="D1354" t="inlineStr"/>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
@@ -30156,7 +30220,11 @@
           <t>hameed@juntrantech.com</t>
         </is>
       </c>
-      <c r="D1355" t="inlineStr"/>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
@@ -30174,7 +30242,11 @@
           <t>sebastian.rodriguez@netcore.co.in</t>
         </is>
       </c>
-      <c r="D1356" t="inlineStr"/>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
@@ -30192,7 +30264,11 @@
           <t>seema@heptagon.in</t>
         </is>
       </c>
-      <c r="D1357" t="inlineStr"/>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
@@ -30210,7 +30286,11 @@
           <t>seema.singh@sigtuple.com</t>
         </is>
       </c>
-      <c r="D1358" t="inlineStr"/>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
@@ -30228,7 +30308,11 @@
           <t>selvi.ganapathi@talentica.com</t>
         </is>
       </c>
-      <c r="D1359" t="inlineStr"/>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
@@ -30246,7 +30330,11 @@
           <t>shagun.bhunchal@magicedtech.com</t>
         </is>
       </c>
-      <c r="D1360" t="inlineStr"/>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
@@ -30264,7 +30352,11 @@
           <t>shoaib.shah@blazeclan.com</t>
         </is>
       </c>
-      <c r="D1361" t="inlineStr"/>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
@@ -30282,7 +30374,11 @@
           <t>shahed@quadrantresource.com</t>
         </is>
       </c>
-      <c r="D1362" t="inlineStr"/>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -30396,7 +30396,11 @@
           <t>shaheen@prodevans.com</t>
         </is>
       </c>
-      <c r="D1363" t="inlineStr"/>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
@@ -30414,7 +30418,11 @@
           <t>shail.parashar@testingxperts.com</t>
         </is>
       </c>
-      <c r="D1364" t="inlineStr"/>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
@@ -30432,7 +30440,11 @@
           <t>shailender@buddi.ai</t>
         </is>
       </c>
-      <c r="D1365" t="inlineStr"/>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
@@ -30450,7 +30462,11 @@
           <t>shailesh.banaeet@nitorinfotech.com</t>
         </is>
       </c>
-      <c r="D1366" t="inlineStr"/>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
@@ -30468,7 +30484,11 @@
           <t>shailesh@mirafra.com</t>
         </is>
       </c>
-      <c r="D1367" t="inlineStr"/>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
@@ -30486,7 +30506,11 @@
           <t>shaili.trivedi@volansys.com</t>
         </is>
       </c>
-      <c r="D1368" t="inlineStr"/>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
@@ -30504,7 +30528,11 @@
           <t>shakeel@matchpointsolutions.com</t>
         </is>
       </c>
-      <c r="D1369" t="inlineStr"/>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
@@ -30522,7 +30550,11 @@
           <t>shalaka.kothawale@bizom.com</t>
         </is>
       </c>
-      <c r="D1370" t="inlineStr"/>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
@@ -30540,7 +30572,11 @@
           <t>singh.shalini@rxlogix.com</t>
         </is>
       </c>
-      <c r="D1371" t="inlineStr"/>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -30594,7 +30594,11 @@
           <t>shalinib@sixsails.com</t>
         </is>
       </c>
-      <c r="D1372" t="inlineStr"/>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
@@ -30612,7 +30616,11 @@
           <t>shalini@intelegain.com</t>
         </is>
       </c>
-      <c r="D1373" t="inlineStr"/>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
@@ -30630,7 +30638,11 @@
           <t>shalini.director@accelalpha.com</t>
         </is>
       </c>
-      <c r="D1374" t="inlineStr"/>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
@@ -30648,7 +30660,11 @@
           <t>shalini.garlapally@dataintensity.com</t>
         </is>
       </c>
-      <c r="D1375" t="inlineStr"/>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
@@ -30666,7 +30682,11 @@
           <t>shalini.james@deque.com</t>
         </is>
       </c>
-      <c r="D1376" t="inlineStr"/>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
@@ -30684,7 +30704,11 @@
           <t>shalini@erelego.com</t>
         </is>
       </c>
-      <c r="D1377" t="inlineStr"/>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
@@ -30702,7 +30726,11 @@
           <t>shalini.pathak@arkinfo.in</t>
         </is>
       </c>
-      <c r="D1378" t="inlineStr"/>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
@@ -30720,7 +30748,11 @@
           <t>shalu.chinai@indianic.com</t>
         </is>
       </c>
-      <c r="D1379" t="inlineStr"/>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
@@ -30738,7 +30770,11 @@
           <t>shambhavi.sharma@nexval.com</t>
         </is>
       </c>
-      <c r="D1380" t="inlineStr"/>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
@@ -30756,7 +30792,11 @@
           <t>shamika.kulkarni@infrabeat.com</t>
         </is>
       </c>
-      <c r="D1381" t="inlineStr"/>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
@@ -30774,7 +30814,11 @@
           <t>shamita.nandi@mjunction.in</t>
         </is>
       </c>
-      <c r="D1382" t="inlineStr"/>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
@@ -30792,7 +30836,11 @@
           <t>shamli.krishnan@cloudmoyo.com</t>
         </is>
       </c>
-      <c r="D1383" t="inlineStr"/>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
@@ -30810,7 +30858,11 @@
           <t>shamna.libu@naicoits.com</t>
         </is>
       </c>
-      <c r="D1384" t="inlineStr"/>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
@@ -30828,7 +30880,11 @@
           <t>shams.tabrez@editorialistyx.com</t>
         </is>
       </c>
-      <c r="D1385" t="inlineStr"/>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
@@ -30846,7 +30902,11 @@
           <t>shani.ramakrishnan@ritesoftware.com</t>
         </is>
       </c>
-      <c r="D1386" t="inlineStr"/>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
@@ -30864,7 +30924,11 @@
           <t>shankar.d@ritesoftware.com</t>
         </is>
       </c>
-      <c r="D1387" t="inlineStr"/>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
@@ -30882,7 +30946,11 @@
           <t>shanthi.abayam@solverminds.com</t>
         </is>
       </c>
-      <c r="D1388" t="inlineStr"/>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
@@ -30900,7 +30968,11 @@
           <t>sharad.srivastava@blumeglobal.com</t>
         </is>
       </c>
-      <c r="D1389" t="inlineStr"/>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
@@ -30918,7 +30990,11 @@
           <t>sharanya.g@concord.net</t>
         </is>
       </c>
-      <c r="D1390" t="inlineStr"/>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
@@ -30936,7 +31012,11 @@
           <t>sharat.m@fivesdigital.com</t>
         </is>
       </c>
-      <c r="D1391" t="inlineStr"/>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
@@ -30954,7 +31034,11 @@
           <t>sharika.bhatte@spiceworks.com</t>
         </is>
       </c>
-      <c r="D1392" t="inlineStr"/>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
@@ -30972,7 +31056,11 @@
           <t>sharmar@codeforce.com</t>
         </is>
       </c>
-      <c r="D1393" t="inlineStr"/>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
@@ -30990,7 +31078,11 @@
           <t>sharmila@talentployer.com</t>
         </is>
       </c>
-      <c r="D1394" t="inlineStr"/>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
@@ -31008,7 +31100,11 @@
           <t>sharmilaa.k@evolgence.com</t>
         </is>
       </c>
-      <c r="D1395" t="inlineStr"/>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -31122,7 +31122,11 @@
           <t>sharon.manaloor@litmus7.com</t>
         </is>
       </c>
-      <c r="D1396" t="inlineStr"/>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
@@ -31140,7 +31144,11 @@
           <t>sharon.narang@wibmo.com</t>
         </is>
       </c>
-      <c r="D1397" t="inlineStr"/>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
@@ -31158,7 +31166,11 @@
           <t>sharon.nijhawan@dltlabs.io</t>
         </is>
       </c>
-      <c r="D1398" t="inlineStr"/>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
@@ -31176,7 +31188,11 @@
           <t>sharvari.lingayat@milessoft.com</t>
         </is>
       </c>
-      <c r="D1399" t="inlineStr"/>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
@@ -31194,7 +31210,11 @@
           <t>sharwari.shah@revgurus.com</t>
         </is>
       </c>
-      <c r="D1400" t="inlineStr"/>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
@@ -31212,7 +31232,11 @@
           <t>shashank.s@replicon.com</t>
         </is>
       </c>
-      <c r="D1401" t="inlineStr"/>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
@@ -31230,7 +31254,11 @@
           <t>shashi.dhar@smartims.com</t>
         </is>
       </c>
-      <c r="D1402" t="inlineStr"/>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
@@ -31248,7 +31276,11 @@
           <t>shashikanta@celcomsolutions.com</t>
         </is>
       </c>
-      <c r="D1403" t="inlineStr"/>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
@@ -31266,7 +31298,11 @@
           <t>shashi@multicorewareinc.com</t>
         </is>
       </c>
-      <c r="D1404" t="inlineStr"/>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -31320,7 +31320,11 @@
           <t>shashwat.mittra@urbanladder.com</t>
         </is>
       </c>
-      <c r="D1405" t="inlineStr"/>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
@@ -31338,7 +31342,11 @@
           <t>shavee.s@algonomy.com</t>
         </is>
       </c>
-      <c r="D1406" t="inlineStr"/>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
@@ -31356,7 +31364,11 @@
           <t>sheena.malhotra@netsmartz.com</t>
         </is>
       </c>
-      <c r="D1407" t="inlineStr"/>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
@@ -31374,7 +31386,11 @@
           <t>sbiswas@cognitusconsulting.com</t>
         </is>
       </c>
-      <c r="D1408" t="inlineStr"/>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
@@ -31392,7 +31408,11 @@
           <t>sheetal.deshmukh@contractpodai.com</t>
         </is>
       </c>
-      <c r="D1409" t="inlineStr"/>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
@@ -31410,7 +31430,11 @@
           <t>sheetal@gameopedia.com</t>
         </is>
       </c>
-      <c r="D1410" t="inlineStr"/>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
@@ -31428,7 +31452,11 @@
           <t>sheetal.pote@saviantconsulting.com</t>
         </is>
       </c>
-      <c r="D1411" t="inlineStr"/>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
@@ -31446,7 +31474,11 @@
           <t>sheetal.sawant@aeriestechnology.com</t>
         </is>
       </c>
-      <c r="D1412" t="inlineStr"/>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
@@ -31464,7 +31496,11 @@
           <t>shefali@dynproindia.com</t>
         </is>
       </c>
-      <c r="D1413" t="inlineStr"/>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
@@ -31482,7 +31518,11 @@
           <t>shelton.b@cynetsystems.com</t>
         </is>
       </c>
-      <c r="D1414" t="inlineStr"/>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
@@ -31500,7 +31540,11 @@
           <t>shenoj.balaraman@rebit.org.in</t>
         </is>
       </c>
-      <c r="D1415" t="inlineStr"/>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
@@ -31518,7 +31562,11 @@
           <t>shhweta@cashkaro.com</t>
         </is>
       </c>
-      <c r="D1416" t="inlineStr"/>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
@@ -31536,7 +31584,11 @@
           <t>shikha.dhillon@decimaltech.com</t>
         </is>
       </c>
-      <c r="D1417" t="inlineStr"/>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
@@ -31554,7 +31606,11 @@
           <t>shikha@rahinfotech.com</t>
         </is>
       </c>
-      <c r="D1418" t="inlineStr"/>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
@@ -31572,7 +31628,11 @@
           <t>shikha.gupta@tatacommunications.com</t>
         </is>
       </c>
-      <c r="D1419" t="inlineStr"/>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -31650,7 +31650,11 @@
           <t>shikha.gupta@winwire.com</t>
         </is>
       </c>
-      <c r="D1420" t="inlineStr"/>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
@@ -31668,7 +31672,11 @@
           <t>shikha.kothari@klearnow.com</t>
         </is>
       </c>
-      <c r="D1421" t="inlineStr"/>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
@@ -31686,7 +31694,11 @@
           <t>shikha.soni@franconnect.com</t>
         </is>
       </c>
-      <c r="D1422" t="inlineStr"/>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
@@ -31704,7 +31716,11 @@
           <t>shilpam@codeforce.com</t>
         </is>
       </c>
-      <c r="D1423" t="inlineStr"/>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
@@ -31722,7 +31738,11 @@
           <t>shilpa.malhotra@mindtickle.com</t>
         </is>
       </c>
-      <c r="D1424" t="inlineStr"/>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
@@ -31740,7 +31760,11 @@
           <t>shilpa.reddy@aeriestechnology.com</t>
         </is>
       </c>
-      <c r="D1425" t="inlineStr"/>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
@@ -31758,7 +31782,11 @@
           <t>sshukla@anaqua.com</t>
         </is>
       </c>
-      <c r="D1426" t="inlineStr"/>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
@@ -31776,7 +31804,11 @@
           <t>shilpa.tungikar@infrasofttech.com</t>
         </is>
       </c>
-      <c r="D1427" t="inlineStr"/>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
@@ -31794,7 +31826,11 @@
           <t>shilpi.saklani@metro-gsc.in</t>
         </is>
       </c>
-      <c r="D1428" t="inlineStr"/>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
@@ -31812,7 +31848,11 @@
           <t>shilpi@netomi.com</t>
         </is>
       </c>
-      <c r="D1429" t="inlineStr"/>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
@@ -31830,7 +31870,11 @@
           <t>shilpikar@petroit.com</t>
         </is>
       </c>
-      <c r="D1430" t="inlineStr"/>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
@@ -31848,7 +31892,11 @@
           <t>shipra.lavania@wundermanthompson.com</t>
         </is>
       </c>
-      <c r="D1431" t="inlineStr"/>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
@@ -31866,7 +31914,11 @@
           <t>shipra.pandit@juspay.in</t>
         </is>
       </c>
-      <c r="D1432" t="inlineStr"/>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
@@ -31884,7 +31936,11 @@
           <t>shipra.rai@niveussolutions.com</t>
         </is>
       </c>
-      <c r="D1433" t="inlineStr"/>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
@@ -31902,7 +31958,11 @@
           <t>shirin.varghese@sugarboxnetworks.com</t>
         </is>
       </c>
-      <c r="D1434" t="inlineStr"/>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
@@ -31920,7 +31980,11 @@
           <t>shirish.bavdekar@3ds.com</t>
         </is>
       </c>
-      <c r="D1435" t="inlineStr"/>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
@@ -31938,7 +32002,11 @@
           <t>shishir.singh@milkbasket.com</t>
         </is>
       </c>
-      <c r="D1436" t="inlineStr"/>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
@@ -31956,7 +32024,11 @@
           <t>shiva@winwire.com</t>
         </is>
       </c>
-      <c r="D1437" t="inlineStr"/>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
@@ -31974,7 +32046,11 @@
           <t>shiva@comakeit.com</t>
         </is>
       </c>
-      <c r="D1438" t="inlineStr"/>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
@@ -31992,7 +32068,11 @@
           <t>sshukla@tanishasystems.com</t>
         </is>
       </c>
-      <c r="D1439" t="inlineStr"/>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
@@ -32010,7 +32090,11 @@
           <t>shivangi@sensehq.com</t>
         </is>
       </c>
-      <c r="D1440" t="inlineStr"/>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
@@ -32028,7 +32112,11 @@
           <t>shivangi@gatewaytechnolabs.com</t>
         </is>
       </c>
-      <c r="D1441" t="inlineStr"/>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
@@ -32046,7 +32134,11 @@
           <t>shivani.chaturvedi@mjunction.in</t>
         </is>
       </c>
-      <c r="D1442" t="inlineStr"/>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
@@ -32064,7 +32156,11 @@
           <t>shivani@virtualheight.com</t>
         </is>
       </c>
-      <c r="D1443" t="inlineStr"/>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -32178,7 +32178,11 @@
           <t>khanna.shivani@digitate.com</t>
         </is>
       </c>
-      <c r="D1444" t="inlineStr"/>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
@@ -32196,7 +32200,11 @@
           <t>shivani@eminds.ai</t>
         </is>
       </c>
-      <c r="D1445" t="inlineStr"/>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
@@ -32214,7 +32222,11 @@
           <t>shivani@acpl.com</t>
         </is>
       </c>
-      <c r="D1446" t="inlineStr"/>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
@@ -32232,7 +32244,11 @@
           <t>shoaib.ahmed@nuware.com</t>
         </is>
       </c>
-      <c r="D1447" t="inlineStr"/>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
@@ -32250,7 +32266,11 @@
           <t>shobana@hubilo.com</t>
         </is>
       </c>
-      <c r="D1448" t="inlineStr"/>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
@@ -32268,7 +32288,11 @@
           <t>first@softenger.com</t>
         </is>
       </c>
-      <c r="D1449" t="inlineStr"/>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
@@ -32286,7 +32310,11 @@
           <t>shraddha@digite.com</t>
         </is>
       </c>
-      <c r="D1450" t="inlineStr"/>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
@@ -32304,7 +32332,11 @@
           <t>shradha.sule@northgateps.com</t>
         </is>
       </c>
-      <c r="D1451" t="inlineStr"/>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
@@ -32322,7 +32354,11 @@
           <t>shravan@sigmoid.com</t>
         </is>
       </c>
-      <c r="D1452" t="inlineStr"/>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -32376,7 +32376,11 @@
           <t>shreeja.santosh@lrn.com</t>
         </is>
       </c>
-      <c r="D1453" t="inlineStr"/>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
@@ -32394,7 +32398,11 @@
           <t>shreelipta.mishra@blujaysolutions.com</t>
         </is>
       </c>
-      <c r="D1454" t="inlineStr"/>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
@@ -32412,7 +32420,11 @@
           <t>shreesh_katti@bluerose-tech.com</t>
         </is>
       </c>
-      <c r="D1455" t="inlineStr"/>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
@@ -32430,7 +32442,11 @@
           <t>shreyasi@valuepitch.com</t>
         </is>
       </c>
-      <c r="D1456" t="inlineStr"/>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
@@ -32448,7 +32464,11 @@
           <t>shrikant@agileglobalsolutions.com</t>
         </is>
       </c>
-      <c r="D1457" t="inlineStr"/>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
@@ -32466,7 +32486,11 @@
           <t>shruti.bhargava@netcomlearning.com</t>
         </is>
       </c>
-      <c r="D1458" t="inlineStr"/>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
@@ -32484,7 +32508,11 @@
           <t>shruti.gandhi@moolya.com</t>
         </is>
       </c>
-      <c r="D1459" t="inlineStr"/>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
@@ -32502,7 +32530,11 @@
           <t>shruti.malhotra@orange.com</t>
         </is>
       </c>
-      <c r="D1460" t="inlineStr"/>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
@@ -32520,7 +32552,11 @@
           <t>shubham@kastechssg.com</t>
         </is>
       </c>
-      <c r="D1461" t="inlineStr"/>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
@@ -32538,7 +32574,11 @@
           <t>shubha.menon@soltius.co.id</t>
         </is>
       </c>
-      <c r="D1462" t="inlineStr"/>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
@@ -32556,7 +32596,11 @@
           <t>shubhada.kale@atyeti.com</t>
         </is>
       </c>
-      <c r="D1463" t="inlineStr"/>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
@@ -32574,7 +32618,11 @@
           <t>shubhamkatiyar@ameyo.com</t>
         </is>
       </c>
-      <c r="D1464" t="inlineStr"/>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
@@ -32592,7 +32640,11 @@
           <t>bose@precisiontechcorp.com</t>
         </is>
       </c>
-      <c r="D1465" t="inlineStr"/>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
@@ -32610,7 +32662,11 @@
           <t>shubhra.narang@c-zentrix.com</t>
         </is>
       </c>
-      <c r="D1466" t="inlineStr"/>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
@@ -32628,7 +32684,11 @@
           <t>shuchi.nijhawan@ekaplus.com</t>
         </is>
       </c>
-      <c r="D1467" t="inlineStr"/>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
@@ -32646,7 +32706,11 @@
           <t>shweta@valuecoders.com</t>
         </is>
       </c>
-      <c r="D1468" t="inlineStr"/>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
@@ -32664,7 +32728,11 @@
           <t>shweta@desteksolutions.com</t>
         </is>
       </c>
-      <c r="D1469" t="inlineStr"/>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
@@ -32682,7 +32750,11 @@
           <t>smurthy@aurusinc.com</t>
         </is>
       </c>
-      <c r="D1470" t="inlineStr"/>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
@@ -32700,7 +32772,11 @@
           <t>shwetasetia@ayoconnect.id</t>
         </is>
       </c>
-      <c r="D1471" t="inlineStr"/>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
@@ -32718,7 +32794,11 @@
           <t>shweta@signitysolutions.com</t>
         </is>
       </c>
-      <c r="D1472" t="inlineStr"/>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
@@ -32736,7 +32816,11 @@
           <t>shwetha@rudderstack.com</t>
         </is>
       </c>
-      <c r="D1473" t="inlineStr"/>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
@@ -32754,7 +32838,11 @@
           <t>shyam.warrier@neudesic.com</t>
         </is>
       </c>
-      <c r="D1474" t="inlineStr"/>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
@@ -32772,7 +32860,11 @@
           <t>shyama@lesoft.com</t>
         </is>
       </c>
-      <c r="D1475" t="inlineStr"/>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
@@ -32790,7 +32882,11 @@
           <t>shyamili.satyendran@tarento.com</t>
         </is>
       </c>
-      <c r="D1476" t="inlineStr"/>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -32904,7 +32904,11 @@
           <t>shyni.k@netcon.in</t>
         </is>
       </c>
-      <c r="D1477" t="inlineStr"/>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
@@ -32922,7 +32926,11 @@
           <t>siddharth.balakrishnan@crmit.com</t>
         </is>
       </c>
-      <c r="D1478" t="inlineStr"/>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
@@ -32940,7 +32948,11 @@
           <t>siddharth.gaur@credencys.com</t>
         </is>
       </c>
-      <c r="D1479" t="inlineStr"/>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
@@ -32958,7 +32970,11 @@
           <t>sijimolj@aditiconsulting.com</t>
         </is>
       </c>
-      <c r="D1480" t="inlineStr"/>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
@@ -32976,7 +32992,11 @@
           <t>simran.kalra@avataar.me</t>
         </is>
       </c>
-      <c r="D1481" t="inlineStr"/>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
@@ -32994,7 +33014,11 @@
           <t>simran.nair@hexagon.com</t>
         </is>
       </c>
-      <c r="D1482" t="inlineStr"/>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
@@ -33012,7 +33036,11 @@
           <t>sprabakar@sciohealthanalytics.com</t>
         </is>
       </c>
-      <c r="D1483" t="inlineStr"/>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
@@ -33030,7 +33058,11 @@
           <t>sindhuja.parthasarathy@mindtickle.com</t>
         </is>
       </c>
-      <c r="D1484" t="inlineStr"/>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
@@ -33048,7 +33080,11 @@
           <t>sini@ittdigital.com</t>
         </is>
       </c>
-      <c r="D1485" t="inlineStr"/>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
@@ -33066,7 +33102,11 @@
           <t>sp@calliduscloud.com</t>
         </is>
       </c>
-      <c r="D1486" t="inlineStr"/>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
@@ -33084,7 +33124,11 @@
           <t>sirisree.dayanand@aggne.com</t>
         </is>
       </c>
-      <c r="D1487" t="inlineStr"/>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
@@ -33102,7 +33146,11 @@
           <t>sitaram.kuruganti@quadrantresource.com</t>
         </is>
       </c>
-      <c r="D1488" t="inlineStr"/>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
@@ -33120,7 +33168,11 @@
           <t>sivasankar.r@provintl.com</t>
         </is>
       </c>
-      <c r="D1489" t="inlineStr"/>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
@@ -33138,7 +33190,11 @@
           <t>smita.narkar@infinite-uptime.com</t>
         </is>
       </c>
-      <c r="D1490" t="inlineStr"/>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
@@ -33156,7 +33212,11 @@
           <t>smitha@cybersecit.net</t>
         </is>
       </c>
-      <c r="D1491" t="inlineStr"/>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
@@ -33174,7 +33234,11 @@
           <t>smitha.pradeep@aptos.com</t>
         </is>
       </c>
-      <c r="D1492" t="inlineStr"/>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
@@ -33192,7 +33256,11 @@
           <t>smitha.s@truglobal.com</t>
         </is>
       </c>
-      <c r="D1493" t="inlineStr"/>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
@@ -33210,7 +33278,11 @@
           <t>smitha.sajo@applexus.com</t>
         </is>
       </c>
-      <c r="D1494" t="inlineStr"/>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
@@ -33228,7 +33300,11 @@
           <t>smitha@alchemysolutions.asia</t>
         </is>
       </c>
-      <c r="D1495" t="inlineStr"/>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
@@ -33246,7 +33322,11 @@
           <t>sneha@merklescience.com</t>
         </is>
       </c>
-      <c r="D1496" t="inlineStr"/>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
@@ -33264,7 +33344,11 @@
           <t>sneha@virinchi.com</t>
         </is>
       </c>
-      <c r="D1497" t="inlineStr"/>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
@@ -33282,7 +33366,11 @@
           <t>sneha@tavisca.com</t>
         </is>
       </c>
-      <c r="D1498" t="inlineStr"/>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
@@ -33300,7 +33388,11 @@
           <t>snehdeep.ambarkar@cientra.com</t>
         </is>
       </c>
-      <c r="D1499" t="inlineStr"/>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
@@ -33318,7 +33410,11 @@
           <t>snigdha@saavn.com</t>
         </is>
       </c>
-      <c r="D1500" t="inlineStr"/>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -33432,7 +33432,11 @@
           <t>solution.head@solutionanalysts.com</t>
         </is>
       </c>
-      <c r="D1501" t="inlineStr"/>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
@@ -33450,7 +33454,11 @@
           <t>sgupta@encoress.com</t>
         </is>
       </c>
-      <c r="D1502" t="inlineStr"/>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
@@ -33468,7 +33476,11 @@
           <t>somesh.sharma@infostride.com</t>
         </is>
       </c>
-      <c r="D1503" t="inlineStr"/>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
@@ -33486,7 +33498,11 @@
           <t>somya.babu@gramtarang.in</t>
         </is>
       </c>
-      <c r="D1504" t="inlineStr"/>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
@@ -33504,7 +33520,11 @@
           <t>sonal.srivastava@mobilecoderz.com</t>
         </is>
       </c>
-      <c r="D1505" t="inlineStr"/>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
@@ -33522,7 +33542,11 @@
           <t>sonal.upadhyay@thepsi.com</t>
         </is>
       </c>
-      <c r="D1506" t="inlineStr"/>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
@@ -33540,7 +33564,11 @@
           <t>sonali.bhave@infrasofttech.com</t>
         </is>
       </c>
-      <c r="D1507" t="inlineStr"/>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
@@ -33558,7 +33586,11 @@
           <t>sonalip@selectsourceintl.com</t>
         </is>
       </c>
-      <c r="D1508" t="inlineStr"/>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
@@ -33576,7 +33608,11 @@
           <t>hr@cyntexa.com</t>
         </is>
       </c>
-      <c r="D1509" t="inlineStr"/>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
@@ -33594,7 +33630,11 @@
           <t>sonali.titus@intelegencia.com</t>
         </is>
       </c>
-      <c r="D1510" t="inlineStr"/>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
@@ -33612,7 +33652,11 @@
           <t>sonam.dwivedi@transunion.com</t>
         </is>
       </c>
-      <c r="D1511" t="inlineStr"/>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
@@ -33630,7 +33674,11 @@
           <t>soni@intellolabs.com</t>
         </is>
       </c>
-      <c r="D1512" t="inlineStr"/>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
@@ -33648,7 +33696,11 @@
           <t>sonia.gahlot@fivesdigital.com</t>
         </is>
       </c>
-      <c r="D1513" t="inlineStr"/>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
@@ -33666,7 +33718,11 @@
           <t>sonia@klausit.com</t>
         </is>
       </c>
-      <c r="D1514" t="inlineStr"/>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
@@ -33684,7 +33740,11 @@
           <t>sophronia@reshamandi.com</t>
         </is>
       </c>
-      <c r="D1515" t="inlineStr"/>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
@@ -33702,7 +33762,11 @@
           <t>soumya@zoondia.in</t>
         </is>
       </c>
-      <c r="D1516" t="inlineStr"/>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
@@ -33720,7 +33784,11 @@
           <t>soumya@impress.ai</t>
         </is>
       </c>
-      <c r="D1517" t="inlineStr"/>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
@@ -33738,7 +33806,11 @@
           <t>soundarya.murugaiyan@cts.co</t>
         </is>
       </c>
-      <c r="D1518" t="inlineStr"/>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
@@ -33756,7 +33828,11 @@
           <t>sourabh.jain@fiserv.com</t>
         </is>
       </c>
-      <c r="D1519" t="inlineStr"/>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
@@ -33774,7 +33850,11 @@
           <t>s.rai@drishti.com</t>
         </is>
       </c>
-      <c r="D1520" t="inlineStr"/>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
@@ -33792,7 +33872,11 @@
           <t>sourabha.ravi@valuepointsystems.com</t>
         </is>
       </c>
-      <c r="D1521" t="inlineStr"/>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
@@ -33810,7 +33894,11 @@
           <t>sourik.s@frontizo.in</t>
         </is>
       </c>
-      <c r="D1522" t="inlineStr"/>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
@@ -33828,7 +33916,11 @@
           <t>sowmya@probeinformation.com</t>
         </is>
       </c>
-      <c r="D1523" t="inlineStr"/>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
@@ -33846,7 +33938,11 @@
           <t>sowmya@ibhubs.co</t>
         </is>
       </c>
-      <c r="D1524" t="inlineStr"/>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -33960,7 +33960,11 @@
           <t>sree@straviso.com</t>
         </is>
       </c>
-      <c r="D1525" t="inlineStr"/>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
@@ -33978,7 +33982,11 @@
           <t>sree.umamaheswari@impigertech.com</t>
         </is>
       </c>
-      <c r="D1526" t="inlineStr"/>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
@@ -33996,7 +34004,11 @@
           <t>sreeja.sreedharan@skuad.io</t>
         </is>
       </c>
-      <c r="D1527" t="inlineStr"/>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
@@ -34014,7 +34026,11 @@
           <t>sreeparna.samanta@urbanladder.com</t>
         </is>
       </c>
-      <c r="D1528" t="inlineStr"/>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
@@ -34032,7 +34048,11 @@
           <t>sreepriya@eagleview.co.in</t>
         </is>
       </c>
-      <c r="D1529" t="inlineStr"/>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
@@ -34050,7 +34070,11 @@
           <t>sreeram@qualizeal.com</t>
         </is>
       </c>
-      <c r="D1530" t="inlineStr"/>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
@@ -34068,7 +34092,11 @@
           <t>smohanty@primusglobal.com</t>
         </is>
       </c>
-      <c r="D1531" t="inlineStr"/>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
@@ -34086,7 +34114,11 @@
           <t>sreevalli.k@sstech.us</t>
         </is>
       </c>
-      <c r="D1532" t="inlineStr"/>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
@@ -34104,7 +34136,11 @@
           <t>sreevidhya.shashi@itorizon.com</t>
         </is>
       </c>
-      <c r="D1533" t="inlineStr"/>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -34158,7 +34158,11 @@
           <t>sputta@aztecsoftware.com</t>
         </is>
       </c>
-      <c r="D1534" t="inlineStr"/>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
@@ -34176,7 +34180,11 @@
           <t>sridevi@sedintechnologies.com</t>
         </is>
       </c>
-      <c r="D1535" t="inlineStr"/>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
@@ -34194,7 +34202,11 @@
           <t>sridevi.v@jeevantechnologies.com</t>
         </is>
       </c>
-      <c r="D1536" t="inlineStr"/>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
@@ -34212,7 +34224,11 @@
           <t>sridhar.barige@jsw.in</t>
         </is>
       </c>
-      <c r="D1537" t="inlineStr"/>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
@@ -34230,7 +34246,11 @@
           <t>sridhar.kotha@gupshup.io</t>
         </is>
       </c>
-      <c r="D1538" t="inlineStr"/>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
@@ -34248,7 +34268,11 @@
           <t>sridhar.m@fluentgrid.com</t>
         </is>
       </c>
-      <c r="D1539" t="inlineStr"/>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
@@ -34266,7 +34290,11 @@
           <t>sridhar.srinivasan@boardex.com</t>
         </is>
       </c>
-      <c r="D1540" t="inlineStr"/>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
@@ -34284,7 +34312,11 @@
           <t>srikanthb@techpointsolutions.com</t>
         </is>
       </c>
-      <c r="D1541" t="inlineStr"/>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
@@ -34302,7 +34334,11 @@
           <t>srikanth.e@mergenit.com</t>
         </is>
       </c>
-      <c r="D1542" t="inlineStr"/>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
@@ -34320,7 +34356,11 @@
           <t>srikanth.sathyanarayana@komprise.com</t>
         </is>
       </c>
-      <c r="D1543" t="inlineStr"/>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
@@ -34338,7 +34378,11 @@
           <t>srikrishna@fugoservices.com</t>
         </is>
       </c>
-      <c r="D1544" t="inlineStr"/>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
@@ -34356,7 +34400,11 @@
           <t>srinath.g@nexval.com</t>
         </is>
       </c>
-      <c r="D1545" t="inlineStr"/>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
@@ -34374,7 +34422,11 @@
           <t>srini@technogeninc.com</t>
         </is>
       </c>
-      <c r="D1546" t="inlineStr"/>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
@@ -34392,7 +34444,11 @@
           <t>srinidhi.d@keka.com</t>
         </is>
       </c>
-      <c r="D1547" t="inlineStr"/>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
@@ -34410,7 +34466,11 @@
           <t>srinivas@collaboratesolutions.com</t>
         </is>
       </c>
-      <c r="D1548" t="inlineStr"/>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
@@ -34428,7 +34488,11 @@
           <t>srinivas.polaris@polarismanagement.com</t>
         </is>
       </c>
-      <c r="D1549" t="inlineStr"/>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
@@ -34446,7 +34510,11 @@
           <t>srinivas.talampuranam@inspirage.com</t>
         </is>
       </c>
-      <c r="D1550" t="inlineStr"/>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
@@ -34464,7 +34532,11 @@
           <t>ssundaram@tetrasoft.us</t>
         </is>
       </c>
-      <c r="D1551" t="inlineStr"/>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
@@ -34482,7 +34554,11 @@
           <t>srivathsan.mg@kumaran.com</t>
         </is>
       </c>
-      <c r="D1552" t="inlineStr"/>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
@@ -34500,7 +34576,11 @@
           <t>srividhya.deshpande@springml.com</t>
         </is>
       </c>
-      <c r="D1553" t="inlineStr"/>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
@@ -34518,7 +34598,11 @@
           <t>stephen@eoxvantage.com</t>
         </is>
       </c>
-      <c r="D1554" t="inlineStr"/>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
@@ -34536,7 +34620,11 @@
           <t>suba@geval6.com</t>
         </is>
       </c>
-      <c r="D1555" t="inlineStr"/>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
@@ -34554,7 +34642,11 @@
           <t>subbarao.c@softpath.net</t>
         </is>
       </c>
-      <c r="D1556" t="inlineStr"/>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
@@ -34572,7 +34664,11 @@
           <t>sdas@edrinfo.com</t>
         </is>
       </c>
-      <c r="D1557" t="inlineStr"/>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -34686,7 +34686,11 @@
           <t>subhashbv@macomsolutions.com</t>
         </is>
       </c>
-      <c r="D1558" t="inlineStr"/>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
@@ -34704,7 +34708,11 @@
           <t>subhash.chandra@silverlinecrm.com</t>
         </is>
       </c>
-      <c r="D1559" t="inlineStr"/>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
@@ -34722,7 +34730,11 @@
           <t>subramanian.adaikalam@sumtotalsystems. com</t>
         </is>
       </c>
-      <c r="D1560" t="inlineStr"/>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
@@ -34740,7 +34752,11 @@
           <t>subramanian@logisofttechinc.com</t>
         </is>
       </c>
-      <c r="D1561" t="inlineStr"/>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
@@ -34758,7 +34774,11 @@
           <t>sponnusamy@aequor.com</t>
         </is>
       </c>
-      <c r="D1562" t="inlineStr"/>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
@@ -34776,7 +34796,11 @@
           <t>subramanya@reshamandi.com</t>
         </is>
       </c>
-      <c r="D1563" t="inlineStr"/>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
@@ -34794,7 +34818,11 @@
           <t>subrina@flobiz.in</t>
         </is>
       </c>
-      <c r="D1564" t="inlineStr"/>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
@@ -34812,7 +34840,11 @@
           <t>mathew@techautocons.com</t>
         </is>
       </c>
-      <c r="D1565" t="inlineStr"/>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
@@ -34830,7 +34862,11 @@
           <t>sucheta.ukidve@mindstix.com</t>
         </is>
       </c>
-      <c r="D1566" t="inlineStr"/>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -34884,7 +34884,11 @@
           <t>sudeep.chakkingal@ssitsol.com</t>
         </is>
       </c>
-      <c r="D1567" t="inlineStr"/>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
@@ -34902,7 +34906,11 @@
           <t>sudeep.luthra@orange.com</t>
         </is>
       </c>
-      <c r="D1568" t="inlineStr"/>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
@@ -34920,7 +34928,11 @@
           <t>sudhaav@buddi.ai</t>
         </is>
       </c>
-      <c r="D1569" t="inlineStr"/>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
@@ -34938,7 +34950,11 @@
           <t>sudhakar@noblesoft.com</t>
         </is>
       </c>
-      <c r="D1570" t="inlineStr"/>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
@@ -34956,7 +34972,11 @@
           <t>sudhindra.sarnobat@isourceinfosystems.com</t>
         </is>
       </c>
-      <c r="D1571" t="inlineStr"/>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
@@ -34974,7 +34994,11 @@
           <t>sudhir.b@aeriestechnology.com</t>
         </is>
       </c>
-      <c r="D1572" t="inlineStr"/>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
@@ -34992,7 +35016,11 @@
           <t>sudhir.salve@searshc.com</t>
         </is>
       </c>
-      <c r="D1573" t="inlineStr"/>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
@@ -35010,7 +35038,11 @@
           <t>sudhir.shinde@nielseniq.com</t>
         </is>
       </c>
-      <c r="D1574" t="inlineStr"/>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
@@ -35028,7 +35060,11 @@
           <t>suguna.rajaram@ymedialabs.com</t>
         </is>
       </c>
-      <c r="D1575" t="inlineStr"/>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
@@ -35046,7 +35082,11 @@
           <t>suhasinir@amzetta.com</t>
         </is>
       </c>
-      <c r="D1576" t="inlineStr"/>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
@@ -35064,7 +35104,11 @@
           <t>sujathag@celcomsolutions.com</t>
         </is>
       </c>
-      <c r="D1577" t="inlineStr"/>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
@@ -35082,7 +35126,11 @@
           <t>sujatha.v@oneglobesystems.com</t>
         </is>
       </c>
-      <c r="D1578" t="inlineStr"/>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
@@ -35100,7 +35148,11 @@
           <t>sujee@crayondata.com</t>
         </is>
       </c>
-      <c r="D1579" t="inlineStr"/>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
@@ -35118,7 +35170,11 @@
           <t>sujeet.rao@diverselynx.com</t>
         </is>
       </c>
-      <c r="D1580" t="inlineStr"/>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
@@ -35136,7 +35192,11 @@
           <t>sujit.jiandani@aethereus.com</t>
         </is>
       </c>
-      <c r="D1581" t="inlineStr"/>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
@@ -35154,7 +35214,11 @@
           <t>sukeshni.tulasi@napierhealthcare.com</t>
         </is>
       </c>
-      <c r="D1582" t="inlineStr"/>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
@@ -35172,7 +35236,11 @@
           <t>sukhpreet.sandhu@itilite.com</t>
         </is>
       </c>
-      <c r="D1583" t="inlineStr"/>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -35258,7 +35258,11 @@
           <t>sulabh.daigavhane@truminds.com</t>
         </is>
       </c>
-      <c r="D1584" t="inlineStr"/>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
@@ -35276,7 +35280,11 @@
           <t>sumalatha.d@ritesoftware.com</t>
         </is>
       </c>
-      <c r="D1585" t="inlineStr"/>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
@@ -35294,7 +35302,11 @@
           <t>suman.bhattacharjee@webskitters.com</t>
         </is>
       </c>
-      <c r="D1586" t="inlineStr"/>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
@@ -35312,7 +35324,11 @@
           <t>suman.kitawat@fivesplash.in</t>
         </is>
       </c>
-      <c r="D1587" t="inlineStr"/>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
@@ -35330,7 +35346,11 @@
           <t>suman.mukherjee@ultimatesolutions.in</t>
         </is>
       </c>
-      <c r="D1588" t="inlineStr"/>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
@@ -35348,7 +35368,11 @@
           <t>sumarani.y@ekaplus.com</t>
         </is>
       </c>
-      <c r="D1589" t="inlineStr"/>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
@@ -35366,7 +35390,11 @@
           <t>sumit.k@nrconsultingservice.com</t>
         </is>
       </c>
-      <c r="D1590" t="inlineStr"/>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
@@ -35384,7 +35412,11 @@
           <t>sumit.midha@intellolabs.com</t>
         </is>
       </c>
-      <c r="D1591" t="inlineStr"/>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
@@ -35402,7 +35434,11 @@
           <t>sumukhi.jairam@nttdata.com</t>
         </is>
       </c>
-      <c r="D1592" t="inlineStr"/>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -35456,7 +35456,11 @@
           <t>sunaina@u3infotech.com</t>
         </is>
       </c>
-      <c r="D1593" t="inlineStr"/>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
@@ -35474,7 +35478,11 @@
           <t>sunandha@telliant.net</t>
         </is>
       </c>
-      <c r="D1594" t="inlineStr"/>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
@@ -35492,7 +35500,11 @@
           <t>sundeep.dasa@valgenesis.com</t>
         </is>
       </c>
-      <c r="D1595" t="inlineStr"/>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
@@ -35510,7 +35522,11 @@
           <t>sundeep.pandey@puresoftware.com</t>
         </is>
       </c>
-      <c r="D1596" t="inlineStr"/>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
@@ -35528,7 +35544,11 @@
           <t>sunder.rangarajan@businessintegra.com</t>
         </is>
       </c>
-      <c r="D1597" t="inlineStr"/>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
@@ -35546,7 +35566,11 @@
           <t>sunetra@hiverhq.com</t>
         </is>
       </c>
-      <c r="D1598" t="inlineStr"/>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
@@ -35564,7 +35588,11 @@
           <t>skapoor@milcorp.com</t>
         </is>
       </c>
-      <c r="D1599" t="inlineStr"/>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
@@ -35582,7 +35610,11 @@
           <t>sunils2@innov.in</t>
         </is>
       </c>
-      <c r="D1600" t="inlineStr"/>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
@@ -35600,7 +35632,11 @@
           <t>sunila_jaikumar@edgeverve.com</t>
         </is>
       </c>
-      <c r="D1601" t="inlineStr"/>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
@@ -35618,7 +35654,11 @@
           <t>sunit.kanoi@ag-technologies.com</t>
         </is>
       </c>
-      <c r="D1602" t="inlineStr"/>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
@@ -35636,7 +35676,11 @@
           <t>sdave@relsci.com</t>
         </is>
       </c>
-      <c r="D1603" t="inlineStr"/>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
@@ -35654,7 +35698,11 @@
           <t>sunithas@affluentgs.com</t>
         </is>
       </c>
-      <c r="D1604" t="inlineStr"/>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
@@ -35672,7 +35720,11 @@
           <t>sunny.chavan@mediaagility.com</t>
         </is>
       </c>
-      <c r="D1605" t="inlineStr"/>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
@@ -35690,7 +35742,11 @@
           <t>sunny.shroff@unitech-rio.com.br</t>
         </is>
       </c>
-      <c r="D1606" t="inlineStr"/>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
@@ -35708,7 +35764,11 @@
           <t>sunny.walia@axeno.co</t>
         </is>
       </c>
-      <c r="D1607" t="inlineStr"/>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
@@ -35726,7 +35786,11 @@
           <t>ssekhar@utopiainc.com</t>
         </is>
       </c>
-      <c r="D1608" t="inlineStr"/>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
@@ -35744,7 +35808,11 @@
           <t>supreeth.gudla@euclidinnovations.com</t>
         </is>
       </c>
-      <c r="D1609" t="inlineStr"/>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
@@ -35762,7 +35830,11 @@
           <t>supriya.a@ecolabdigitalcenter.in</t>
         </is>
       </c>
-      <c r="D1610" t="inlineStr"/>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
@@ -35780,7 +35852,11 @@
           <t>hr.mumbai@konverge.co.in</t>
         </is>
       </c>
-      <c r="D1611" t="inlineStr"/>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
@@ -35798,7 +35874,11 @@
           <t>supriya.lulla@doyen.co.in</t>
         </is>
       </c>
-      <c r="D1612" t="inlineStr"/>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
@@ -35816,7 +35896,11 @@
           <t>supriya.shonu@deeptek.ai</t>
         </is>
       </c>
-      <c r="D1613" t="inlineStr"/>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
@@ -35834,7 +35918,11 @@
           <t>surabhi.sharma@se2.com</t>
         </is>
       </c>
-      <c r="D1614" t="inlineStr"/>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
@@ -35852,7 +35940,11 @@
           <t>suraj.shylaja@g10x.com</t>
         </is>
       </c>
-      <c r="D1615" t="inlineStr"/>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
@@ -35870,7 +35962,11 @@
           <t>surajeet@stockedge.com</t>
         </is>
       </c>
-      <c r="D1616" t="inlineStr"/>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -35984,7 +35984,11 @@
           <t>surbhi.gupta@enquero.com</t>
         </is>
       </c>
-      <c r="D1617" t="inlineStr"/>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
@@ -36002,7 +36006,11 @@
           <t>surbhi.sinha@kapture.cx</t>
         </is>
       </c>
-      <c r="D1618" t="inlineStr"/>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
@@ -36020,7 +36028,11 @@
           <t>suresh.aade@foodhub.com</t>
         </is>
       </c>
-      <c r="D1619" t="inlineStr"/>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
@@ -36038,7 +36050,11 @@
           <t>sureshc@vuram.com</t>
         </is>
       </c>
-      <c r="D1620" t="inlineStr"/>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
@@ -36056,7 +36072,11 @@
           <t>suresh@truetechsolutions.in</t>
         </is>
       </c>
-      <c r="D1621" t="inlineStr"/>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
@@ -36074,7 +36094,11 @@
           <t>suresh@aspirenxt.com</t>
         </is>
       </c>
-      <c r="D1622" t="inlineStr"/>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
@@ -36092,7 +36116,11 @@
           <t>suresh.n@wrenchsolutions.com</t>
         </is>
       </c>
-      <c r="D1623" t="inlineStr"/>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
@@ -36110,7 +36138,11 @@
           <t>sureshkumar.tedlapu@criticalriver.com</t>
         </is>
       </c>
-      <c r="D1624" t="inlineStr"/>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
@@ -36128,7 +36160,11 @@
           <t>tsuresh@kutirtech.com</t>
         </is>
       </c>
-      <c r="D1625" t="inlineStr"/>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -36182,7 +36182,11 @@
           <t>surinderc@damcogroup.com</t>
         </is>
       </c>
-      <c r="D1626" t="inlineStr"/>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
@@ -36200,7 +36204,11 @@
           <t>suriya.kumar@kumaran.com</t>
         </is>
       </c>
-      <c r="D1627" t="inlineStr"/>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
@@ -36218,7 +36226,11 @@
           <t>surojitc@interrait.com</t>
         </is>
       </c>
-      <c r="D1628" t="inlineStr"/>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
@@ -36236,7 +36248,11 @@
           <t>suruchi.handa@azilen.com</t>
         </is>
       </c>
-      <c r="D1629" t="inlineStr"/>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
@@ -36254,7 +36270,11 @@
           <t>skhosla@contecglobal.com</t>
         </is>
       </c>
-      <c r="D1630" t="inlineStr"/>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
@@ -36272,7 +36292,11 @@
           <t>susan.dsilva@aujas.com</t>
         </is>
       </c>
-      <c r="D1631" t="inlineStr"/>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
@@ -36290,7 +36314,11 @@
           <t>susan@kissflow.com</t>
         </is>
       </c>
-      <c r="D1632" t="inlineStr"/>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
@@ -36308,7 +36336,11 @@
           <t>susheelk@ironsystems.com</t>
         </is>
       </c>
-      <c r="D1633" t="inlineStr"/>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
@@ -36326,7 +36358,11 @@
           <t>sushil.kumar@expediteinc.com</t>
         </is>
       </c>
-      <c r="D1634" t="inlineStr"/>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
@@ -36344,7 +36380,11 @@
           <t>sushmita.aduri@teklink.com</t>
         </is>
       </c>
-      <c r="D1635" t="inlineStr"/>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
@@ -36362,7 +36402,11 @@
           <t>susmita.kaushik@blazeclan.com</t>
         </is>
       </c>
-      <c r="D1636" t="inlineStr"/>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
@@ -36380,7 +36424,11 @@
           <t>suva.dasgupta@theblueflamelabs.com</t>
         </is>
       </c>
-      <c r="D1637" t="inlineStr"/>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
@@ -36398,7 +36446,11 @@
           <t>suvarna_f@sigma-byte.com</t>
         </is>
       </c>
-      <c r="D1638" t="inlineStr"/>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
@@ -36416,7 +36468,11 @@
           <t>suvro.karmakar@ubique-systems.com</t>
         </is>
       </c>
-      <c r="D1639" t="inlineStr"/>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
@@ -36434,7 +36490,11 @@
           <t>suzanna.tapala@ankercloud.com</t>
         </is>
       </c>
-      <c r="D1640" t="inlineStr"/>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
@@ -36452,7 +36512,11 @@
           <t>sveta.shenoy@technoidentity.com</t>
         </is>
       </c>
-      <c r="D1641" t="inlineStr"/>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
@@ -36470,7 +36534,11 @@
           <t>swagato.sengupta@areteanstech.com</t>
         </is>
       </c>
-      <c r="D1642" t="inlineStr"/>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
@@ -36488,7 +36556,11 @@
           <t>swaminathan.srinivasan@transactcampus. com</t>
         </is>
       </c>
-      <c r="D1643" t="inlineStr"/>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
@@ -36506,7 +36578,11 @@
           <t>swapna.jaladi@savantis.com</t>
         </is>
       </c>
-      <c r="D1644" t="inlineStr"/>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
@@ -36524,7 +36600,11 @@
           <t>swapna.krishna@theoptimum.net</t>
         </is>
       </c>
-      <c r="D1645" t="inlineStr"/>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
@@ -36542,7 +36622,11 @@
           <t>swapna@avestacs.com</t>
         </is>
       </c>
-      <c r="D1646" t="inlineStr"/>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
@@ -36560,7 +36644,11 @@
           <t>snag@tataunistore.com</t>
         </is>
       </c>
-      <c r="D1647" t="inlineStr"/>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
@@ -36578,7 +36666,11 @@
           <t>swapnil.bhoskar@pragmasys.in</t>
         </is>
       </c>
-      <c r="D1648" t="inlineStr"/>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
@@ -36596,7 +36688,11 @@
           <t>swapnil.pilkhane@aqmtechnologies.com</t>
         </is>
       </c>
-      <c r="D1649" t="inlineStr"/>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -36710,7 +36710,11 @@
           <t>swapnil.trikane@irisbusiness.com</t>
         </is>
       </c>
-      <c r="D1650" t="inlineStr"/>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
@@ -36728,7 +36732,11 @@
           <t>swaroop.gokhale@mediaagility.com</t>
         </is>
       </c>
-      <c r="D1651" t="inlineStr"/>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
@@ -36746,7 +36754,11 @@
           <t>swarup@polygon.technology</t>
         </is>
       </c>
-      <c r="D1652" t="inlineStr"/>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
@@ -36764,7 +36776,11 @@
           <t>swarup.chowdhury@qtsolv.com</t>
         </is>
       </c>
-      <c r="D1653" t="inlineStr"/>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
@@ -36782,7 +36798,11 @@
           <t>snarayan@atsg.net</t>
         </is>
       </c>
-      <c r="D1654" t="inlineStr"/>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
@@ -36800,7 +36820,11 @@
           <t>swathi.s@envoyglobal.com</t>
         </is>
       </c>
-      <c r="D1655" t="inlineStr"/>
+      <c r="D1655" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
@@ -36818,7 +36842,11 @@
           <t>swati.d@safe.security</t>
         </is>
       </c>
-      <c r="D1656" t="inlineStr"/>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
@@ -36836,7 +36864,11 @@
           <t>swati_m@elsner.com</t>
         </is>
       </c>
-      <c r="D1657" t="inlineStr"/>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
@@ -36854,7 +36886,11 @@
           <t>swatip@zimetrics.com</t>
         </is>
       </c>
-      <c r="D1658" t="inlineStr"/>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
@@ -36872,7 +36908,11 @@
           <t>swati.sharma@triotree.in</t>
         </is>
       </c>
-      <c r="D1659" t="inlineStr"/>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
@@ -36890,7 +36930,11 @@
           <t>suryavanshi.swati@mantratec.com</t>
         </is>
       </c>
-      <c r="D1660" t="inlineStr"/>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
@@ -36908,7 +36952,11 @@
           <t>sweety.nair@puresoftware.com</t>
         </is>
       </c>
-      <c r="D1661" t="inlineStr"/>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
@@ -36926,7 +36974,11 @@
           <t>sweety.rath@aspect.com</t>
         </is>
       </c>
-      <c r="D1662" t="inlineStr"/>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
@@ -36944,7 +36996,11 @@
           <t>sbidwai@saltside.se</t>
         </is>
       </c>
-      <c r="D1663" t="inlineStr"/>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
@@ -36962,7 +37018,11 @@
           <t>sweta@rizzle.tv</t>
         </is>
       </c>
-      <c r="D1664" t="inlineStr"/>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
@@ -36980,7 +37040,11 @@
           <t>smishra@ivp.in</t>
         </is>
       </c>
-      <c r="D1665" t="inlineStr"/>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
@@ -36998,7 +37062,11 @@
           <t>swetha@hackerearth.com</t>
         </is>
       </c>
-      <c r="D1666" t="inlineStr"/>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
@@ -37016,7 +37084,11 @@
           <t>swetha@intonenetworks.com</t>
         </is>
       </c>
-      <c r="D1667" t="inlineStr"/>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
@@ -37034,7 +37106,11 @@
           <t>syed.faizan@rsrit.com</t>
         </is>
       </c>
-      <c r="D1668" t="inlineStr"/>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
@@ -37052,7 +37128,11 @@
           <t>syed@dixitindia.com</t>
         </is>
       </c>
-      <c r="D1669" t="inlineStr"/>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
@@ -37070,7 +37150,11 @@
           <t>syed@helpshift.com</t>
         </is>
       </c>
-      <c r="D1670" t="inlineStr"/>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
@@ -37088,7 +37172,11 @@
           <t>syedmehandi@cedcoss.com</t>
         </is>
       </c>
-      <c r="D1671" t="inlineStr"/>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
@@ -37106,7 +37194,11 @@
           <t>syed@panzertechnologies.com</t>
         </is>
       </c>
-      <c r="D1672" t="inlineStr"/>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
@@ -37124,7 +37216,11 @@
           <t>syed.rizvi@megasoftsol.com</t>
         </is>
       </c>
-      <c r="D1673" t="inlineStr"/>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -37238,7 +37238,11 @@
           <t>tanisha@91social.com</t>
         </is>
       </c>
-      <c r="D1674" t="inlineStr"/>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
@@ -37256,7 +37260,11 @@
           <t>tsaxena@trimaxamericas.com</t>
         </is>
       </c>
-      <c r="D1675" t="inlineStr"/>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
@@ -37274,7 +37282,11 @@
           <t>tanuj.sonawale@riomed.com</t>
         </is>
       </c>
-      <c r="D1676" t="inlineStr"/>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
@@ -37292,7 +37304,11 @@
           <t>tanuj@codersbrain.com</t>
         </is>
       </c>
-      <c r="D1677" t="inlineStr"/>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
@@ -37310,7 +37326,11 @@
           <t>tanul.jain@cyware.com</t>
         </is>
       </c>
-      <c r="D1678" t="inlineStr"/>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
@@ -37328,7 +37348,11 @@
           <t>tanvi.s@commerceiq.ai</t>
         </is>
       </c>
-      <c r="D1679" t="inlineStr"/>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
@@ -37346,7 +37370,11 @@
           <t>tanvi.mittal@vlinkinfo.com</t>
         </is>
       </c>
-      <c r="D1680" t="inlineStr"/>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
@@ -37364,7 +37392,11 @@
           <t>tanvi.salpekar@maantic.com</t>
         </is>
       </c>
-      <c r="D1681" t="inlineStr"/>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
@@ -37382,7 +37414,11 @@
           <t>tapas@spartanpoker.com</t>
         </is>
       </c>
-      <c r="D1682" t="inlineStr"/>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
@@ -37400,7 +37436,11 @@
           <t>tara.cherian@reflectionsinfos.com</t>
         </is>
       </c>
-      <c r="D1683" t="inlineStr"/>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
@@ -37418,7 +37458,11 @@
           <t>tariq@pfinfotech.com</t>
         </is>
       </c>
-      <c r="D1684" t="inlineStr"/>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
@@ -37436,7 +37480,11 @@
           <t>tarit.bhaumik@nevaehtech.com</t>
         </is>
       </c>
-      <c r="D1685" t="inlineStr"/>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
@@ -37454,7 +37502,11 @@
           <t>tasneem.mujir@ecolab.com</t>
         </is>
       </c>
-      <c r="D1686" t="inlineStr"/>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
@@ -37472,7 +37524,11 @@
           <t>krtk@suprasoft.com</t>
         </is>
       </c>
-      <c r="D1687" t="inlineStr"/>
+      <c r="D1687" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
@@ -37490,7 +37546,11 @@
           <t>tejinder@truckx.com</t>
         </is>
       </c>
-      <c r="D1688" t="inlineStr"/>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
@@ -37508,7 +37568,11 @@
           <t>terencea@observe.ai</t>
         </is>
       </c>
-      <c r="D1689" t="inlineStr"/>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
@@ -37526,7 +37590,11 @@
           <t>tess.burlow@symbiosystech.com</t>
         </is>
       </c>
-      <c r="D1690" t="inlineStr"/>
+      <c r="D1690" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
@@ -37544,7 +37612,11 @@
           <t>thangaraj@uniphore.com</t>
         </is>
       </c>
-      <c r="D1691" t="inlineStr"/>
+      <c r="D1691" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
@@ -37562,7 +37634,11 @@
           <t>thejaswini.kulkarni@sakhatech.com</t>
         </is>
       </c>
-      <c r="D1692" t="inlineStr"/>
+      <c r="D1692" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
@@ -37580,7 +37656,11 @@
           <t>thierry.flury@orange.com</t>
         </is>
       </c>
-      <c r="D1693" t="inlineStr"/>
+      <c r="D1693" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
@@ -37598,7 +37678,11 @@
           <t>thomask@azuga.com</t>
         </is>
       </c>
-      <c r="D1694" t="inlineStr"/>
+      <c r="D1694" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
@@ -37616,7 +37700,11 @@
           <t>thrishala.n@optit.in</t>
         </is>
       </c>
-      <c r="D1695" t="inlineStr"/>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
@@ -37634,7 +37722,11 @@
           <t>timcy@exlyapp.com</t>
         </is>
       </c>
-      <c r="D1696" t="inlineStr"/>
+      <c r="D1696" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
@@ -37652,7 +37744,11 @@
           <t>tisha@loconav.com</t>
         </is>
       </c>
-      <c r="D1697" t="inlineStr"/>
+      <c r="D1697" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -37766,7 +37766,11 @@
           <t>t.jain@novelvox.com</t>
         </is>
       </c>
-      <c r="D1698" t="inlineStr"/>
+      <c r="D1698" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1699">
       <c r="A1699" t="inlineStr">
@@ -37784,7 +37788,11 @@
           <t>trisha.chandra@nirvanasolutions.com</t>
         </is>
       </c>
-      <c r="D1699" t="inlineStr"/>
+      <c r="D1699" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
@@ -37802,7 +37810,11 @@
           <t>trupti.pansare@inteliment.com</t>
         </is>
       </c>
-      <c r="D1700" t="inlineStr"/>
+      <c r="D1700" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
@@ -37820,7 +37832,11 @@
           <t>trupti.shukla@optym.com</t>
         </is>
       </c>
-      <c r="D1701" t="inlineStr"/>
+      <c r="D1701" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
@@ -37838,7 +37854,11 @@
           <t>tpochampally@hostanalytics.com</t>
         </is>
       </c>
-      <c r="D1702" t="inlineStr"/>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
@@ -37856,7 +37876,11 @@
           <t>udaykumar@cadmaxx.com</t>
         </is>
       </c>
-      <c r="D1703" t="inlineStr"/>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1704">
       <c r="A1704" t="inlineStr">
@@ -37874,7 +37898,11 @@
           <t>udit@dataincindia.com</t>
         </is>
       </c>
-      <c r="D1704" t="inlineStr"/>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1705">
       <c r="A1705" t="inlineStr">
@@ -37892,7 +37920,11 @@
           <t>usarkar@netwoven.com</t>
         </is>
       </c>
-      <c r="D1705" t="inlineStr"/>
+      <c r="D1705" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1706">
       <c r="A1706" t="inlineStr">
@@ -37910,7 +37942,11 @@
           <t>ujjwaal.d@valentabpo.com</t>
         </is>
       </c>
-      <c r="D1706" t="inlineStr"/>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1707">
       <c r="A1707" t="inlineStr">
@@ -37928,7 +37964,11 @@
           <t>uma_maheshwari@mindtree.com</t>
         </is>
       </c>
-      <c r="D1707" t="inlineStr"/>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1708">
       <c r="A1708" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -37986,7 +37986,11 @@
           <t>uma.hr@magnasoft.com</t>
         </is>
       </c>
-      <c r="D1708" t="inlineStr"/>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1709">
       <c r="A1709" t="inlineStr">
@@ -38004,7 +38008,11 @@
           <t>umar.k@acuverconsulting.com</t>
         </is>
       </c>
-      <c r="D1709" t="inlineStr"/>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1710">
       <c r="A1710" t="inlineStr">
@@ -38022,7 +38030,11 @@
           <t>umesh.kamath@maxval.com</t>
         </is>
       </c>
-      <c r="D1710" t="inlineStr"/>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1711">
       <c r="A1711" t="inlineStr">
@@ -38040,7 +38052,11 @@
           <t>umesh.yadav@dynpro.com</t>
         </is>
       </c>
-      <c r="D1711" t="inlineStr"/>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1712">
       <c r="A1712" t="inlineStr">
@@ -38058,7 +38074,11 @@
           <t>usha.chirayil@reflectionsinfos.com</t>
         </is>
       </c>
-      <c r="D1712" t="inlineStr"/>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1713">
       <c r="A1713" t="inlineStr">
@@ -38076,7 +38096,11 @@
           <t>usha.jaiswal@systematixindia.com</t>
         </is>
       </c>
-      <c r="D1713" t="inlineStr"/>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1714">
       <c r="A1714" t="inlineStr">
@@ -38094,7 +38118,11 @@
           <t>usha.nath@nathcorp.com</t>
         </is>
       </c>
-      <c r="D1714" t="inlineStr"/>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1715">
       <c r="A1715" t="inlineStr">
@@ -38112,7 +38140,11 @@
           <t>usha@cube84.com</t>
         </is>
       </c>
-      <c r="D1715" t="inlineStr"/>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1716">
       <c r="A1716" t="inlineStr">
@@ -38130,7 +38162,11 @@
           <t>uthappa.kuppanda@solugenix.com</t>
         </is>
       </c>
-      <c r="D1716" t="inlineStr"/>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1717">
       <c r="A1717" t="inlineStr">
@@ -38148,7 +38184,11 @@
           <t>utkarsht@observe.ai</t>
         </is>
       </c>
-      <c r="D1717" t="inlineStr"/>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1718">
       <c r="A1718" t="inlineStr">
@@ -38166,7 +38206,11 @@
           <t>utsav.kothari@embee.co.in</t>
         </is>
       </c>
-      <c r="D1718" t="inlineStr"/>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1719">
       <c r="A1719" t="inlineStr">
@@ -38184,7 +38228,11 @@
           <t>vaibhav.khanna@fci-ccm.com</t>
         </is>
       </c>
-      <c r="D1719" t="inlineStr"/>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1720">
       <c r="A1720" t="inlineStr">
@@ -38202,7 +38250,11 @@
           <t>vaibhav@scienaptic.com</t>
         </is>
       </c>
-      <c r="D1720" t="inlineStr"/>
+      <c r="D1720" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1721">
       <c r="A1721" t="inlineStr">
@@ -38220,7 +38272,11 @@
           <t>kumar.v@nrconsultingservice.com</t>
         </is>
       </c>
-      <c r="D1721" t="inlineStr"/>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1722">
       <c r="A1722" t="inlineStr">
@@ -38238,7 +38294,11 @@
           <t>r.vaibhav@pixis.ai</t>
         </is>
       </c>
-      <c r="D1722" t="inlineStr"/>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1723">
       <c r="A1723" t="inlineStr">
@@ -38256,7 +38316,11 @@
           <t>vaibhavi.j@infogen-labs.com</t>
         </is>
       </c>
-      <c r="D1723" t="inlineStr"/>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1724">
       <c r="A1724" t="inlineStr">
@@ -38274,7 +38338,11 @@
           <t>vaidhyanathan@infinitysts.com</t>
         </is>
       </c>
-      <c r="D1724" t="inlineStr"/>
+      <c r="D1724" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1725">
       <c r="A1725" t="inlineStr">
@@ -38292,7 +38360,11 @@
           <t>vaidyanathan@calsof.com</t>
         </is>
       </c>
-      <c r="D1725" t="inlineStr"/>
+      <c r="D1725" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1726">
       <c r="A1726" t="inlineStr">
@@ -38310,7 +38382,11 @@
           <t>vgandhi@vibrenthealth.com</t>
         </is>
       </c>
-      <c r="D1726" t="inlineStr"/>
+      <c r="D1726" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1727">
       <c r="A1727" t="inlineStr">
@@ -38328,7 +38404,11 @@
           <t>vamshi.krishna@ritesoftware.com</t>
         </is>
       </c>
-      <c r="D1727" t="inlineStr"/>
+      <c r="D1727" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1728">
       <c r="A1728" t="inlineStr">
@@ -38346,7 +38426,11 @@
           <t>vamsi.krishna@atmecs.com</t>
         </is>
       </c>
-      <c r="D1728" t="inlineStr"/>
+      <c r="D1728" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1729">
       <c r="A1729" t="inlineStr">
@@ -38364,7 +38448,11 @@
           <t>vandana.chawla@innefu.com</t>
         </is>
       </c>
-      <c r="D1729" t="inlineStr"/>
+      <c r="D1729" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1730">
       <c r="A1730" t="inlineStr">
@@ -38382,7 +38470,11 @@
           <t>vandana.pandey@adapty.com</t>
         </is>
       </c>
-      <c r="D1730" t="inlineStr"/>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1731">
       <c r="A1731" t="inlineStr">
@@ -38400,7 +38492,11 @@
           <t>vandana.roy@vfirst.com</t>
         </is>
       </c>
-      <c r="D1731" t="inlineStr"/>
+      <c r="D1731" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1732">
       <c r="A1732" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -38514,7 +38514,11 @@
           <t>vani.sathvik@ekaplus.com</t>
         </is>
       </c>
-      <c r="D1732" t="inlineStr"/>
+      <c r="D1732" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1733">
       <c r="A1733" t="inlineStr">
@@ -38532,7 +38536,11 @@
           <t>vanitha.nitin@sunlife.com</t>
         </is>
       </c>
-      <c r="D1733" t="inlineStr"/>
+      <c r="D1733" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1734">
       <c r="A1734" t="inlineStr">
@@ -38550,7 +38558,11 @@
           <t>varaprasad.m@fluentgrid.com</t>
         </is>
       </c>
-      <c r="D1734" t="inlineStr"/>
+      <c r="D1734" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1735">
       <c r="A1735" t="inlineStr">
@@ -38568,7 +38580,11 @@
           <t>vara.tupalli@amnetdigital.com</t>
         </is>
       </c>
-      <c r="D1735" t="inlineStr"/>
+      <c r="D1735" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1736">
       <c r="A1736" t="inlineStr">
@@ -38586,7 +38602,11 @@
           <t>vardhini.mani@agile-ft.com</t>
         </is>
       </c>
-      <c r="D1736" t="inlineStr"/>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1737">
       <c r="A1737" t="inlineStr">
@@ -38604,7 +38624,11 @@
           <t>varna.nair@nxtgen.com</t>
         </is>
       </c>
-      <c r="D1737" t="inlineStr"/>
+      <c r="D1737" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1738">
       <c r="A1738" t="inlineStr">
@@ -38622,7 +38646,11 @@
           <t>tyson@rapidinnovation.dev</t>
         </is>
       </c>
-      <c r="D1738" t="inlineStr"/>
+      <c r="D1738" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1739">
       <c r="A1739" t="inlineStr">
@@ -38640,7 +38668,11 @@
           <t>varsha@consystentinfo.com</t>
         </is>
       </c>
-      <c r="D1739" t="inlineStr"/>
+      <c r="D1739" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1740">
       <c r="A1740" t="inlineStr">
@@ -38658,7 +38690,11 @@
           <t>varsha.sethia@fintellix.com</t>
         </is>
       </c>
-      <c r="D1740" t="inlineStr"/>
+      <c r="D1740" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1741">
       <c r="A1741" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -38712,7 +38712,11 @@
           <t>varsha.shekar@servicemax.com</t>
         </is>
       </c>
-      <c r="D1741" t="inlineStr"/>
+      <c r="D1741" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1742">
       <c r="A1742" t="inlineStr">
@@ -38730,7 +38734,11 @@
           <t>vhatmode@tavisca.com</t>
         </is>
       </c>
-      <c r="D1742" t="inlineStr"/>
+      <c r="D1742" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1743">
       <c r="A1743" t="inlineStr">
@@ -38748,7 +38756,11 @@
           <t>varun.wadhwa@birdeye.com</t>
         </is>
       </c>
-      <c r="D1743" t="inlineStr"/>
+      <c r="D1743" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1744">
       <c r="A1744" t="inlineStr">
@@ -38766,7 +38778,11 @@
           <t>vasanthi.n@greyorange.com</t>
         </is>
       </c>
-      <c r="D1744" t="inlineStr"/>
+      <c r="D1744" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1745">
       <c r="A1745" t="inlineStr">
@@ -38784,7 +38800,11 @@
           <t>vasu.p@nbhcindia.com</t>
         </is>
       </c>
-      <c r="D1745" t="inlineStr"/>
+      <c r="D1745" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1746">
       <c r="A1746" t="inlineStr">
@@ -38802,7 +38822,11 @@
           <t>vasudevm@kensium.com</t>
         </is>
       </c>
-      <c r="D1746" t="inlineStr"/>
+      <c r="D1746" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1747">
       <c r="A1747" t="inlineStr">
@@ -38820,7 +38844,11 @@
           <t>vedha@cloudthing.com</t>
         </is>
       </c>
-      <c r="D1747" t="inlineStr"/>
+      <c r="D1747" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1748">
       <c r="A1748" t="inlineStr">
@@ -38838,7 +38866,11 @@
           <t>veena.bhagwat@infrabeat.com</t>
         </is>
       </c>
-      <c r="D1748" t="inlineStr"/>
+      <c r="D1748" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1749">
       <c r="A1749" t="inlineStr">
@@ -38856,7 +38888,11 @@
           <t>veena.rao@highstreetit.com</t>
         </is>
       </c>
-      <c r="D1749" t="inlineStr"/>
+      <c r="D1749" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1750">
       <c r="A1750" t="inlineStr">
@@ -38874,7 +38910,11 @@
           <t>veena.satish@moengage.com</t>
         </is>
       </c>
-      <c r="D1750" t="inlineStr"/>
+      <c r="D1750" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1751">
       <c r="A1751" t="inlineStr">
@@ -38892,7 +38932,11 @@
           <t>veena.vishnu@plansource.com</t>
         </is>
       </c>
-      <c r="D1751" t="inlineStr"/>
+      <c r="D1751" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1752">
       <c r="A1752" t="inlineStr">
@@ -38910,7 +38954,11 @@
           <t>vradha@v2soft.com</t>
         </is>
       </c>
-      <c r="D1752" t="inlineStr"/>
+      <c r="D1752" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1753">
       <c r="A1753" t="inlineStr">
@@ -38928,7 +38976,11 @@
           <t>cvenkat@aditiconsulting.com</t>
         </is>
       </c>
-      <c r="D1753" t="inlineStr"/>
+      <c r="D1753" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1754">
       <c r="A1754" t="inlineStr">
@@ -38946,7 +38998,11 @@
           <t>venkat.r@mresult.com</t>
         </is>
       </c>
-      <c r="D1754" t="inlineStr"/>
+      <c r="D1754" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1755">
       <c r="A1755" t="inlineStr">
@@ -38964,7 +39020,11 @@
           <t>ratnakar@corp.untd.com</t>
         </is>
       </c>
-      <c r="D1755" t="inlineStr"/>
+      <c r="D1755" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1756">
       <c r="A1756" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -39042,7 +39042,11 @@
           <t>venkata.kuruhuri@symphonycorp.com</t>
         </is>
       </c>
-      <c r="D1756" t="inlineStr"/>
+      <c r="D1756" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1757">
       <c r="A1757" t="inlineStr">
@@ -39060,7 +39064,11 @@
           <t>vs@changepond.com</t>
         </is>
       </c>
-      <c r="D1757" t="inlineStr"/>
+      <c r="D1757" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1758">
       <c r="A1758" t="inlineStr">
@@ -39078,7 +39086,11 @@
           <t>venkatesh.bj@vrize.com</t>
         </is>
       </c>
-      <c r="D1758" t="inlineStr"/>
+      <c r="D1758" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1759">
       <c r="A1759" t="inlineStr">
@@ -39096,7 +39108,11 @@
           <t>venkateshg@useready.com</t>
         </is>
       </c>
-      <c r="D1759" t="inlineStr"/>
+      <c r="D1759" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1760">
       <c r="A1760" t="inlineStr">
@@ -39114,7 +39130,11 @@
           <t>vickky.sahoo@lanetteam.com</t>
         </is>
       </c>
-      <c r="D1760" t="inlineStr"/>
+      <c r="D1760" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1761">
       <c r="A1761" t="inlineStr">
@@ -39132,7 +39152,11 @@
           <t>vidhya.sam@superops.ai</t>
         </is>
       </c>
-      <c r="D1761" t="inlineStr"/>
+      <c r="D1761" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1762">
       <c r="A1762" t="inlineStr">
@@ -39150,7 +39174,11 @@
           <t>vidya.salve@wovvtech.com</t>
         </is>
       </c>
-      <c r="D1762" t="inlineStr"/>
+      <c r="D1762" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1763">
       <c r="A1763" t="inlineStr">
@@ -39168,7 +39196,11 @@
           <t>vsrikumar@reputation.com</t>
         </is>
       </c>
-      <c r="D1763" t="inlineStr"/>
+      <c r="D1763" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1764">
       <c r="A1764" t="inlineStr">
@@ -39186,7 +39218,11 @@
           <t>vigilmthomas@tonetag.com</t>
         </is>
       </c>
-      <c r="D1764" t="inlineStr"/>
+      <c r="D1764" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1765">
       <c r="A1765" t="inlineStr">
@@ -39204,7 +39240,11 @@
           <t>vignesh.m@myhealthchampion.com</t>
         </is>
       </c>
-      <c r="D1765" t="inlineStr"/>
+      <c r="D1765" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1766">
       <c r="A1766" t="inlineStr">
@@ -39222,7 +39262,11 @@
           <t>vignesh.sanga@savantis.com</t>
         </is>
       </c>
-      <c r="D1766" t="inlineStr"/>
+      <c r="D1766" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1767">
       <c r="A1767" t="inlineStr">
@@ -39240,7 +39284,11 @@
           <t>u.vignesh@introlligent.com</t>
         </is>
       </c>
-      <c r="D1767" t="inlineStr"/>
+      <c r="D1767" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1768">
       <c r="A1768" t="inlineStr">
@@ -39258,7 +39306,11 @@
           <t>vijay.arcot@ymedialabs.com</t>
         </is>
       </c>
-      <c r="D1768" t="inlineStr"/>
+      <c r="D1768" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1769">
       <c r="A1769" t="inlineStr">
@@ -39276,7 +39328,11 @@
           <t>vijay.gupta@rahisystems.com</t>
         </is>
       </c>
-      <c r="D1769" t="inlineStr"/>
+      <c r="D1769" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1770">
       <c r="A1770" t="inlineStr">
@@ -39294,7 +39350,11 @@
           <t>vijay.kumar@bukuwarung.com</t>
         </is>
       </c>
-      <c r="D1770" t="inlineStr"/>
+      <c r="D1770" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1771">
       <c r="A1771" t="inlineStr">
@@ -39312,7 +39372,11 @@
           <t>vijaykumar.r@contus.in</t>
         </is>
       </c>
-      <c r="D1771" t="inlineStr"/>
+      <c r="D1771" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1772">
       <c r="A1772" t="inlineStr">
@@ -39330,7 +39394,11 @@
           <t>vijaypundir@dwao.in</t>
         </is>
       </c>
-      <c r="D1772" t="inlineStr"/>
+      <c r="D1772" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1773">
       <c r="A1773" t="inlineStr">
@@ -39348,7 +39416,11 @@
           <t>vijay.rai@apollo.engineer</t>
         </is>
       </c>
-      <c r="D1773" t="inlineStr"/>
+      <c r="D1773" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1774">
       <c r="A1774" t="inlineStr">
@@ -39366,7 +39438,11 @@
           <t>vijay.r@navasoftware.com</t>
         </is>
       </c>
-      <c r="D1774" t="inlineStr"/>
+      <c r="D1774" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1775">
       <c r="A1775" t="inlineStr">
@@ -39384,7 +39460,11 @@
           <t>vijay@leadiq.com</t>
         </is>
       </c>
-      <c r="D1775" t="inlineStr"/>
+      <c r="D1775" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1776">
       <c r="A1776" t="inlineStr">
@@ -39402,7 +39482,11 @@
           <t>vijay.t@ipsoft.com</t>
         </is>
       </c>
-      <c r="D1776" t="inlineStr"/>
+      <c r="D1776" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1777">
       <c r="A1777" t="inlineStr">
@@ -39420,7 +39504,11 @@
           <t>vijay.tiwari@hal-dz.com</t>
         </is>
       </c>
-      <c r="D1777" t="inlineStr"/>
+      <c r="D1777" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1778">
       <c r="A1778" t="inlineStr">
@@ -39438,7 +39526,11 @@
           <t>vijay.unnikrishnan@acqueon.com</t>
         </is>
       </c>
-      <c r="D1778" t="inlineStr"/>
+      <c r="D1778" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1779">
       <c r="A1779" t="inlineStr">
@@ -39456,7 +39548,11 @@
           <t>vijayar@sightspectrum.com</t>
         </is>
       </c>
-      <c r="D1779" t="inlineStr"/>
+      <c r="D1779" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1780">
       <c r="A1780" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -39570,7 +39570,11 @@
           <t>vijaya.talluri@g10x.com</t>
         </is>
       </c>
-      <c r="D1780" t="inlineStr"/>
+      <c r="D1780" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1781">
       <c r="A1781" t="inlineStr">
@@ -39588,7 +39592,11 @@
           <t>vijayakrishna.t@lera.us</t>
         </is>
       </c>
-      <c r="D1781" t="inlineStr"/>
+      <c r="D1781" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1782">
       <c r="A1782" t="inlineStr">
@@ -39606,7 +39614,11 @@
           <t>vijayalakshmi.s@payoda.com</t>
         </is>
       </c>
-      <c r="D1782" t="inlineStr"/>
+      <c r="D1782" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1783">
       <c r="A1783" t="inlineStr">
@@ -39624,7 +39636,11 @@
           <t>vijayeta@sellcraft.net</t>
         </is>
       </c>
-      <c r="D1783" t="inlineStr"/>
+      <c r="D1783" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1784">
       <c r="A1784" t="inlineStr">
@@ -39642,7 +39658,11 @@
           <t>vijil@appinessworld.com</t>
         </is>
       </c>
-      <c r="D1784" t="inlineStr"/>
+      <c r="D1784" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1785">
       <c r="A1785" t="inlineStr">
@@ -39660,7 +39680,11 @@
           <t>viju@imocha.io</t>
         </is>
       </c>
-      <c r="D1785" t="inlineStr"/>
+      <c r="D1785" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1786">
       <c r="A1786" t="inlineStr">
@@ -39678,7 +39702,11 @@
           <t>vikass@interrait.com</t>
         </is>
       </c>
-      <c r="D1786" t="inlineStr"/>
+      <c r="D1786" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1787">
       <c r="A1787" t="inlineStr">
@@ -39696,7 +39724,11 @@
           <t>vikas.kumar@altudo.co</t>
         </is>
       </c>
-      <c r="D1787" t="inlineStr"/>
+      <c r="D1787" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1788">
       <c r="A1788" t="inlineStr">
@@ -39714,7 +39746,11 @@
           <t>vkallianpur@cordys.com</t>
         </is>
       </c>
-      <c r="D1788" t="inlineStr"/>
+      <c r="D1788" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1789">
       <c r="A1789" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -39768,7 +39768,11 @@
           <t>vikram.kallianpur@innovapptive.com</t>
         </is>
       </c>
-      <c r="D1789" t="inlineStr"/>
+      <c r="D1789" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1790">
       <c r="A1790" t="inlineStr">
@@ -39786,7 +39790,11 @@
           <t>vikram@gyftr.com</t>
         </is>
       </c>
-      <c r="D1790" t="inlineStr"/>
+      <c r="D1790" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1791">
       <c r="A1791" t="inlineStr">
@@ -39804,7 +39812,11 @@
           <t>vikrant@weblineindia.com</t>
         </is>
       </c>
-      <c r="D1791" t="inlineStr"/>
+      <c r="D1791" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1792">
       <c r="A1792" t="inlineStr">
@@ -39822,7 +39834,11 @@
           <t>vikrant.goyal@games24x7.com</t>
         </is>
       </c>
-      <c r="D1792" t="inlineStr"/>
+      <c r="D1792" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1793">
       <c r="A1793" t="inlineStr">
@@ -39840,7 +39856,11 @@
           <t>vimal.balsara@cdpindia.com</t>
         </is>
       </c>
-      <c r="D1793" t="inlineStr"/>
+      <c r="D1793" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1794">
       <c r="A1794" t="inlineStr">
@@ -39858,7 +39878,11 @@
           <t>vinay.karrow@belwo.com</t>
         </is>
       </c>
-      <c r="D1794" t="inlineStr"/>
+      <c r="D1794" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1795">
       <c r="A1795" t="inlineStr">
@@ -39876,7 +39900,11 @@
           <t>vinay.kn@cropin.com</t>
         </is>
       </c>
-      <c r="D1795" t="inlineStr"/>
+      <c r="D1795" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1796">
       <c r="A1796" t="inlineStr">
@@ -39894,7 +39922,11 @@
           <t>vinay.mahajan@techgenies.com</t>
         </is>
       </c>
-      <c r="D1796" t="inlineStr"/>
+      <c r="D1796" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1797">
       <c r="A1797" t="inlineStr">
@@ -39912,7 +39944,11 @@
           <t>vinay.s@manthan.com</t>
         </is>
       </c>
-      <c r="D1797" t="inlineStr"/>
+      <c r="D1797" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1798">
       <c r="A1798" t="inlineStr">
@@ -39930,7 +39966,11 @@
           <t>vineela.gopalajosyula@itelligencegroup.com</t>
         </is>
       </c>
-      <c r="D1798" t="inlineStr"/>
+      <c r="D1798" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1799">
       <c r="A1799" t="inlineStr">
@@ -39948,7 +39988,11 @@
           <t>vineets@svam.com</t>
         </is>
       </c>
-      <c r="D1799" t="inlineStr"/>
+      <c r="D1799" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1800">
       <c r="A1800" t="inlineStr">
@@ -39966,7 +40010,11 @@
           <t>vinibha@dsrc.com</t>
         </is>
       </c>
-      <c r="D1800" t="inlineStr"/>
+      <c r="D1800" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1801">
       <c r="A1801" t="inlineStr">
@@ -39984,7 +40032,11 @@
           <t>vinita.jayapalan@provintl.com</t>
         </is>
       </c>
-      <c r="D1801" t="inlineStr"/>
+      <c r="D1801" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1802">
       <c r="A1802" t="inlineStr">
@@ -40002,7 +40054,11 @@
           <t>vinny@tops-int.com</t>
         </is>
       </c>
-      <c r="D1802" t="inlineStr"/>
+      <c r="D1802" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1803">
       <c r="A1803" t="inlineStr">
@@ -40020,7 +40076,11 @@
           <t>vinny@webguruz.in</t>
         </is>
       </c>
-      <c r="D1803" t="inlineStr"/>
+      <c r="D1803" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1804">
       <c r="A1804" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -40098,7 +40098,11 @@
           <t>vinod.ch@neelblue.com</t>
         </is>
       </c>
-      <c r="D1804" t="inlineStr"/>
+      <c r="D1804" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1805">
       <c r="A1805" t="inlineStr">
@@ -40116,7 +40120,11 @@
           <t>vinod.malik@a1technology.com</t>
         </is>
       </c>
-      <c r="D1805" t="inlineStr"/>
+      <c r="D1805" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1806">
       <c r="A1806" t="inlineStr">
@@ -40134,7 +40142,11 @@
           <t>vinod@ally.io</t>
         </is>
       </c>
-      <c r="D1806" t="inlineStr"/>
+      <c r="D1806" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1807">
       <c r="A1807" t="inlineStr">
@@ -40152,7 +40164,11 @@
           <t>vinod.r@o2finfosolutions.com</t>
         </is>
       </c>
-      <c r="D1807" t="inlineStr"/>
+      <c r="D1807" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1808">
       <c r="A1808" t="inlineStr">
@@ -40170,7 +40186,11 @@
           <t>vinok.sequeria@jda.com</t>
         </is>
       </c>
-      <c r="D1808" t="inlineStr"/>
+      <c r="D1808" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1809">
       <c r="A1809" t="inlineStr">
@@ -40188,7 +40208,11 @@
           <t>vinutha.govindan@resulticks.com</t>
         </is>
       </c>
-      <c r="D1809" t="inlineStr"/>
+      <c r="D1809" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1810">
       <c r="A1810" t="inlineStr">
@@ -40206,7 +40230,11 @@
           <t>vipin.r@codilar.com</t>
         </is>
       </c>
-      <c r="D1810" t="inlineStr"/>
+      <c r="D1810" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1811">
       <c r="A1811" t="inlineStr">
@@ -40224,7 +40252,11 @@
           <t>vipin.sharma@vtnetzwelt.com</t>
         </is>
       </c>
-      <c r="D1811" t="inlineStr"/>
+      <c r="D1811" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1812">
       <c r="A1812" t="inlineStr">
@@ -40242,7 +40274,11 @@
           <t>viraaj@headout.com</t>
         </is>
       </c>
-      <c r="D1812" t="inlineStr"/>
+      <c r="D1812" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1813">
       <c r="A1813" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -40296,7 +40296,11 @@
           <t>vishakha.saini@infostride.com</t>
         </is>
       </c>
-      <c r="D1813" t="inlineStr"/>
+      <c r="D1813" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1814">
       <c r="A1814" t="inlineStr">
@@ -40314,7 +40318,11 @@
           <t>vishakha.s@mindgate.in</t>
         </is>
       </c>
-      <c r="D1814" t="inlineStr"/>
+      <c r="D1814" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1815">
       <c r="A1815" t="inlineStr">
@@ -40332,7 +40340,11 @@
           <t>vishal.kanade@zenart.com</t>
         </is>
       </c>
-      <c r="D1815" t="inlineStr"/>
+      <c r="D1815" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1816">
       <c r="A1816" t="inlineStr">
@@ -40350,7 +40362,11 @@
           <t>vishal.naithani@mylofamily.com</t>
         </is>
       </c>
-      <c r="D1816" t="inlineStr"/>
+      <c r="D1816" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1817">
       <c r="A1817" t="inlineStr">
@@ -40368,7 +40384,11 @@
           <t>vishal@alumnux.com</t>
         </is>
       </c>
-      <c r="D1817" t="inlineStr"/>
+      <c r="D1817" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1818">
       <c r="A1818" t="inlineStr">
@@ -40386,7 +40406,11 @@
           <t>vishma@litmus7.com</t>
         </is>
       </c>
-      <c r="D1818" t="inlineStr"/>
+      <c r="D1818" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1819">
       <c r="A1819" t="inlineStr">
@@ -40404,7 +40428,11 @@
           <t>vishnu.vardhan@bitlasoft.com</t>
         </is>
       </c>
-      <c r="D1819" t="inlineStr"/>
+      <c r="D1819" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1820">
       <c r="A1820" t="inlineStr">
@@ -40422,7 +40450,11 @@
           <t>varora@unifocus.com</t>
         </is>
       </c>
-      <c r="D1820" t="inlineStr"/>
+      <c r="D1820" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1821">
       <c r="A1821" t="inlineStr">
@@ -40440,7 +40472,11 @@
           <t>vishva.paneri@lipi.in</t>
         </is>
       </c>
-      <c r="D1821" t="inlineStr"/>
+      <c r="D1821" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1822">
       <c r="A1822" t="inlineStr">
@@ -40458,7 +40494,11 @@
           <t>vishwa@platform9.com</t>
         </is>
       </c>
-      <c r="D1822" t="inlineStr"/>
+      <c r="D1822" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1823">
       <c r="A1823" t="inlineStr">
@@ -40476,7 +40516,11 @@
           <t>vishwajit@shivaami.com</t>
         </is>
       </c>
-      <c r="D1823" t="inlineStr"/>
+      <c r="D1823" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1824">
       <c r="A1824" t="inlineStr">
@@ -40494,7 +40538,11 @@
           <t>vishwanath.belliappa@codecraft.co.in</t>
         </is>
       </c>
-      <c r="D1824" t="inlineStr"/>
+      <c r="D1824" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1825">
       <c r="A1825" t="inlineStr">
@@ -40512,7 +40560,11 @@
           <t>vithika@optimizeitsystems.com</t>
         </is>
       </c>
-      <c r="D1825" t="inlineStr"/>
+      <c r="D1825" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1826">
       <c r="A1826" t="inlineStr">
@@ -40530,7 +40582,11 @@
           <t>vivekj@selectsourceintl.com</t>
         </is>
       </c>
-      <c r="D1826" t="inlineStr"/>
+      <c r="D1826" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1827">
       <c r="A1827" t="inlineStr">
@@ -40548,7 +40604,11 @@
           <t>vivek@pacificbpo.com</t>
         </is>
       </c>
-      <c r="D1827" t="inlineStr"/>
+      <c r="D1827" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1828">
       <c r="A1828" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -40626,7 +40626,11 @@
           <t>vivek@helius-tech.com</t>
         </is>
       </c>
-      <c r="D1828" t="inlineStr"/>
+      <c r="D1828" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1829">
       <c r="A1829" t="inlineStr">
@@ -40644,7 +40648,11 @@
           <t>vivek.saxena@newstechnologyservices.com</t>
         </is>
       </c>
-      <c r="D1829" t="inlineStr"/>
+      <c r="D1829" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1830">
       <c r="A1830" t="inlineStr">
@@ -40662,7 +40670,11 @@
           <t>viveksingh@jupitice.com</t>
         </is>
       </c>
-      <c r="D1830" t="inlineStr"/>
+      <c r="D1830" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1831">
       <c r="A1831" t="inlineStr">
@@ -40680,7 +40692,11 @@
           <t>vram.v@ducenit.com</t>
         </is>
       </c>
-      <c r="D1831" t="inlineStr"/>
+      <c r="D1831" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1832">
       <c r="A1832" t="inlineStr">
@@ -40698,7 +40714,11 @@
           <t>vyas.ramaraj@trustrace.com</t>
         </is>
       </c>
-      <c r="D1832" t="inlineStr"/>
+      <c r="D1832" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1833">
       <c r="A1833" t="inlineStr">
@@ -40716,7 +40736,11 @@
           <t>yasar.j@techmango.net</t>
         </is>
       </c>
-      <c r="D1833" t="inlineStr"/>
+      <c r="D1833" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1834">
       <c r="A1834" t="inlineStr">
@@ -40734,7 +40758,11 @@
           <t>yashika@mawaimail.com</t>
         </is>
       </c>
-      <c r="D1834" t="inlineStr"/>
+      <c r="D1834" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1835">
       <c r="A1835" t="inlineStr">
@@ -40752,7 +40780,11 @@
           <t>yashika@vrize.com</t>
         </is>
       </c>
-      <c r="D1835" t="inlineStr"/>
+      <c r="D1835" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1836">
       <c r="A1836" t="inlineStr">
@@ -40770,7 +40802,11 @@
           <t>yashpal.yadav@dynproindia.com</t>
         </is>
       </c>
-      <c r="D1836" t="inlineStr"/>
+      <c r="D1836" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1837">
       <c r="A1837" t="inlineStr">

--- a/hr_contacts.xlsx
+++ b/hr_contacts.xlsx
@@ -40824,7 +40824,11 @@
           <t>yashwanths@blubirch.com</t>
         </is>
       </c>
-      <c r="D1837" t="inlineStr"/>
+      <c r="D1837" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1838">
       <c r="A1838" t="inlineStr">
@@ -40842,7 +40846,11 @@
           <t>yesha.brahmbhatt@contentstack.com</t>
         </is>
       </c>
-      <c r="D1838" t="inlineStr"/>
+      <c r="D1838" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1839">
       <c r="A1839" t="inlineStr">
@@ -40860,7 +40868,11 @@
           <t>yogesh.waran@sandhata.com</t>
         </is>
       </c>
-      <c r="D1839" t="inlineStr"/>
+      <c r="D1839" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1840">
       <c r="A1840" t="inlineStr">
@@ -40878,7 +40890,11 @@
           <t>yogita.sharma@netsmartz.com</t>
         </is>
       </c>
-      <c r="D1840" t="inlineStr"/>
+      <c r="D1840" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1841">
       <c r="A1841" t="inlineStr">
@@ -40896,7 +40912,11 @@
           <t>zarnatrivedi@versa-networks.com</t>
         </is>
       </c>
-      <c r="D1841" t="inlineStr"/>
+      <c r="D1841" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1842">
       <c r="A1842" t="inlineStr">
@@ -40914,7 +40934,11 @@
           <t>zeeshan.khan@luminescent.digital</t>
         </is>
       </c>
-      <c r="D1842" t="inlineStr"/>
+      <c r="D1842" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1843">
       <c r="A1843" t="inlineStr">
@@ -40932,7 +40956,11 @@
           <t>zia.alam@bluepineapple.io</t>
         </is>
       </c>
-      <c r="D1843" t="inlineStr"/>
+      <c r="D1843" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1844">
       <c r="A1844" t="inlineStr">
@@ -40950,7 +40978,11 @@
           <t>zubair.wani@netmagicsolutions.com</t>
         </is>
       </c>
-      <c r="D1844" t="inlineStr"/>
+      <c r="D1844" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
     <row r="1845">
       <c r="A1845" t="inlineStr">
@@ -40968,7 +41000,11 @@
           <t>zulfiqar.syed@netcore.co.in</t>
         </is>
       </c>
-      <c r="D1845" t="inlineStr"/>
+      <c r="D1845" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
